--- a/monthly_closing_template.xlsx
+++ b/monthly_closing_template.xlsx
@@ -1071,7 +1071,7 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="199">
+  <cellXfs count="200">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1487,6 +1487,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1871,7 +1874,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="ko-KR"/>
               </a:p>
@@ -2024,7 +2027,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="ko-KR"/>
               </a:p>
@@ -2161,7 +2164,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
@@ -2273,7 +2276,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
@@ -2400,7 +2403,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
@@ -3658,8 +3661,8 @@
     </row>
     <row r="67" ht="3.75" customHeight="1"/>
     <row r="68" ht="27.75" customHeight="1"/>
-    <row r="69" ht="13.5" customHeight="1">
-      <c r="A69" s="134" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" s="199" t="inlineStr">
         <is>
           <t>※ 특이사항: 전년동기(1~5월) 영업외비용에 법인세추납액 3,100만원 포함 (업무용승용차 비용 불인정 법인세 납부액)</t>
         </is>
@@ -3724,7 +3727,7 @@
     <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="0.33203125" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="13.6640625" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.25" customHeight="1">
@@ -7039,7 +7042,7 @@
     <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -9822,12 +9825,12 @@
     <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
     <col hidden="1" width="12" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="140">
-        <f>TEXT(인덱스!$K$1,"yyyy")&amp;"년 손익계산서(전월대비 증감내역)"</f>
+        <f>"손익계산서(전월대비 증감내역)"</f>
         <v/>
       </c>
     </row>

--- a/monthly_closing_template.xlsx
+++ b/monthly_closing_template.xlsx
@@ -2593,7 +2593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="30.83203125" defaultRowHeight="11.25"/>
   <cols>
     <col width="12.33203125" customWidth="1" min="1" max="1"/>
@@ -2732,26 +2732,20 @@
       <c r="H10" s="150" t="n"/>
     </row>
     <row r="11" ht="43.5" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="129">
+      <c r="B11" s="130">
+        <f>"기간별손익계산서 ["&amp;TEXT(DATE(YEAR($K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR($K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR($K$1),1,1)),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="43.5" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="129">
         <f>TEXT($K$1,"yyyy")&amp;"년 차량별 비용현황[연간누계/월별/당월상세]"</f>
-        <v/>
-      </c>
-      <c r="C11" s="149" t="n"/>
-      <c r="D11" s="149" t="n"/>
-      <c r="E11" s="149" t="n"/>
-      <c r="F11" s="149" t="n"/>
-      <c r="G11" s="149" t="n"/>
-      <c r="H11" s="150" t="n"/>
-    </row>
-    <row r="12" ht="43.5" customHeight="1">
-      <c r="A12" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="130">
-        <f>TEXT($K$1,"yyyy")&amp;"년 운송비 개인별 비용"</f>
         <v/>
       </c>
       <c r="C12" s="149" t="n"/>
@@ -2761,56 +2755,71 @@
       <c r="G12" s="149" t="n"/>
       <c r="H12" s="150" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1"/>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="130">
+        <f>TEXT($K$1,"yyyy")&amp;"년 운송비 개인별 비용"</f>
+        <v/>
+      </c>
+      <c r="C13" s="149" t="n"/>
+      <c r="D13" s="149" t="n"/>
+      <c r="E13" s="149" t="n"/>
+      <c r="F13" s="149" t="n"/>
+      <c r="G13" s="149" t="n"/>
+      <c r="H13" s="150" t="n"/>
+    </row>
     <row r="14" ht="18" customHeight="1"/>
     <row r="15" ht="9.75" customHeight="1"/>
-    <row r="16" ht="27.75" customHeight="1">
-      <c r="D16" s="126" t="inlineStr">
+    <row r="16" ht="27.75" customHeight="1"/>
+    <row r="17" ht="15" customHeight="1">
+      <c r="D17" s="126" t="inlineStr">
         <is>
           <t>결재</t>
         </is>
       </c>
-      <c r="E16" s="126" t="inlineStr">
+      <c r="E17" s="126" t="inlineStr">
         <is>
           <t>담당</t>
         </is>
       </c>
-      <c r="F16" s="126" t="inlineStr">
+      <c r="F17" s="126" t="inlineStr">
         <is>
           <t>이사</t>
         </is>
       </c>
-      <c r="G16" s="126" t="inlineStr">
+      <c r="G17" s="126" t="inlineStr">
         <is>
           <t>임원</t>
         </is>
       </c>
-      <c r="H16" s="126" t="inlineStr">
+      <c r="H17" s="126" t="inlineStr">
         <is>
           <t>사장</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="D17" s="151" t="n"/>
-      <c r="E17" s="127" t="n"/>
-      <c r="F17" s="127" t="n"/>
-      <c r="G17" s="127" t="n"/>
-      <c r="H17" s="127" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="D18" s="151" t="n"/>
-      <c r="E18" s="151" t="n"/>
-      <c r="F18" s="151" t="n"/>
-      <c r="G18" s="151" t="n"/>
-      <c r="H18" s="151" t="n"/>
+      <c r="E18" s="127" t="n"/>
+      <c r="F18" s="127" t="n"/>
+      <c r="G18" s="127" t="n"/>
+      <c r="H18" s="127" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="D19" s="152" t="n"/>
-      <c r="E19" s="152" t="n"/>
-      <c r="F19" s="152" t="n"/>
-      <c r="G19" s="152" t="n"/>
-      <c r="H19" s="152" t="n"/>
+      <c r="D19" s="151" t="n"/>
+      <c r="E19" s="151" t="n"/>
+      <c r="F19" s="151" t="n"/>
+      <c r="G19" s="151" t="n"/>
+      <c r="H19" s="151" t="n"/>
+    </row>
+    <row r="20">
+      <c r="D20" s="152" t="n"/>
+      <c r="E20" s="152" t="n"/>
+      <c r="F20" s="152" t="n"/>
+      <c r="G20" s="152" t="n"/>
+      <c r="H20" s="152" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">

--- a/monthly_closing_template.xlsx
+++ b/monthly_closing_template.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="손익계산서" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'인덱스'!$A$1:$H$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'인덱스'!$A$1:$H$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'재무상태표(내역)'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'재무상태표(내역)'!$A$1:$K$80</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'매출액대비 비율분석'!$A$1:$K$61</definedName>
@@ -40,7 +40,7 @@
     <numFmt numFmtId="168" formatCode="###,##0"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="50">
+  <fonts count="51">
     <font>
       <name val="굴림체"/>
       <charset val="129"/>
@@ -375,8 +375,11 @@
       <color rgb="FF333333"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -437,8 +440,14 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="49">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -1066,12 +1075,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1489,6 +1507,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2593,7 +2630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="30.83203125" defaultRowHeight="11.25"/>
   <cols>
     <col width="12.33203125" customWidth="1" min="1" max="1"/>
@@ -2656,10 +2693,10 @@
       <c r="H5" s="150" t="n"/>
     </row>
     <row r="6" ht="43.5" customHeight="1">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="201" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="129" t="inlineStr">
+      <c r="B6" s="202" t="inlineStr">
         <is>
           <t xml:space="preserve">핵심지표 요약 </t>
         </is>
@@ -2687,11 +2724,11 @@
       <c r="H7" s="150" t="n"/>
     </row>
     <row r="8" hidden="1" ht="43.5" customHeight="1">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="201" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="128">
-        <f>"월별손익계산서 ["&amp;TEXT(DATE(YEAR($K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR($K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR($K$1),1,1)),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
+      <c r="B8" s="202">
+        <f>"손익계산서(매출액대비 비율분석) ["&amp;TEXT(DATE(YEAR($K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR($K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR($K$1),1,1)),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
         <v/>
       </c>
       <c r="C8" s="149" t="n"/>
@@ -2702,11 +2739,11 @@
       <c r="H8" s="150" t="n"/>
     </row>
     <row r="9" ht="43.5" customHeight="1">
-      <c r="A9" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="129">
-        <f>"손익계산서(매출액대비 비율분석) ["&amp;TEXT(DATE(YEAR($K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR($K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR($K$1),1,1)),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
+      <c r="A9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="130">
+        <f>"손익계산서(전월대비 증감) ["&amp;TEXT(EOMONTH($K$1,-2)+1,"yyyy")&amp;"년"&amp;TEXT(MONTH(EOMONTH($K$1,-2)+1),"00")&amp;"월"&amp;TEXT(DAY(EOMONTH($K$1,-2)+1),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
         <v/>
       </c>
       <c r="C9" s="149" t="n"/>
@@ -2717,11 +2754,11 @@
       <c r="H9" s="150" t="n"/>
     </row>
     <row r="10" ht="43.5" customHeight="1">
-      <c r="A10" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="130">
-        <f>"손익계산서(전월대비 증감) ["&amp;TEXT(EOMONTH($K$1,-2)+1,"yyyy")&amp;"년"&amp;TEXT(MONTH(EOMONTH($K$1,-2)+1),"00")&amp;"월"&amp;TEXT(DAY(EOMONTH($K$1,-2)+1),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
+      <c r="A10" s="201" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="203">
+        <f>"기간별손익계산서 ["&amp;TEXT(DATE(YEAR($K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR($K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR($K$1),1,1)),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
         <v/>
       </c>
       <c r="C10" s="149" t="n"/>
@@ -2733,19 +2770,25 @@
     </row>
     <row r="11" ht="43.5" customHeight="1">
       <c r="A11" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="130">
-        <f>"기간별손익계산서 ["&amp;TEXT(DATE(YEAR($K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR($K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR($K$1),1,1)),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
-        <v/>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B11" s="204">
+        <f>TEXT($K$1,"yyyy")&amp;"년 차량별 비용현황[연간누계/월별/당월상세]"</f>
+        <v/>
+      </c>
+      <c r="C11" s="149" t="n"/>
+      <c r="D11" s="149" t="n"/>
+      <c r="E11" s="149" t="n"/>
+      <c r="F11" s="149" t="n"/>
+      <c r="G11" s="149" t="n"/>
+      <c r="H11" s="150" t="n"/>
     </row>
     <row r="12" ht="43.5" customHeight="1">
-      <c r="A12" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="129">
-        <f>TEXT($K$1,"yyyy")&amp;"년 차량별 비용현황[연간누계/월별/당월상세]"</f>
+      <c r="A12" s="201" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="203">
+        <f>TEXT($K$1,"yyyy")&amp;"년 운송비 개인별 비용"</f>
         <v/>
       </c>
       <c r="C12" s="149" t="n"/>
@@ -2755,84 +2798,65 @@
       <c r="G12" s="149" t="n"/>
       <c r="H12" s="150" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="130">
-        <f>TEXT($K$1,"yyyy")&amp;"년 운송비 개인별 비용"</f>
-        <v/>
-      </c>
-      <c r="C13" s="149" t="n"/>
-      <c r="D13" s="149" t="n"/>
-      <c r="E13" s="149" t="n"/>
-      <c r="F13" s="149" t="n"/>
-      <c r="G13" s="149" t="n"/>
-      <c r="H13" s="150" t="n"/>
-    </row>
+    <row r="13" ht="18" customHeight="1"/>
     <row r="14" ht="18" customHeight="1"/>
-    <row r="15" ht="9.75" customHeight="1"/>
-    <row r="16" ht="27.75" customHeight="1"/>
+    <row r="15" ht="9.75" customHeight="1">
+      <c r="D15" s="205" t="inlineStr">
+        <is>
+          <t>결재</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="27.75" customHeight="1">
+      <c r="D16" s="200" t="n"/>
+      <c r="E16" s="206" t="inlineStr">
+        <is>
+          <t>담당</t>
+        </is>
+      </c>
+      <c r="F16" s="206" t="inlineStr">
+        <is>
+          <t>이사</t>
+        </is>
+      </c>
+      <c r="G16" s="206" t="inlineStr">
+        <is>
+          <t>임원</t>
+        </is>
+      </c>
+      <c r="H16" s="206" t="inlineStr">
+        <is>
+          <t>사장</t>
+        </is>
+      </c>
+    </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="D17" s="126" t="inlineStr">
-        <is>
-          <t>결재</t>
-        </is>
-      </c>
-      <c r="E17" s="126" t="inlineStr">
-        <is>
-          <t>담당</t>
-        </is>
-      </c>
-      <c r="F17" s="126" t="inlineStr">
-        <is>
-          <t>이사</t>
-        </is>
-      </c>
-      <c r="G17" s="126" t="inlineStr">
-        <is>
-          <t>임원</t>
-        </is>
-      </c>
-      <c r="H17" s="126" t="inlineStr">
-        <is>
-          <t>사장</t>
-        </is>
-      </c>
+      <c r="D17" s="200" t="n"/>
+      <c r="E17" s="151" t="n"/>
+      <c r="F17" s="151" t="n"/>
+      <c r="G17" s="151" t="n"/>
+      <c r="H17" s="151" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="D18" s="151" t="n"/>
-      <c r="E18" s="127" t="n"/>
-      <c r="F18" s="127" t="n"/>
-      <c r="G18" s="127" t="n"/>
-      <c r="H18" s="127" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="D19" s="151" t="n"/>
-      <c r="E19" s="151" t="n"/>
-      <c r="F19" s="151" t="n"/>
-      <c r="G19" s="151" t="n"/>
-      <c r="H19" s="151" t="n"/>
-    </row>
-    <row r="20">
-      <c r="D20" s="152" t="n"/>
-      <c r="E20" s="152" t="n"/>
-      <c r="F20" s="152" t="n"/>
-      <c r="G20" s="152" t="n"/>
-      <c r="H20" s="152" t="n"/>
-    </row>
+      <c r="D18" s="200" t="n"/>
+      <c r="E18" s="152" t="n"/>
+      <c r="F18" s="152" t="n"/>
+      <c r="G18" s="152" t="n"/>
+      <c r="H18" s="152" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="F17:F19"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="E17:E19"/>
     <mergeCell ref="B9:H9"/>
-    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="D15:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="H16:H18"/>
     <mergeCell ref="B12:H12"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="G16:G18"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="D16:D19"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B10:H10"/>

--- a/monthly_closing_template.xlsx
+++ b/monthly_closing_template.xlsx
@@ -2735,10 +2735,9 @@
           <t>구분</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>전년동기 대비 (2025년 1~6월)</t>
-        </is>
+      <c r="B5" s="2">
+        <f>"전년동기 대비 ("&amp;(YEAR(인덱스!$K$1)-1)&amp;"년 1~"&amp;MONTH(인덱스!$K$1)&amp;"월)"</f>
+        <v/>
       </c>
       <c r="C5" s="23" t="n"/>
       <c r="D5" s="23" t="n"/>
@@ -2758,10 +2757,9 @@
           <t>당기(1~6월)</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
-        <is>
-          <t>전년동기(1~6월)</t>
-        </is>
+      <c r="C6" s="27">
+        <f>"전년동기(1~"&amp;MONTH(인덱스!$K$1)&amp;"월)"</f>
+        <v/>
       </c>
       <c r="D6" s="28" t="inlineStr">
         <is>

--- a/monthly_closing_template.xlsx
+++ b/monthly_closing_template.xlsx
@@ -2685,7 +2685,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.708333333333333" right="0.708333333333333" top="1.92916666666667" bottom="0.747916666666667" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -3553,7 +3553,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="1.18125" bottom="0.9840277777777779" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -6859,7 +6859,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39375" right="0.39375" top="0.590277777777778" bottom="0.551388888888889" header="0.511811023622047" footer="0.315277777777778"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="66" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="66" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;P/2</oddFooter>
@@ -9644,7 +9644,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.590277777777778" bottom="0.354861111111111" header="0.511811023622047" footer="0.315277777777778"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="77" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="77" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;P/1</oddFooter>
@@ -13129,7 +13129,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.590277777777778" bottom="0.354861111111111" header="0.511811023622047" footer="0.315277777777778"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="61" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="61" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;P/1</oddFooter>

--- a/monthly_closing_template.xlsx
+++ b/monthly_closing_template.xlsx
@@ -2752,10 +2752,9 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="154" t="n"/>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t>당기(1~6월)</t>
-        </is>
+      <c r="B6" s="26">
+        <f>"당기(1~"&amp;MONTH(인덱스!$K$1)&amp;"월)"</f>
+        <v/>
       </c>
       <c r="C6" s="27">
         <f>"전년동기(1~"&amp;MONTH(인덱스!$K$1)&amp;"월)"</f>

--- a/monthly_closing_template.xlsx
+++ b/monthly_closing_template.xlsx
@@ -24,9 +24,6 @@
     <sheet name="손익계산서" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="그래프_월">=OFFSET(요약!$A$29,0,0,MONTH(인덱스!$K$1),1)</definedName>
-    <definedName name="그래프_매출액">=OFFSET(요약!$B$29,0,0,MONTH(인덱스!$K$1),1)</definedName>
-    <definedName name="그래프_영업이익">=OFFSET(요약!$C$29,0,0,MONTH(인덱스!$K$1),1)</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">기간별손익계산서!$A$1:$G$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'매출액대비 비율분석'!$A$1:$K$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">손익계산서!$A$1:$E$55</definedName>
@@ -36,7 +33,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">전월대비증감!$A$1:$Q$55</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'재무상태표(내역)'!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -2712,7 +2709,7 @@
           </c:errBars>
           <c:cat>
             <c:strRef>
-              <c:f>그래프_월</c:f>
+              <c:f>요약!$A$29:$A$40</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -2738,7 +2735,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>그래프_매출액</c:f>
+              <c:f>요약!$B$29:$B$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0,;\(#,##0,\);\-</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2873,7 +2870,7 @@
           </c:errBars>
           <c:cat>
             <c:strRef>
-              <c:f>그래프_월</c:f>
+              <c:f>요약!$A$29:$A$40</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -2899,7 +2896,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>그래프_영업이익</c:f>
+              <c:f>요약!$C$29:$C$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0,;\(#,##0,\);\-</c:formatCode>
                 <c:ptCount val="6"/>

--- a/monthly_closing_template.xlsx
+++ b/monthly_closing_template.xlsx
@@ -3645,7 +3645,7 @@
   <phoneticPr fontId="41" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="1.92916666666667" bottom="0.74791666666666701" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -4232,12 +4232,10 @@
         <v>1월</v>
       </c>
       <c r="B29" s="53">
-        <f>IF(1&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,1),"")</f>
-        <v>2735381647</v>
+        <f>IF(1&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,1),NA())</f>
       </c>
       <c r="C29" s="54">
-        <f>IF(1&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,1),"")</f>
-        <v>201922246</v>
+        <f>IF(1&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,1),NA())</f>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
@@ -4246,12 +4244,10 @@
         <v>2월</v>
       </c>
       <c r="B30" s="22">
-        <f>IF(2&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,2),"")</f>
-        <v>2447781972</v>
+        <f>IF(2&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,2),NA())</f>
       </c>
       <c r="C30" s="56">
-        <f>IF(2&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,2),"")</f>
-        <v>177990712</v>
+        <f>IF(2&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,2),NA())</f>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
@@ -4260,12 +4256,10 @@
         <v>3월</v>
       </c>
       <c r="B31" s="22">
-        <f>IF(3&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,3),"")</f>
-        <v>4328182055</v>
+        <f>IF(3&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,3),NA())</f>
       </c>
       <c r="C31" s="56">
-        <f>IF(3&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,3),"")</f>
-        <v>448657414</v>
+        <f>IF(3&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,3),NA())</f>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
@@ -4274,12 +4268,10 @@
         <v>4월</v>
       </c>
       <c r="B32" s="22">
-        <f>IF(4&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,4),"")</f>
-        <v>4152427518</v>
+        <f>IF(4&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,4),NA())</f>
       </c>
       <c r="C32" s="56">
-        <f>IF(4&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,4),"")</f>
-        <v>316863055</v>
+        <f>IF(4&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,4),NA())</f>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1">
@@ -4288,12 +4280,10 @@
         <v>5월</v>
       </c>
       <c r="B33" s="22">
-        <f>IF(5&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,5),"")</f>
-        <v>2755697515</v>
+        <f>IF(5&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,5),NA())</f>
       </c>
       <c r="C33" s="56">
-        <f>IF(5&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,5),"")</f>
-        <v>244208873</v>
+        <f>IF(5&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,5),NA())</f>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1">
@@ -4302,96 +4292,82 @@
         <v>6월</v>
       </c>
       <c r="B34" s="22">
-        <f>IF(6&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,6),"")</f>
-        <v>2793851873</v>
+        <f>IF(6&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,6),NA())</f>
       </c>
       <c r="C34" s="56">
-        <f>IF(6&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,6),"")</f>
-        <v>151504066</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15" hidden="1" customHeight="1">
+        <f>IF(6&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,6),NA())</f>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15" customHeight="1">
       <c r="A35" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),7,1))&amp;"월","")</f>
         <v>7월</v>
       </c>
       <c r="B35" s="22">
-        <f>IF(7&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,7),"")</f>
-        <v>2306642756</v>
+        <f>IF(7&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,7),NA())</f>
       </c>
       <c r="C35" s="56">
-        <f>IF(7&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,7),"")</f>
-        <v>166909868</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15" hidden="1" customHeight="1">
+        <f>IF(7&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,7),NA())</f>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15" customHeight="1">
       <c r="A36" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),8,1))&amp;"월","")</f>
         <v>8월</v>
       </c>
-      <c r="B36" s="22" t="str">
-        <f>IF(8&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,8),"")</f>
-        <v/>
-      </c>
-      <c r="C36" s="56" t="str">
-        <f>IF(8&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,8),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15" hidden="1" customHeight="1">
+      <c r="B36" s="22">
+        <f>IF(8&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,8),NA())</f>
+      </c>
+      <c r="C36" s="56">
+        <f>IF(8&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,8),NA())</f>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15" customHeight="1">
       <c r="A37" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),9,1))&amp;"월","")</f>
         <v>9월</v>
       </c>
-      <c r="B37" s="22" t="str">
-        <f>IF(9&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,9),"")</f>
-        <v/>
-      </c>
-      <c r="C37" s="56" t="str">
-        <f>IF(9&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,9),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15" hidden="1" customHeight="1">
+      <c r="B37" s="22">
+        <f>IF(9&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,9),NA())</f>
+      </c>
+      <c r="C37" s="56">
+        <f>IF(9&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,9),NA())</f>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15" customHeight="1">
       <c r="A38" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),10,1))&amp;"월","")</f>
         <v>10월</v>
       </c>
-      <c r="B38" s="22" t="str">
-        <f>IF(10&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,10),"")</f>
-        <v/>
-      </c>
-      <c r="C38" s="56" t="str">
-        <f>IF(10&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,10),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="15" hidden="1" customHeight="1">
+      <c r="B38" s="22">
+        <f>IF(10&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,10),NA())</f>
+      </c>
+      <c r="C38" s="56">
+        <f>IF(10&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,10),NA())</f>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15" customHeight="1">
       <c r="A39" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),11,1))&amp;"월","")</f>
         <v>11월</v>
       </c>
-      <c r="B39" s="22" t="str">
-        <f>IF(11&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,11),"")</f>
-        <v/>
-      </c>
-      <c r="C39" s="56" t="str">
-        <f>IF(11&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,11),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15" hidden="1" customHeight="1">
+      <c r="B39" s="22">
+        <f>IF(11&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,11),NA())</f>
+      </c>
+      <c r="C39" s="56">
+        <f>IF(11&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,11),NA())</f>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15" customHeight="1">
       <c r="A40" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),12,1))&amp;"월","")</f>
         <v>12월</v>
       </c>
-      <c r="B40" s="22" t="str">
-        <f>IF(12&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,12),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="56" t="str">
-        <f>IF(12&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,12),"")</f>
-        <v/>
+      <c r="B40" s="22">
+        <f>IF(12&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,12),NA())</f>
+      </c>
+      <c r="C40" s="56">
+        <f>IF(12&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,12),NA())</f>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16.5" customHeight="1">
@@ -4456,7 +4432,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="1.1812499999999999" bottom="0.98402777777777795" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -7593,7 +7569,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39374999999999999" right="0.39374999999999999" top="0.59027777777777801" bottom="0.55138888888888904" header="0.511811023622047" footer="0.31527777777777799"/>
-  <pageSetup paperSize="9" scale="66" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="66" orientation="portrait" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P/2</oddFooter>
   </headerFooter>
@@ -10258,7 +10234,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.59027777777777801" bottom="0.35486111111111102" header="0.511811023622047" footer="0.31527777777777799"/>
-  <pageSetup paperSize="9" scale="77" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="77" orientation="portrait" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P/1</oddFooter>
   </headerFooter>
@@ -13554,7 +13530,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.59027777777777801" bottom="0.35486111111111102" header="0.511811023622047" footer="0.31527777777777799"/>
-  <pageSetup paperSize="9" scale="61" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="61" orientation="portrait" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P/1</oddFooter>
   </headerFooter>
@@ -15356,6 +15332,24 @@
       <c r="H1" s="123" t="s">
         <v>194</v>
       </c>
+      <c r="I1" s="123" t="s">
+        <v>316</v>
+      </c>
+      <c r="J1" s="123" t="s">
+        <v>317</v>
+      </c>
+      <c r="K1" s="123" t="s">
+        <v>318</v>
+      </c>
+      <c r="L1" s="123" t="s">
+        <v>319</v>
+      </c>
+      <c r="M1" s="123" t="s">
+        <v>320</v>
+      </c>
+      <c r="N1" s="123" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="2" spans="1:17" ht="13.5" customHeight="1">
       <c r="A2" s="121" t="s">
@@ -15382,9 +15376,14 @@
       <c r="H2" s="124">
         <v>2793851873</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="125">
         <v>2306642756</v>
       </c>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
       <c r="P2" t="str">
         <f t="shared" ref="P2:P42" si="0">IF(A2="","",SUBSTITUTE(A2," ",""))</f>
         <v>Ⅰ.매출액</v>
@@ -15419,9 +15418,14 @@
       <c r="H3" s="124">
         <v>2793851873</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="125">
         <v>2306642756</v>
       </c>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
       <c r="P3" t="str">
         <f t="shared" si="0"/>
         <v>상품매출</v>
@@ -15456,9 +15460,14 @@
       <c r="H4" s="124">
         <v>0</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
+      <c r="I4" s="125">
+        <v>0</v>
+      </c>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="125"/>
+      <c r="M4" s="125"/>
+      <c r="N4" s="125"/>
       <c r="P4" t="str">
         <f t="shared" si="0"/>
         <v>상품수출매출</v>
@@ -15493,9 +15502,14 @@
       <c r="H5" s="124">
         <v>2262213603</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="125">
         <v>1849254182</v>
       </c>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="125"/>
       <c r="P5" t="str">
         <f t="shared" si="0"/>
         <v>Ⅱ.매출원가</v>
@@ -15530,9 +15544,14 @@
       <c r="H6" s="124">
         <v>2262213603</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="125">
         <v>1849254182</v>
       </c>
+      <c r="J6" s="125"/>
+      <c r="K6" s="125"/>
+      <c r="L6" s="125"/>
+      <c r="M6" s="125"/>
+      <c r="N6" s="125"/>
       <c r="P6" t="str">
         <f t="shared" si="0"/>
         <v>상품매출원가</v>
@@ -15567,9 +15586,14 @@
       <c r="H7" s="124">
         <v>2688555911</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="125">
         <v>2999324483</v>
       </c>
+      <c r="J7" s="125"/>
+      <c r="K7" s="125"/>
+      <c r="L7" s="125"/>
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
       <c r="P7" t="str">
         <f t="shared" si="0"/>
         <v>기초상품재고액</v>
@@ -15604,9 +15628,14 @@
       <c r="H8" s="124">
         <v>2581553781</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="125">
         <v>1731716093</v>
       </c>
+      <c r="J8" s="125"/>
+      <c r="K8" s="125"/>
+      <c r="L8" s="125"/>
+      <c r="M8" s="125"/>
+      <c r="N8" s="125"/>
       <c r="P8" t="str">
         <f t="shared" si="0"/>
         <v>당기상품매입액</v>
@@ -15641,9 +15670,14 @@
       <c r="H9" s="124">
         <v>8571606</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="125">
         <v>18170958</v>
       </c>
+      <c r="J9" s="125"/>
+      <c r="K9" s="125"/>
+      <c r="L9" s="125"/>
+      <c r="M9" s="125"/>
+      <c r="N9" s="125"/>
       <c r="P9" t="str">
         <f t="shared" si="0"/>
         <v>매입할인</v>
@@ -15678,9 +15712,14 @@
       <c r="H10" s="124">
         <v>2999324483</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="125">
         <v>2863615436</v>
       </c>
+      <c r="J10" s="125"/>
+      <c r="K10" s="125"/>
+      <c r="L10" s="125"/>
+      <c r="M10" s="125"/>
+      <c r="N10" s="125"/>
       <c r="P10" t="str">
         <f t="shared" si="0"/>
         <v>기말상품재고액</v>
@@ -15715,9 +15754,14 @@
       <c r="H11" s="124">
         <v>531638270</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="125">
         <v>457388574</v>
       </c>
+      <c r="J11" s="125"/>
+      <c r="K11" s="125"/>
+      <c r="L11" s="125"/>
+      <c r="M11" s="125"/>
+      <c r="N11" s="125"/>
       <c r="P11" t="str">
         <f t="shared" si="0"/>
         <v>Ⅲ.매출총이익</v>
@@ -15752,9 +15796,14 @@
       <c r="H12" s="124">
         <v>380134204</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="125">
         <v>290478706</v>
       </c>
+      <c r="J12" s="125"/>
+      <c r="K12" s="125"/>
+      <c r="L12" s="125"/>
+      <c r="M12" s="125"/>
+      <c r="N12" s="125"/>
       <c r="P12" t="str">
         <f t="shared" si="0"/>
         <v>Ⅳ.판매관리비</v>
@@ -15789,9 +15838,14 @@
       <c r="H13" s="124">
         <v>177293452</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="125">
         <v>168626792</v>
       </c>
+      <c r="J13" s="125"/>
+      <c r="K13" s="125"/>
+      <c r="L13" s="125"/>
+      <c r="M13" s="125"/>
+      <c r="N13" s="125"/>
       <c r="P13" t="str">
         <f t="shared" si="0"/>
         <v>직원급여</v>
@@ -15826,9 +15880,14 @@
       <c r="H14" s="124">
         <v>85067840</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
+      <c r="I14" s="125">
+        <v>0</v>
+      </c>
+      <c r="J14" s="125"/>
+      <c r="K14" s="125"/>
+      <c r="L14" s="125"/>
+      <c r="M14" s="125"/>
+      <c r="N14" s="125"/>
       <c r="P14" t="str">
         <f t="shared" si="0"/>
         <v>퇴직급여</v>
@@ -15863,9 +15922,14 @@
       <c r="H15" s="124">
         <v>15736532</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="125">
         <v>18127455</v>
       </c>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
       <c r="P15" t="str">
         <f t="shared" si="0"/>
         <v>복리후생비</v>
@@ -15900,9 +15964,14 @@
       <c r="H16" s="124">
         <v>750486</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="125">
         <v>636400</v>
       </c>
+      <c r="J16" s="125"/>
+      <c r="K16" s="125"/>
+      <c r="L16" s="125"/>
+      <c r="M16" s="125"/>
+      <c r="N16" s="125"/>
       <c r="P16" t="str">
         <f t="shared" si="0"/>
         <v>여비교통비</v>
@@ -15937,9 +16006,14 @@
       <c r="H17" s="124">
         <v>5154220</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="125">
         <v>5192422</v>
       </c>
+      <c r="J17" s="125"/>
+      <c r="K17" s="125"/>
+      <c r="L17" s="125"/>
+      <c r="M17" s="125"/>
+      <c r="N17" s="125"/>
       <c r="P17" t="str">
         <f t="shared" si="0"/>
         <v>접대비</v>
@@ -15974,9 +16048,14 @@
       <c r="H18" s="124">
         <v>1566533</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="125">
         <v>1509882</v>
       </c>
+      <c r="J18" s="125"/>
+      <c r="K18" s="125"/>
+      <c r="L18" s="125"/>
+      <c r="M18" s="125"/>
+      <c r="N18" s="125"/>
       <c r="P18" t="str">
         <f t="shared" si="0"/>
         <v>통신비</v>
@@ -16011,9 +16090,14 @@
       <c r="H19" s="124">
         <v>30840</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="125">
         <v>46640</v>
       </c>
+      <c r="J19" s="125"/>
+      <c r="K19" s="125"/>
+      <c r="L19" s="125"/>
+      <c r="M19" s="125"/>
+      <c r="N19" s="125"/>
       <c r="P19" t="str">
         <f t="shared" si="0"/>
         <v>수도광열비</v>
@@ -16048,9 +16132,14 @@
       <c r="H20" s="124">
         <v>958881</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="125">
         <v>1251761</v>
       </c>
+      <c r="J20" s="125"/>
+      <c r="K20" s="125"/>
+      <c r="L20" s="125"/>
+      <c r="M20" s="125"/>
+      <c r="N20" s="125"/>
       <c r="P20" t="str">
         <f t="shared" si="0"/>
         <v>전력비</v>
@@ -16085,9 +16174,14 @@
       <c r="H21" s="124">
         <v>10475430</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="125">
         <v>9505300</v>
       </c>
+      <c r="J21" s="125"/>
+      <c r="K21" s="125"/>
+      <c r="L21" s="125"/>
+      <c r="M21" s="125"/>
+      <c r="N21" s="125"/>
       <c r="P21" t="str">
         <f t="shared" si="0"/>
         <v>세금과공과금</v>
@@ -16122,9 +16216,14 @@
       <c r="H22" s="124">
         <v>11662649</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="125">
         <v>11662649</v>
       </c>
+      <c r="J22" s="125"/>
+      <c r="K22" s="125"/>
+      <c r="L22" s="125"/>
+      <c r="M22" s="125"/>
+      <c r="N22" s="125"/>
       <c r="P22" t="str">
         <f t="shared" si="0"/>
         <v>감가상각비</v>
@@ -16159,9 +16258,14 @@
       <c r="H23" s="124">
         <v>13500000</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="125">
         <v>13500000</v>
       </c>
+      <c r="J23" s="125"/>
+      <c r="K23" s="125"/>
+      <c r="L23" s="125"/>
+      <c r="M23" s="125"/>
+      <c r="N23" s="125"/>
       <c r="P23" t="str">
         <f t="shared" si="0"/>
         <v>지급임차료</v>
@@ -16196,9 +16300,14 @@
       <c r="H24" s="124">
         <v>4097930</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="125">
         <v>3231430</v>
       </c>
+      <c r="J24" s="125"/>
+      <c r="K24" s="125"/>
+      <c r="L24" s="125"/>
+      <c r="M24" s="125"/>
+      <c r="N24" s="125"/>
       <c r="P24" t="str">
         <f t="shared" si="0"/>
         <v>보험료</v>
@@ -16233,9 +16342,14 @@
       <c r="H25" s="124">
         <v>23455020</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="125">
         <v>25875037</v>
       </c>
+      <c r="J25" s="125"/>
+      <c r="K25" s="125"/>
+      <c r="L25" s="125"/>
+      <c r="M25" s="125"/>
+      <c r="N25" s="125"/>
       <c r="P25" t="str">
         <f t="shared" si="0"/>
         <v>차량유지비</v>
@@ -16270,9 +16384,14 @@
       <c r="H26" s="124">
         <v>2250264</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="125">
         <v>1038336</v>
       </c>
+      <c r="J26" s="125"/>
+      <c r="K26" s="125"/>
+      <c r="L26" s="125"/>
+      <c r="M26" s="125"/>
+      <c r="N26" s="125"/>
       <c r="P26" t="str">
         <f t="shared" si="0"/>
         <v>운반비</v>
@@ -16307,9 +16426,14 @@
       <c r="H27" s="124">
         <v>1602097</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="125">
         <v>5562265</v>
       </c>
+      <c r="J27" s="125"/>
+      <c r="K27" s="125"/>
+      <c r="L27" s="125"/>
+      <c r="M27" s="125"/>
+      <c r="N27" s="125"/>
       <c r="P27" t="str">
         <f t="shared" si="0"/>
         <v>소모품비</v>
@@ -16344,9 +16468,14 @@
       <c r="H28" s="124">
         <v>26532030</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="125">
         <v>24712337</v>
       </c>
+      <c r="J28" s="125"/>
+      <c r="K28" s="125"/>
+      <c r="L28" s="125"/>
+      <c r="M28" s="125"/>
+      <c r="N28" s="125"/>
       <c r="P28" t="str">
         <f t="shared" si="0"/>
         <v>지급수수료</v>
@@ -16381,9 +16510,14 @@
       <c r="H29" s="124">
         <v>0</v>
       </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
+      <c r="I29" s="125">
+        <v>0</v>
+      </c>
+      <c r="J29" s="125"/>
+      <c r="K29" s="125"/>
+      <c r="L29" s="125"/>
+      <c r="M29" s="125"/>
+      <c r="N29" s="125"/>
       <c r="P29" t="str">
         <f t="shared" si="0"/>
         <v>수출제비용</v>
@@ -16418,9 +16552,14 @@
       <c r="H30" s="124">
         <v>151504066</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="125">
         <v>166909868</v>
       </c>
+      <c r="J30" s="125"/>
+      <c r="K30" s="125"/>
+      <c r="L30" s="125"/>
+      <c r="M30" s="125"/>
+      <c r="N30" s="125"/>
       <c r="P30" t="str">
         <f t="shared" si="0"/>
         <v>Ⅴ.영업이익</v>
@@ -16455,9 +16594,14 @@
       <c r="H31" s="124">
         <v>41809649</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="125">
         <v>8088561</v>
       </c>
+      <c r="J31" s="125"/>
+      <c r="K31" s="125"/>
+      <c r="L31" s="125"/>
+      <c r="M31" s="125"/>
+      <c r="N31" s="125"/>
       <c r="P31" t="str">
         <f t="shared" si="0"/>
         <v>Ⅵ.영업외수익</v>
@@ -16492,9 +16636,14 @@
       <c r="H32" s="124">
         <v>38353858</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="125">
         <v>4637774</v>
       </c>
+      <c r="J32" s="125"/>
+      <c r="K32" s="125"/>
+      <c r="L32" s="125"/>
+      <c r="M32" s="125"/>
+      <c r="N32" s="125"/>
       <c r="P32" t="str">
         <f t="shared" si="0"/>
         <v>이자수익</v>
@@ -16529,9 +16678,14 @@
       <c r="H33" s="124">
         <v>0</v>
       </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
+      <c r="I33" s="125">
+        <v>0</v>
+      </c>
+      <c r="J33" s="125"/>
+      <c r="K33" s="125"/>
+      <c r="L33" s="125"/>
+      <c r="M33" s="125"/>
+      <c r="N33" s="125"/>
       <c r="P33" t="str">
         <f t="shared" si="0"/>
         <v>외환차익</v>
@@ -16566,9 +16720,14 @@
       <c r="H34" s="124">
         <v>0</v>
       </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
+      <c r="I34" s="125">
+        <v>0</v>
+      </c>
+      <c r="J34" s="125"/>
+      <c r="K34" s="125"/>
+      <c r="L34" s="125"/>
+      <c r="M34" s="125"/>
+      <c r="N34" s="125"/>
       <c r="P34" t="str">
         <f t="shared" si="0"/>
         <v>유형자산처분이익</v>
@@ -16603,9 +16762,14 @@
       <c r="H35" s="124">
         <v>3455791</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="125">
         <v>3450787</v>
       </c>
+      <c r="J35" s="125"/>
+      <c r="K35" s="125"/>
+      <c r="L35" s="125"/>
+      <c r="M35" s="125"/>
+      <c r="N35" s="125"/>
       <c r="P35" t="str">
         <f t="shared" si="0"/>
         <v>잡이익</v>
@@ -16640,9 +16804,14 @@
       <c r="H36" s="124">
         <v>92006</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="125">
         <v>1930</v>
       </c>
+      <c r="J36" s="125"/>
+      <c r="K36" s="125"/>
+      <c r="L36" s="125"/>
+      <c r="M36" s="125"/>
+      <c r="N36" s="125"/>
       <c r="P36" t="str">
         <f t="shared" si="0"/>
         <v>Ⅶ.영업외비용</v>
@@ -16677,9 +16846,14 @@
       <c r="H37" s="124">
         <v>0</v>
       </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
+      <c r="I37" s="125">
+        <v>0</v>
+      </c>
+      <c r="J37" s="125"/>
+      <c r="K37" s="125"/>
+      <c r="L37" s="125"/>
+      <c r="M37" s="125"/>
+      <c r="N37" s="125"/>
       <c r="P37" t="str">
         <f t="shared" si="0"/>
         <v>외환차손</v>
@@ -16714,9 +16888,14 @@
       <c r="H38" s="124">
         <v>0</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
+      <c r="I38" s="125">
+        <v>0</v>
+      </c>
+      <c r="J38" s="125"/>
+      <c r="K38" s="125"/>
+      <c r="L38" s="125"/>
+      <c r="M38" s="125"/>
+      <c r="N38" s="125"/>
       <c r="P38" t="str">
         <f t="shared" si="0"/>
         <v>유형자산처분손실</v>
@@ -16751,9 +16930,14 @@
       <c r="H39" s="124">
         <v>92006</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="125">
         <v>1930</v>
       </c>
+      <c r="J39" s="125"/>
+      <c r="K39" s="125"/>
+      <c r="L39" s="125"/>
+      <c r="M39" s="125"/>
+      <c r="N39" s="125"/>
       <c r="P39" t="str">
         <f t="shared" si="0"/>
         <v>잡손실</v>
@@ -16788,9 +16972,14 @@
       <c r="H40" s="124">
         <v>193221709</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="125">
         <v>174996499</v>
       </c>
+      <c r="J40" s="125"/>
+      <c r="K40" s="125"/>
+      <c r="L40" s="125"/>
+      <c r="M40" s="125"/>
+      <c r="N40" s="125"/>
       <c r="P40" t="str">
         <f t="shared" si="0"/>
         <v>Ⅷ.법인세비용차감전순이익</v>
@@ -16825,9 +17014,14 @@
       <c r="H41" s="124">
         <v>0</v>
       </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
+      <c r="I41" s="125">
+        <v>0</v>
+      </c>
+      <c r="J41" s="125"/>
+      <c r="K41" s="125"/>
+      <c r="L41" s="125"/>
+      <c r="M41" s="125"/>
+      <c r="N41" s="125"/>
       <c r="P41" t="str">
         <f t="shared" si="0"/>
         <v>Ⅸ.법인세비용</v>
@@ -16862,9 +17056,14 @@
       <c r="H42" s="124">
         <v>193221709</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="124">
         <v>174996499</v>
       </c>
+      <c r="J42" s="124"/>
+      <c r="K42" s="124"/>
+      <c r="L42" s="124"/>
+      <c r="M42" s="124"/>
+      <c r="N42" s="124"/>
       <c r="P42" t="str">
         <f t="shared" si="0"/>
         <v>Ⅹ.당기순이익</v>
@@ -16883,6 +17082,12 @@
       <c r="F43" s="124"/>
       <c r="G43" s="124"/>
       <c r="H43" s="124"/>
+      <c r="I43" s="124"/>
+      <c r="J43" s="124"/>
+      <c r="K43" s="124"/>
+      <c r="L43" s="124"/>
+      <c r="M43" s="124"/>
+      <c r="N43" s="124"/>
     </row>
     <row r="44" spans="1:17" ht="13.5" customHeight="1">
       <c r="A44" s="119"/>
@@ -16893,6 +17098,12 @@
       <c r="F44" s="124"/>
       <c r="G44" s="124"/>
       <c r="H44" s="124"/>
+      <c r="I44" s="124"/>
+      <c r="J44" s="124"/>
+      <c r="K44" s="124"/>
+      <c r="L44" s="124"/>
+      <c r="M44" s="124"/>
+      <c r="N44" s="124"/>
     </row>
     <row r="45" spans="1:17" ht="11.25" customHeight="1">
       <c r="A45" s="121"/>
@@ -16903,6 +17114,12 @@
       <c r="F45" s="124"/>
       <c r="G45" s="124"/>
       <c r="H45" s="124"/>
+      <c r="I45" s="124"/>
+      <c r="J45" s="124"/>
+      <c r="K45" s="124"/>
+      <c r="L45" s="124"/>
+      <c r="M45" s="124"/>
+      <c r="N45" s="124"/>
     </row>
     <row r="46" spans="1:17" ht="13.5" customHeight="1">
       <c r="A46" s="121"/>
@@ -16913,6 +17130,12 @@
       <c r="F46" s="124"/>
       <c r="G46" s="124"/>
       <c r="H46" s="124"/>
+      <c r="I46" s="124"/>
+      <c r="J46" s="124"/>
+      <c r="K46" s="124"/>
+      <c r="L46" s="124"/>
+      <c r="M46" s="124"/>
+      <c r="N46" s="124"/>
     </row>
     <row r="47" spans="1:17" ht="13.5" customHeight="1">
       <c r="A47" s="121"/>
@@ -16923,6 +17146,12 @@
       <c r="F47" s="124"/>
       <c r="G47" s="124"/>
       <c r="H47" s="124"/>
+      <c r="I47" s="124"/>
+      <c r="J47" s="124"/>
+      <c r="K47" s="124"/>
+      <c r="L47" s="124"/>
+      <c r="M47" s="124"/>
+      <c r="N47" s="124"/>
     </row>
     <row r="48" spans="1:17" ht="13.5" customHeight="1">
       <c r="A48" s="121"/>
@@ -16933,6 +17162,12 @@
       <c r="F48" s="124"/>
       <c r="G48" s="124"/>
       <c r="H48" s="124"/>
+      <c r="I48" s="124"/>
+      <c r="J48" s="124"/>
+      <c r="K48" s="124"/>
+      <c r="L48" s="124"/>
+      <c r="M48" s="124"/>
+      <c r="N48" s="124"/>
     </row>
     <row r="49" ht="11.25" customHeight="1"/>
     <row r="50" ht="11.25" customHeight="1"/>

--- a/monthly_closing_template.xlsx
+++ b/monthly_closing_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\창현관리부\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA27388-5824-4379-A7E0-FEF1691E8F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAADDAC-EA27-4C71-BD9A-32D87E14E000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2385" yWindow="975" windowWidth="21930" windowHeight="14250" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="인덱스" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">전월대비증감!$A$1:$Q$55</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'재무상태표(내역)'!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="318">
   <si>
     <t>결산기준일</t>
   </si>
@@ -106,18 +106,9 @@
     <t>■ 손익 요약  (단위: 천원)</t>
   </si>
   <si>
-    <t>전년동기 대비 (2025년 1~6월)</t>
-  </si>
-  <si>
     <t>전기 대비 (2025년 연간)</t>
   </si>
   <si>
-    <t>당기(1~6월)</t>
-  </si>
-  <si>
-    <t>전년동기(1~6월)</t>
-  </si>
-  <si>
     <t>증감액</t>
   </si>
   <si>
@@ -656,9 +647,6 @@
   </si>
   <si>
     <t>5월: 총36명, 6월: 총36명</t>
-  </si>
-  <si>
-    <t>변동없음</t>
   </si>
   <si>
     <t>6월:상반기 퇴직연금 불입</t>
@@ -2196,26 +2184,23 @@
     <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2227,6 +2212,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2245,9 +2236,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2711,7 +2699,7 @@
             <c:strRef>
               <c:f>요약!$A$29:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1월</c:v>
                 </c:pt>
@@ -2730,6 +2718,24 @@
                 <c:pt idx="5">
                   <c:v>6월</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>7월</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8월</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9월</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10월</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11월</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12월</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
@@ -2738,7 +2744,7 @@
               <c:f>요약!$B$29:$B$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0,;\(#,##0,\);\-</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>2735381647</c:v>
                 </c:pt>
@@ -2756,6 +2762,24 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>2793851873</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2306642756</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2872,7 +2896,7 @@
             <c:strRef>
               <c:f>요약!$A$29:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1월</c:v>
                 </c:pt>
@@ -2891,6 +2915,24 @@
                 <c:pt idx="5">
                   <c:v>6월</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>7월</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8월</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9월</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10월</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11월</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12월</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
@@ -2899,7 +2941,7 @@
               <c:f>요약!$C$29:$C$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0,;\(#,##0,\);\-</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>201922246</c:v>
                 </c:pt>
@@ -2917,6 +2959,24 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>151504066</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>166909868</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3411,17 +3471,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1">
-      <c r="A1" s="134" t="str">
+      <c r="A1" s="126" t="str">
         <f>TEXT($K$1,"yyyy")&amp;"년 1월~"&amp;MONTH($K$1)&amp;"월 월차 결산서 [ ㈜ 창현 ]"</f>
         <v>2026년 1월~7월 월차 결산서 [ ㈜ 창현 ]</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
       <c r="J1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3439,16 +3499,16 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="136" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
     </row>
     <row r="4" spans="1:13" ht="34.5" customHeight="1">
       <c r="A4" t="s">
@@ -3459,159 +3519,159 @@
       <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="136" t="s">
+      <c r="B5" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="131"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="131"/>
-      <c r="F5" s="131"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="132"/>
+      <c r="C5" s="129"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="130"/>
     </row>
     <row r="6" spans="1:13" ht="43.5" customHeight="1">
       <c r="A6" s="8">
         <v>1</v>
       </c>
-      <c r="B6" s="133" t="s">
+      <c r="B6" s="140" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="131"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="131"/>
-      <c r="F6" s="131"/>
-      <c r="G6" s="131"/>
-      <c r="H6" s="132"/>
+      <c r="C6" s="129"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="130"/>
     </row>
     <row r="7" spans="1:13" ht="43.5" customHeight="1">
       <c r="A7" s="9">
         <v>2</v>
       </c>
-      <c r="B7" s="130" t="str">
+      <c r="B7" s="135" t="str">
         <f>"재무상태표 ["&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 현재]"</f>
         <v>재무상태표 [2026년07월31일 현재]</v>
       </c>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="132"/>
+      <c r="C7" s="129"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="130"/>
     </row>
     <row r="8" spans="1:13" ht="43.5" customHeight="1">
       <c r="A8" s="8">
         <v>3</v>
       </c>
-      <c r="B8" s="133" t="str">
+      <c r="B8" s="140" t="str">
         <f>"손익계산서(매출액대비 비율분석) ["&amp;TEXT(DATE(YEAR($K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR($K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR($K$1),1,1)),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
         <v>손익계산서(매출액대비 비율분석) [2026년01월01일 부터 2026년07월31일 까지]</v>
       </c>
-      <c r="C8" s="131"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="131"/>
-      <c r="F8" s="131"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="132"/>
+      <c r="C8" s="129"/>
+      <c r="D8" s="129"/>
+      <c r="E8" s="129"/>
+      <c r="F8" s="129"/>
+      <c r="G8" s="129"/>
+      <c r="H8" s="130"/>
     </row>
     <row r="9" spans="1:13" ht="43.5" customHeight="1">
       <c r="A9" s="9">
         <v>4</v>
       </c>
-      <c r="B9" s="130" t="str">
+      <c r="B9" s="135" t="str">
         <f>"손익계산서(전월대비 증감) ["&amp;TEXT(EOMONTH($K$1,-2)+1,"yyyy")&amp;"년"&amp;TEXT(MONTH(EOMONTH($K$1,-2)+1),"00")&amp;"월"&amp;TEXT(DAY(EOMONTH($K$1,-2)+1),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
         <v>손익계산서(전월대비 증감) [2026년06월01일 부터 2026년07월31일 까지]</v>
       </c>
-      <c r="C9" s="131"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="131"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="132"/>
+      <c r="C9" s="129"/>
+      <c r="D9" s="129"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="130"/>
     </row>
     <row r="10" spans="1:13" ht="43.5" customHeight="1">
       <c r="A10" s="8">
         <v>5</v>
       </c>
-      <c r="B10" s="138" t="str">
+      <c r="B10" s="137" t="str">
         <f>"기간별손익계산서 ["&amp;TEXT(DATE(YEAR($K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR($K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR($K$1),1,1)),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
         <v>기간별손익계산서 [2026년01월01일 부터 2026년07월31일 까지]</v>
       </c>
-      <c r="C10" s="131"/>
-      <c r="D10" s="131"/>
-      <c r="E10" s="131"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="132"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="129"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="130"/>
     </row>
     <row r="11" spans="1:13" ht="43.5" customHeight="1">
       <c r="A11" s="9">
         <v>6</v>
       </c>
-      <c r="B11" s="139" t="str">
+      <c r="B11" s="138" t="str">
         <f>TEXT($K$1,"yyyy")&amp;"년 차량별 비용현황[연간누계/월별/당월상세]"</f>
         <v>2026년 차량별 비용현황[연간누계/월별/당월상세]</v>
       </c>
-      <c r="C11" s="131"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="132"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="130"/>
     </row>
     <row r="12" spans="1:13" ht="43.5" customHeight="1">
       <c r="A12" s="8">
         <v>7</v>
       </c>
-      <c r="B12" s="138" t="str">
+      <c r="B12" s="137" t="str">
         <f>TEXT($K$1,"yyyy")&amp;"년 운송비 개인별 비용"</f>
         <v>2026년 운송비 개인별 비용</v>
       </c>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="131"/>
-      <c r="G12" s="131"/>
-      <c r="H12" s="132"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="130"/>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1"/>
     <row r="14" spans="1:13" ht="32.25" customHeight="1"/>
     <row r="15" spans="1:13" ht="9.75" customHeight="1">
-      <c r="D15" s="140" t="s">
+      <c r="D15" s="139" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="126" t="s">
+      <c r="E15" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="126" t="s">
+      <c r="F15" s="133" t="s">
         <v>9</v>
       </c>
-      <c r="G15" s="126" t="s">
+      <c r="G15" s="133" t="s">
         <v>10</v>
       </c>
-      <c r="H15" s="126" t="s">
+      <c r="H15" s="133" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="27.75" customHeight="1">
-      <c r="D16" s="129"/>
-      <c r="E16" s="127"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="127"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="134"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="134"/>
     </row>
     <row r="17" spans="4:8" ht="21" customHeight="1">
-      <c r="D17" s="129"/>
-      <c r="E17" s="128"/>
-      <c r="F17" s="128"/>
-      <c r="G17" s="128"/>
-      <c r="H17" s="128"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="131"/>
+      <c r="H17" s="131"/>
     </row>
     <row r="18" spans="4:8" ht="21" customHeight="1">
-      <c r="D18" s="129"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="129"/>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="132"/>
+      <c r="H18" s="132"/>
     </row>
     <row r="19" spans="4:8" ht="15" customHeight="1">
       <c r="D19" s="10"/>
@@ -3622,6 +3682,9 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B6:H6"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="H17:H18"/>
@@ -3638,14 +3701,11 @@
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="E17:E18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B6:H6"/>
   </mergeCells>
   <phoneticPr fontId="41" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="1.92916666666667" bottom="0.74791666666666701" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="97" orientation="portrait" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3668,29 +3728,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
     </row>
     <row r="2" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A2" s="146" t="str">
+      <c r="A2" s="147" t="str">
         <f>TEXT(인덱스!$K$1,"yyyy")&amp;"년 1월 ~ "&amp;MONTH(인덱스!$K$1)&amp;"월 누적 기준 ( 기준일 : "&amp;TEXT(인덱스!$K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH(인덱스!$K$1),"00")&amp;"월"&amp;TEXT(DAY(인덱스!$K$1),"00")&amp;"일 )"</f>
         <v>2026년 1월 ~ 7월 누적 기준 ( 기준일 : 2026년07월31일 )</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
     </row>
     <row r="3" spans="1:8" ht="18.75" customHeight="1"/>
     <row r="4" spans="1:8" ht="15" customHeight="1">
@@ -3699,48 +3759,51 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A5" s="141" t="s">
+      <c r="A5" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="147">
+      <c r="B5" s="148" t="str">
         <f>"전년동기 대비 ("&amp;(YEAR(인덱스!$K$1)-1)&amp;"년 1~"&amp;MONTH(인덱스!$K$1)&amp;"월)"</f>
-      </c>
-      <c r="C5" s="144"/>
-      <c r="D5" s="144"/>
-      <c r="E5" s="145"/>
-      <c r="F5" s="143" t="s">
+        <v>전년동기 대비 (2025년 1~7월)</v>
+      </c>
+      <c r="C5" s="145"/>
+      <c r="D5" s="145"/>
+      <c r="E5" s="146"/>
+      <c r="F5" s="144" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="145"/>
+      <c r="H5" s="146"/>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1">
+      <c r="A6" s="134"/>
+      <c r="B6" s="12" t="str">
+        <f>"당기(1~"&amp;MONTH(인덱스!$K$1)&amp;"월)"</f>
+        <v>당기(1~7월)</v>
+      </c>
+      <c r="C6" s="13" t="str">
+        <f>"전년동기(1~"&amp;MONTH(인덱스!$K$1)&amp;"월)"</f>
+        <v>전년동기(1~7월)</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="144"/>
-      <c r="H5" s="145"/>
-    </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1">
-      <c r="A6" s="127"/>
-      <c r="B6" s="12">
-        <f>"당기(1~"&amp;MONTH(인덱스!$K$1)&amp;"월)"</f>
-      </c>
-      <c r="C6" s="13">
-        <f>"전년동기(1~"&amp;MONTH(인덱스!$K$1)&amp;"월)"</f>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>18</v>
-      </c>
       <c r="E6" s="15" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1">
       <c r="A7" s="17" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B7" s="18">
         <f>'매출액대비 비율분석'!C9</f>
@@ -3773,7 +3836,7 @@
     </row>
     <row r="8" spans="1:8" ht="16.5" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="22">
         <f>'매출액대비 비율분석'!C12</f>
@@ -3806,7 +3869,7 @@
     </row>
     <row r="9" spans="1:8" ht="16.5" customHeight="1">
       <c r="A9" s="25" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" s="26">
         <f>'매출액대비 비율분석'!C18</f>
@@ -3839,7 +3902,7 @@
     </row>
     <row r="10" spans="1:8" ht="16.5" customHeight="1">
       <c r="A10" s="21" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B10" s="22">
         <f>'매출액대비 비율분석'!C19</f>
@@ -3872,7 +3935,7 @@
     </row>
     <row r="11" spans="1:8" ht="16.5" customHeight="1">
       <c r="A11" s="25" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B11" s="26">
         <f>'매출액대비 비율분석'!C41</f>
@@ -3905,7 +3968,7 @@
     </row>
     <row r="12" spans="1:8" ht="16.5" customHeight="1">
       <c r="A12" s="21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B12" s="22">
         <f>'매출액대비 비율분석'!C42</f>
@@ -3938,7 +4001,7 @@
     </row>
     <row r="13" spans="1:8" ht="16.5" customHeight="1">
       <c r="A13" s="21" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B13" s="22">
         <f>'매출액대비 비율분석'!C50</f>
@@ -3971,7 +4034,7 @@
     </row>
     <row r="14" spans="1:8" ht="16.5" customHeight="1">
       <c r="A14" s="25" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B14" s="26">
         <f>'매출액대비 비율분석'!C58</f>
@@ -4004,7 +4067,7 @@
     </row>
     <row r="15" spans="1:8" ht="16.5" customHeight="1">
       <c r="A15" s="21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B15" s="22">
         <f>'매출액대비 비율분석'!C59</f>
@@ -4037,7 +4100,7 @@
     </row>
     <row r="16" spans="1:8" ht="16.5" customHeight="1">
       <c r="A16" s="25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B16" s="26">
         <f>'매출액대비 비율분석'!C61</f>
@@ -4070,7 +4133,7 @@
     </row>
     <row r="17" spans="1:8" ht="16.5" customHeight="1">
       <c r="A17" s="29" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B17" s="30">
         <f>IFERROR(B11/B7,"")</f>
@@ -4091,7 +4154,7 @@
     </row>
     <row r="18" spans="1:8" ht="16.5" customHeight="1">
       <c r="A18" s="34" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B18" s="35">
         <f>IFERROR(B16/B7,"")</f>
@@ -4112,7 +4175,7 @@
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="30" customHeight="1">
@@ -4120,21 +4183,21 @@
         <v>5</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.5" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B22" s="18">
         <f>('재무상태표(내역)'!C50)+0</f>
@@ -4155,7 +4218,7 @@
     </row>
     <row r="23" spans="1:8" ht="16.5" customHeight="1">
       <c r="A23" s="46" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B23" s="26">
         <f>('재무상태표(내역)'!C65)+0</f>
@@ -4176,7 +4239,7 @@
     </row>
     <row r="24" spans="1:8" ht="16.5" customHeight="1">
       <c r="A24" s="46" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B24" s="26">
         <f>('재무상태표(내역)'!C79)+0</f>
@@ -4197,7 +4260,7 @@
     </row>
     <row r="25" spans="1:8" ht="16.5" customHeight="1">
       <c r="A25" s="49" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B25" s="35">
         <f>IFERROR(B23/B24,"")</f>
@@ -4212,18 +4275,18 @@
     </row>
     <row r="27" spans="1:8" ht="18.75" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="30" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B28" s="42" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C28" s="41" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
@@ -4233,9 +4296,11 @@
       </c>
       <c r="B29" s="53">
         <f>IF(1&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,1),NA())</f>
+        <v>2735381647</v>
       </c>
       <c r="C29" s="54">
         <f>IF(1&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,1),NA())</f>
+        <v>201922246</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
@@ -4245,9 +4310,11 @@
       </c>
       <c r="B30" s="22">
         <f>IF(2&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,2),NA())</f>
+        <v>2447781972</v>
       </c>
       <c r="C30" s="56">
         <f>IF(2&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,2),NA())</f>
+        <v>177990712</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
@@ -4257,9 +4324,11 @@
       </c>
       <c r="B31" s="22">
         <f>IF(3&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,3),NA())</f>
+        <v>4328182055</v>
       </c>
       <c r="C31" s="56">
         <f>IF(3&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,3),NA())</f>
+        <v>448657414</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
@@ -4269,9 +4338,11 @@
       </c>
       <c r="B32" s="22">
         <f>IF(4&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,4),NA())</f>
+        <v>4152427518</v>
       </c>
       <c r="C32" s="56">
         <f>IF(4&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,4),NA())</f>
+        <v>316863055</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1">
@@ -4281,9 +4352,11 @@
       </c>
       <c r="B33" s="22">
         <f>IF(5&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,5),NA())</f>
+        <v>2755697515</v>
       </c>
       <c r="C33" s="56">
         <f>IF(5&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,5),NA())</f>
+        <v>244208873</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1">
@@ -4293,9 +4366,11 @@
       </c>
       <c r="B34" s="22">
         <f>IF(6&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,6),NA())</f>
+        <v>2793851873</v>
       </c>
       <c r="C34" s="56">
         <f>IF(6&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,6),NA())</f>
+        <v>151504066</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" customHeight="1">
@@ -4305,9 +4380,11 @@
       </c>
       <c r="B35" s="22">
         <f>IF(7&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,7),NA())</f>
+        <v>2306642756</v>
       </c>
       <c r="C35" s="56">
         <f>IF(7&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,7),NA())</f>
+        <v>166909868</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1">
@@ -4315,11 +4392,13 @@
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),8,1))&amp;"월","")</f>
         <v>8월</v>
       </c>
-      <c r="B36" s="22">
+      <c r="B36" s="22" t="e">
         <f>IF(8&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,8),NA())</f>
-      </c>
-      <c r="C36" s="56">
+        <v>#N/A</v>
+      </c>
+      <c r="C36" s="56" t="e">
         <f>IF(8&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,8),NA())</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1">
@@ -4327,11 +4406,13 @@
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),9,1))&amp;"월","")</f>
         <v>9월</v>
       </c>
-      <c r="B37" s="22">
+      <c r="B37" s="22" t="e">
         <f>IF(9&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,9),NA())</f>
-      </c>
-      <c r="C37" s="56">
+        <v>#N/A</v>
+      </c>
+      <c r="C37" s="56" t="e">
         <f>IF(9&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,9),NA())</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1">
@@ -4339,11 +4420,13 @@
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),10,1))&amp;"월","")</f>
         <v>10월</v>
       </c>
-      <c r="B38" s="22">
+      <c r="B38" s="22" t="e">
         <f>IF(10&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,10),NA())</f>
-      </c>
-      <c r="C38" s="56">
+        <v>#N/A</v>
+      </c>
+      <c r="C38" s="56" t="e">
         <f>IF(10&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,10),NA())</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15" customHeight="1">
@@ -4351,11 +4434,13 @@
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),11,1))&amp;"월","")</f>
         <v>11월</v>
       </c>
-      <c r="B39" s="22">
+      <c r="B39" s="22" t="e">
         <f>IF(11&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,11),NA())</f>
-      </c>
-      <c r="C39" s="56">
+        <v>#N/A</v>
+      </c>
+      <c r="C39" s="56" t="e">
         <f>IF(11&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,11),NA())</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15" customHeight="1">
@@ -4363,39 +4448,41 @@
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),12,1))&amp;"월","")</f>
         <v>12월</v>
       </c>
-      <c r="B40" s="22">
+      <c r="B40" s="22" t="e">
         <f>IF(12&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,2,12),NA())</f>
-      </c>
-      <c r="C40" s="56">
+        <v>#N/A</v>
+      </c>
+      <c r="C40" s="56" t="e">
         <f>IF(12&lt;=MONTH(인덱스!$K$1),INDEX(기간별손익계산서!$C:$N,30,12),NA())</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16.5" customHeight="1">
       <c r="A41" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="58">
+        <v>39</v>
+      </c>
+      <c r="B41" s="58" t="e">
         <f>SUM(B29:B40)</f>
-        <v>21519965336</v>
-      </c>
-      <c r="C41" s="59">
+        <v>#N/A</v>
+      </c>
+      <c r="C41" s="59" t="e">
         <f>SUM(C29:C40)</f>
-        <v>1708056234</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="3.75" customHeight="1"/>
     <row r="68" spans="1:8" ht="27.75" customHeight="1"/>
     <row r="69" spans="1:8" ht="60" customHeight="1">
-      <c r="A69" s="142" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="135"/>
-      <c r="C69" s="135"/>
-      <c r="D69" s="135"/>
-      <c r="E69" s="135"/>
-      <c r="F69" s="135"/>
-      <c r="G69" s="135"/>
-      <c r="H69" s="135"/>
+      <c r="A69" s="143" t="s">
+        <v>40</v>
+      </c>
+      <c r="B69" s="127"/>
+      <c r="C69" s="127"/>
+      <c r="D69" s="127"/>
+      <c r="E69" s="127"/>
+      <c r="F69" s="127"/>
+      <c r="G69" s="127"/>
+      <c r="H69" s="127"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4432,8 +4519,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="1.1812499999999999" bottom="0.98402777777777795" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="64" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4460,14 +4547,14 @@
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" customHeight="1">
       <c r="A1" s="149" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
+        <v>41</v>
+      </c>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
       <c r="H1" s="60"/>
     </row>
     <row r="2" spans="1:11" ht="10.5" customHeight="1">
@@ -4489,12 +4576,12 @@
         <f>"(당기) "&amp;TEXT(DATE(YEAR(인덱스!$K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR(인덱스!$K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR(인덱스!$K$1),1,1)),"00")&amp;"일"&amp;" - "&amp;TEXT(인덱스!$K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH(인덱스!$K$1),"00")&amp;"월"&amp;TEXT(DAY(인덱스!$K$1),"00")&amp;"일"</f>
         <v>(당기) 2026년01월01일 - 2026년07월31일</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
       <c r="H3" s="5"/>
       <c r="I3" s="62" t="str">
         <f>IF(ROUND(F50,0)=ROUND(F80,0),"대차검증(전기): 일치","대차검증(전기): 불일치 ⚠")</f>
@@ -4506,64 +4593,64 @@
         <f>"(전기) "&amp;TEXT(DATE(YEAR(인덱스!$K$1)-1,1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR(인덱스!$K$1)-1,1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR(인덱스!$K$1)-1,1,1)),"00")&amp;"일"&amp;" - "&amp;TEXT(DATE(YEAR(인덱스!$K$1)-1,12,31),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR(인덱스!$K$1)-1,12,31)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR(인덱스!$K$1)-1,12,31)),"00")&amp;"일"</f>
         <v>(전기) 2025년01월01일 - 2025년12월31일</v>
       </c>
-      <c r="B4" s="135"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
       <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" customHeight="1"/>
     <row r="6" spans="1:11" ht="11.25" customHeight="1">
       <c r="A6" s="63" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G6" s="64" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18.75" customHeight="1">
       <c r="A7" s="150" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="150" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="130"/>
+      <c r="D7" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="150" t="s">
+      <c r="F7" s="130"/>
+      <c r="G7" s="150" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="132"/>
-      <c r="D7" s="150" t="s">
+      <c r="J7" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="150" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="132"/>
-      <c r="G7" s="150" t="s">
-        <v>51</v>
-      </c>
-      <c r="J7" s="66" t="s">
-        <v>52</v>
-      </c>
       <c r="K7" s="66" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="18.75" customHeight="1">
       <c r="A8" s="152"/>
       <c r="B8" s="150" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="132"/>
+        <v>50</v>
+      </c>
+      <c r="C8" s="130"/>
       <c r="D8" s="152"/>
       <c r="E8" s="150" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="132"/>
+        <v>51</v>
+      </c>
+      <c r="F8" s="130"/>
       <c r="G8" s="152"/>
     </row>
     <row r="9" spans="1:11" ht="17.25" customHeight="1">
       <c r="A9" s="67" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B9" s="68"/>
       <c r="C9" s="68"/>
@@ -4590,7 +4677,7 @@
     </row>
     <row r="10" spans="1:11" ht="17.25" customHeight="1">
       <c r="A10" s="74" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B10" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I10,재무상태표!$G:$G,0)),0)</f>
@@ -4632,7 +4719,7 @@
     </row>
     <row r="11" spans="1:11" ht="17.25" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B11" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I11,재무상태표!$G:$G,0)),0)</f>
@@ -4674,7 +4761,7 @@
     </row>
     <row r="12" spans="1:11" ht="17.25" customHeight="1">
       <c r="A12" s="67" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B12" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I12,재무상태표!$G:$G,0)),0)</f>
@@ -4716,7 +4803,7 @@
     </row>
     <row r="13" spans="1:11" ht="17.25" customHeight="1">
       <c r="A13" s="67" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B13" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I13,재무상태표!$G:$G,0)),0)</f>
@@ -4758,7 +4845,7 @@
     </row>
     <row r="14" spans="1:11" ht="17.25" customHeight="1">
       <c r="A14" s="67" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B14" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I14,재무상태표!$G:$G,0)),0)</f>
@@ -4800,7 +4887,7 @@
     </row>
     <row r="15" spans="1:11" ht="17.25" customHeight="1">
       <c r="A15" s="67" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B15" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I15,재무상태표!$G:$G,0)),0)</f>
@@ -4842,7 +4929,7 @@
     </row>
     <row r="16" spans="1:11" ht="17.25" customHeight="1">
       <c r="A16" s="67" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B16" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I16,재무상태표!$G:$G,0)),0)</f>
@@ -4884,7 +4971,7 @@
     </row>
     <row r="17" spans="1:11" ht="17.25" customHeight="1">
       <c r="A17" s="67" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B17" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I17,재무상태표!$G:$G,0)),0)</f>
@@ -4926,7 +5013,7 @@
     </row>
     <row r="18" spans="1:11" ht="17.25" customHeight="1">
       <c r="A18" s="67" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B18" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I18,재무상태표!$G:$G,0)),0)</f>
@@ -4968,7 +5055,7 @@
     </row>
     <row r="19" spans="1:11" ht="17.25" customHeight="1">
       <c r="A19" s="67" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B19" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I19,재무상태표!$G:$G,0)),0)</f>
@@ -5010,7 +5097,7 @@
     </row>
     <row r="20" spans="1:11" ht="17.25" customHeight="1">
       <c r="A20" s="67" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B20" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I20,재무상태표!$G:$G,0)),0)</f>
@@ -5052,7 +5139,7 @@
     </row>
     <row r="21" spans="1:11" ht="17.25" customHeight="1">
       <c r="A21" s="67" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B21" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I21,재무상태표!$G:$G,0)),0)</f>
@@ -5063,7 +5150,7 @@
         <v>15,136,465</v>
       </c>
       <c r="D21" s="85" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E21" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I21,재무상태표!$G:$G,0)),0)</f>
@@ -5096,7 +5183,7 @@
     </row>
     <row r="22" spans="1:11" ht="21.75" customHeight="1">
       <c r="A22" s="67" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B22" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I22,재무상태표!$G:$G,0)),0)</f>
@@ -5107,7 +5194,7 @@
         <v>253,437,222</v>
       </c>
       <c r="D22" s="85" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E22" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I22,재무상태표!$G:$G,0)),0)</f>
@@ -5140,7 +5227,7 @@
     </row>
     <row r="23" spans="1:11" ht="24.75" customHeight="1">
       <c r="A23" s="67" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B23" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I23,재무상태표!$G:$G,0)),0)</f>
@@ -5151,7 +5238,7 @@
         <v>1,000,000</v>
       </c>
       <c r="D23" s="85" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E23" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I23,재무상태표!$G:$G,0)),0)</f>
@@ -5184,7 +5271,7 @@
     </row>
     <row r="24" spans="1:11" ht="17.25" customHeight="1">
       <c r="A24" s="67" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B24" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I24,재무상태표!$G:$G,0)),0)</f>
@@ -5195,7 +5282,7 @@
         <v>4,048,315</v>
       </c>
       <c r="D24" s="84" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E24" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I24,재무상태표!$G:$G,0)),0)</f>
@@ -5228,7 +5315,7 @@
     </row>
     <row r="25" spans="1:11" ht="17.25" customHeight="1">
       <c r="A25" s="67" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B25" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I25,재무상태표!$G:$G,0)),0)</f>
@@ -5239,7 +5326,7 @@
         <v>900,032,000</v>
       </c>
       <c r="D25" s="85" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E25" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I25,재무상태표!$G:$G,0)),0)</f>
@@ -5272,7 +5359,7 @@
     </row>
     <row r="26" spans="1:11" ht="17.25" customHeight="1">
       <c r="A26" s="67" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B26" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I26,재무상태표!$G:$G,0)),0)</f>
@@ -5314,7 +5401,7 @@
     </row>
     <row r="27" spans="1:11" ht="17.25" customHeight="1">
       <c r="A27" s="67" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B27" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I27,재무상태표!$G:$G,0)),0)</f>
@@ -5325,7 +5412,7 @@
         <v>17,540,440</v>
       </c>
       <c r="D27" s="86" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E27" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I27,재무상태표!$G:$G,0)),0)</f>
@@ -5358,7 +5445,7 @@
     </row>
     <row r="28" spans="1:11" ht="17.25" customHeight="1">
       <c r="A28" s="82" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B28" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I28,재무상태표!$G:$G,0)),0)</f>
@@ -5400,7 +5487,7 @@
     </row>
     <row r="29" spans="1:11" ht="17.25" customHeight="1">
       <c r="A29" s="67" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B29" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I29,재무상태표!$G:$G,0)),0)</f>
@@ -5442,7 +5529,7 @@
     </row>
     <row r="30" spans="1:11" ht="17.25" customHeight="1">
       <c r="A30" s="74" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B30" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I30,재무상태표!$G:$G,0)),0)</f>
@@ -5484,7 +5571,7 @@
     </row>
     <row r="31" spans="1:11" ht="17.25" customHeight="1">
       <c r="A31" s="82" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B31" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I31,재무상태표!$G:$G,0)),0)</f>
@@ -5526,7 +5613,7 @@
     </row>
     <row r="32" spans="1:11" ht="17.25" customHeight="1">
       <c r="A32" s="67" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B32" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I32,재무상태표!$G:$G,0)),0)</f>
@@ -5568,7 +5655,7 @@
     </row>
     <row r="33" spans="1:11" ht="17.25" customHeight="1">
       <c r="A33" s="82" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B33" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I33,재무상태표!$G:$G,0)),0)</f>
@@ -5610,7 +5697,7 @@
     </row>
     <row r="34" spans="1:11" ht="17.25" customHeight="1">
       <c r="A34" s="67" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B34" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I34,재무상태표!$G:$G,0)),0)</f>
@@ -5652,7 +5739,7 @@
     </row>
     <row r="35" spans="1:11" ht="17.25" customHeight="1">
       <c r="A35" s="67" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B35" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I35,재무상태표!$G:$G,0)),0)</f>
@@ -5694,7 +5781,7 @@
     </row>
     <row r="36" spans="1:11" ht="17.25" customHeight="1">
       <c r="A36" s="67" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B36" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I36,재무상태표!$G:$G,0)),0)</f>
@@ -5736,7 +5823,7 @@
     </row>
     <row r="37" spans="1:11" ht="17.25" customHeight="1">
       <c r="A37" s="67" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B37" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I37,재무상태표!$G:$G,0)),0)</f>
@@ -5778,7 +5865,7 @@
     </row>
     <row r="38" spans="1:11" ht="17.25" customHeight="1">
       <c r="A38" s="67" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B38" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I38,재무상태표!$G:$G,0)),0)</f>
@@ -5820,7 +5907,7 @@
     </row>
     <row r="39" spans="1:11" ht="17.25" customHeight="1">
       <c r="A39" s="67" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B39" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I39,재무상태표!$G:$G,0)),0)</f>
@@ -5862,7 +5949,7 @@
     </row>
     <row r="40" spans="1:11" ht="17.25" customHeight="1">
       <c r="A40" s="67" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B40" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I40,재무상태표!$G:$G,0)),0)</f>
@@ -5904,7 +5991,7 @@
     </row>
     <row r="41" spans="1:11" ht="17.25" customHeight="1">
       <c r="A41" s="67" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B41" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I41,재무상태표!$G:$G,0)),0)</f>
@@ -5946,7 +6033,7 @@
     </row>
     <row r="42" spans="1:11" ht="17.25" customHeight="1">
       <c r="A42" s="67" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B42" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I42,재무상태표!$G:$G,0)),0)</f>
@@ -5988,7 +6075,7 @@
     </row>
     <row r="43" spans="1:11" ht="17.25" customHeight="1">
       <c r="A43" s="82" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B43" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I43,재무상태표!$G:$G,0)),0)</f>
@@ -6030,7 +6117,7 @@
     </row>
     <row r="44" spans="1:11" ht="17.25" customHeight="1">
       <c r="A44" s="82" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B44" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I44,재무상태표!$G:$G,0)),0)</f>
@@ -6072,7 +6159,7 @@
     </row>
     <row r="45" spans="1:11" ht="21.75" customHeight="1">
       <c r="A45" s="67" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B45" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I45,재무상태표!$G:$G,0)),0)</f>
@@ -6114,7 +6201,7 @@
     </row>
     <row r="46" spans="1:11" ht="21.75" customHeight="1">
       <c r="A46" s="67" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B46" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I46,재무상태표!$G:$G,0)),0)</f>
@@ -6156,7 +6243,7 @@
     </row>
     <row r="47" spans="1:11" ht="25.5" customHeight="1">
       <c r="A47" s="67" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B47" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I47,재무상태표!$G:$G,0)),0)</f>
@@ -6167,7 +6254,7 @@
         <v>140,000,000</v>
       </c>
       <c r="D47" s="85" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E47" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I47,재무상태표!$G:$G,0)),0)</f>
@@ -6200,7 +6287,7 @@
     </row>
     <row r="48" spans="1:11" ht="21.75" customHeight="1">
       <c r="A48" s="67" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B48" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I48,재무상태표!$G:$G,0)),0)</f>
@@ -6211,7 +6298,7 @@
         <v>528,095,860</v>
       </c>
       <c r="D48" s="85" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E48" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I48,재무상태표!$G:$G,0)),0)</f>
@@ -6244,7 +6331,7 @@
     </row>
     <row r="49" spans="1:11" ht="21.75" customHeight="1">
       <c r="A49" s="67" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B49" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I49,재무상태표!$G:$G,0)),0)</f>
@@ -6286,7 +6373,7 @@
     </row>
     <row r="50" spans="1:11" ht="21.75" customHeight="1">
       <c r="A50" s="88" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B50" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I50,재무상태표!$G:$G,0)),0)</f>
@@ -6328,7 +6415,7 @@
     </row>
     <row r="51" spans="1:11" ht="21.75" customHeight="1">
       <c r="A51" s="67" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B51" s="68"/>
       <c r="C51" s="68"/>
@@ -6355,7 +6442,7 @@
     </row>
     <row r="52" spans="1:11" ht="21.75" customHeight="1">
       <c r="A52" s="74" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B52" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I52,재무상태표!$G:$G,0)),0)</f>
@@ -6397,7 +6484,7 @@
     </row>
     <row r="53" spans="1:11" ht="21.75" customHeight="1">
       <c r="A53" s="67" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B53" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I53,재무상태표!$G:$G,0)),0)</f>
@@ -6439,7 +6526,7 @@
     </row>
     <row r="54" spans="1:11" ht="21.75" customHeight="1">
       <c r="A54" s="67" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B54" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I54,재무상태표!$G:$G,0)),0)</f>
@@ -6481,7 +6568,7 @@
     </row>
     <row r="55" spans="1:11" ht="21.75" customHeight="1">
       <c r="A55" s="67" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B55" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I55,재무상태표!$G:$G,0)),0)</f>
@@ -6492,7 +6579,7 @@
         <v>28,248,500</v>
       </c>
       <c r="D55" s="84" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E55" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I55,재무상태표!$G:$G,0)),0)</f>
@@ -6525,7 +6612,7 @@
     </row>
     <row r="56" spans="1:11" ht="21.75" customHeight="1">
       <c r="A56" s="67" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B56" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I56,재무상태표!$G:$G,0)),0)</f>
@@ -6567,7 +6654,7 @@
     </row>
     <row r="57" spans="1:11" ht="21.75" customHeight="1">
       <c r="A57" s="67" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B57" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I57,재무상태표!$G:$G,0)),0)</f>
@@ -6578,7 +6665,7 @@
         <v>43,441,422</v>
       </c>
       <c r="D57" s="85" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E57" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I57,재무상태표!$G:$G,0)),0)</f>
@@ -6611,7 +6698,7 @@
     </row>
     <row r="58" spans="1:11" ht="21.75" customHeight="1">
       <c r="A58" s="67" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B58" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I58,재무상태표!$G:$G,0)),0)</f>
@@ -6653,7 +6740,7 @@
     </row>
     <row r="59" spans="1:11" ht="21.75" customHeight="1">
       <c r="A59" s="67" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B59" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I59,재무상태표!$G:$G,0)),0)</f>
@@ -6695,7 +6782,7 @@
     </row>
     <row r="60" spans="1:11" ht="21.75" customHeight="1">
       <c r="A60" s="67" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B60" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I60,재무상태표!$G:$G,0)),0)</f>
@@ -6706,7 +6793,7 @@
         <v>204,130,142</v>
       </c>
       <c r="D60" s="85" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E60" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I60,재무상태표!$G:$G,0)),0)</f>
@@ -6739,7 +6826,7 @@
     </row>
     <row r="61" spans="1:11" ht="21.75" customHeight="1">
       <c r="A61" s="67" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B61" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I61,재무상태표!$G:$G,0)),0)</f>
@@ -6781,7 +6868,7 @@
     </row>
     <row r="62" spans="1:11" ht="21.75" customHeight="1">
       <c r="A62" s="74" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B62" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I62,재무상태표!$G:$G,0)),0)</f>
@@ -6823,7 +6910,7 @@
     </row>
     <row r="63" spans="1:11" ht="21.75" customHeight="1">
       <c r="A63" s="67" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B63" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I63,재무상태표!$G:$G,0)),0)</f>
@@ -6865,7 +6952,7 @@
     </row>
     <row r="64" spans="1:11" ht="21.75" customHeight="1">
       <c r="A64" s="67" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B64" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I64,재무상태표!$G:$G,0)),0)</f>
@@ -6907,7 +6994,7 @@
     </row>
     <row r="65" spans="1:11" ht="21.75" customHeight="1">
       <c r="A65" s="88" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B65" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I65,재무상태표!$G:$G,0)),0)</f>
@@ -6949,7 +7036,7 @@
     </row>
     <row r="66" spans="1:11" ht="21.75" customHeight="1">
       <c r="A66" s="67" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B66" s="68"/>
       <c r="C66" s="68"/>
@@ -6976,7 +7063,7 @@
     </row>
     <row r="67" spans="1:11" ht="21.75" customHeight="1">
       <c r="A67" s="74" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B67" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I67,재무상태표!$G:$G,0)),0)</f>
@@ -7018,7 +7105,7 @@
     </row>
     <row r="68" spans="1:11" ht="21.75" customHeight="1">
       <c r="A68" s="67" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B68" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I68,재무상태표!$G:$G,0)),0)</f>
@@ -7060,7 +7147,7 @@
     </row>
     <row r="69" spans="1:11" ht="21.75" customHeight="1">
       <c r="A69" s="74" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B69" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I69,재무상태표!$G:$G,0)),0)</f>
@@ -7102,7 +7189,7 @@
     </row>
     <row r="70" spans="1:11" ht="21.75" customHeight="1">
       <c r="A70" s="67" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B70" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I70,재무상태표!$G:$G,0)),0)</f>
@@ -7144,7 +7231,7 @@
     </row>
     <row r="71" spans="1:11" ht="21.75" customHeight="1">
       <c r="A71" s="74" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B71" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I71,재무상태표!$G:$G,0)),0)</f>
@@ -7186,7 +7273,7 @@
     </row>
     <row r="72" spans="1:11" ht="21.75" customHeight="1">
       <c r="A72" s="74" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B72" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I72,재무상태표!$G:$G,0)),0)</f>
@@ -7228,7 +7315,7 @@
     </row>
     <row r="73" spans="1:11" ht="21.75" customHeight="1">
       <c r="A73" s="74" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B73" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I73,재무상태표!$G:$G,0)),0)</f>
@@ -7270,7 +7357,7 @@
     </row>
     <row r="74" spans="1:11" ht="21.75" customHeight="1">
       <c r="A74" s="67" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B74" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I74,재무상태표!$G:$G,0)),0)</f>
@@ -7312,7 +7399,7 @@
     </row>
     <row r="75" spans="1:11" ht="21.75" customHeight="1">
       <c r="A75" s="67" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B75" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I75,재무상태표!$G:$G,0)),0)</f>
@@ -7354,7 +7441,7 @@
     </row>
     <row r="76" spans="1:11" ht="21.75" customHeight="1">
       <c r="A76" s="82" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B76" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I76,재무상태표!$G:$G,0)),0)</f>
@@ -7446,7 +7533,7 @@
     </row>
     <row r="79" spans="1:11" ht="21.75" customHeight="1">
       <c r="A79" s="88" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B79" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I79,재무상태표!$G:$G,0)),0)</f>
@@ -7488,7 +7575,7 @@
     </row>
     <row r="80" spans="1:11" ht="21.75" customHeight="1">
       <c r="A80" s="88" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B80" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I80,재무상태표!$G:$G,0)),0)</f>
@@ -7569,14 +7656,14 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39374999999999999" right="0.39374999999999999" top="0.59027777777777801" bottom="0.55138888888888904" header="0.511811023622047" footer="0.31527777777777799"/>
-  <pageSetup paperSize="9" scale="66" orientation="portrait" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="66" orientation="portrait" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P/2</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="61" max="16383" man="1"/>
   </rowBreaks>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7600,14 +7687,14 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
       <c r="A1" s="149" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
+        <v>128</v>
+      </c>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
     </row>
     <row r="2" spans="1:11" ht="6.75" customHeight="1">
       <c r="A2" s="61"/>
@@ -7647,53 +7734,53 @@
     </row>
     <row r="6" spans="1:11" ht="11.25" customHeight="1">
       <c r="A6" s="63" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G6" s="64" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
       <c r="A7" s="150" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="150" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="130"/>
+      <c r="D7" s="154" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="150" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="132"/>
-      <c r="D7" s="154" t="s">
-        <v>132</v>
-      </c>
-      <c r="E7" s="150" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="132"/>
+      <c r="F7" s="130"/>
       <c r="G7" s="154" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J7" s="66" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K7" s="66" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1">
       <c r="A8" s="152"/>
       <c r="B8" s="150" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="132"/>
+        <v>50</v>
+      </c>
+      <c r="C8" s="130"/>
       <c r="D8" s="152"/>
       <c r="E8" s="150" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="132"/>
+        <v>51</v>
+      </c>
+      <c r="F8" s="130"/>
       <c r="G8" s="152"/>
     </row>
     <row r="9" spans="1:11" ht="16.5" customHeight="1">
       <c r="A9" s="74" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B9" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I9,손익계산서!$G:$G,0)),0)</f>
@@ -7738,7 +7825,7 @@
     </row>
     <row r="10" spans="1:11" ht="16.5" customHeight="1">
       <c r="A10" s="67" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B10" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I10,손익계산서!$G:$G,0)),0)</f>
@@ -7777,7 +7864,7 @@
     </row>
     <row r="11" spans="1:11" ht="16.5" customHeight="1">
       <c r="A11" s="67" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B11" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I11,손익계산서!$G:$G,0)),0)</f>
@@ -7816,7 +7903,7 @@
     </row>
     <row r="12" spans="1:11" ht="16.5" customHeight="1">
       <c r="A12" s="74" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B12" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I12,손익계산서!$G:$G,0)),0)</f>
@@ -7861,7 +7948,7 @@
     </row>
     <row r="13" spans="1:11" ht="16.5" customHeight="1">
       <c r="A13" s="67" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B13" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I13,손익계산서!$G:$G,0)),0)</f>
@@ -7900,7 +7987,7 @@
     </row>
     <row r="14" spans="1:11" ht="16.5" customHeight="1">
       <c r="A14" s="67" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B14" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I14,손익계산서!$G:$G,0)),0)</f>
@@ -7939,7 +8026,7 @@
     </row>
     <row r="15" spans="1:11" ht="16.5" customHeight="1">
       <c r="A15" s="67" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B15" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I15,손익계산서!$G:$G,0)),0)</f>
@@ -7978,7 +8065,7 @@
     </row>
     <row r="16" spans="1:11" ht="16.5" customHeight="1">
       <c r="A16" s="67" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B16" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I16,손익계산서!$G:$G,0)),0)</f>
@@ -8017,7 +8104,7 @@
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1">
       <c r="A17" s="67" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B17" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I17,손익계산서!$G:$G,0)),0)</f>
@@ -8056,7 +8143,7 @@
     </row>
     <row r="18" spans="1:16" ht="17.25" customHeight="1">
       <c r="A18" s="74" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B18" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I18,손익계산서!$G:$G,0)),0)</f>
@@ -8101,7 +8188,7 @@
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1">
       <c r="A19" s="74" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B19" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I19,손익계산서!$G:$G,0)),0)</f>
@@ -8144,12 +8231,12 @@
         <v>-1.957789232550973E-2</v>
       </c>
       <c r="M19" s="97" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1">
       <c r="A20" s="67" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B20" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I20,손익계산서!$G:$G,0)),0)</f>
@@ -8202,7 +8289,7 @@
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1">
       <c r="A21" s="67" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B21" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I21,손익계산서!$G:$G,0)),0)</f>
@@ -8255,7 +8342,7 @@
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1">
       <c r="A22" s="67" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B22" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I22,손익계산서!$G:$G,0)),0)</f>
@@ -8308,7 +8395,7 @@
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1">
       <c r="A23" s="67" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B23" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I23,손익계산서!$G:$G,0)),0)</f>
@@ -8361,7 +8448,7 @@
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1">
       <c r="A24" s="67" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B24" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I24,손익계산서!$G:$G,0)),0)</f>
@@ -8414,7 +8501,7 @@
     </row>
     <row r="25" spans="1:16" ht="16.5" customHeight="1">
       <c r="A25" s="67" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B25" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I25,손익계산서!$G:$G,0)),0)</f>
@@ -8467,7 +8554,7 @@
     </row>
     <row r="26" spans="1:16" ht="16.5" customHeight="1">
       <c r="A26" s="67" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B26" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I26,손익계산서!$G:$G,0)),0)</f>
@@ -8520,7 +8607,7 @@
     </row>
     <row r="27" spans="1:16" ht="16.5" customHeight="1">
       <c r="A27" s="67" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B27" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I27,손익계산서!$G:$G,0)),0)</f>
@@ -8573,7 +8660,7 @@
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1">
       <c r="A28" s="67" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B28" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I28,손익계산서!$G:$G,0)),0)</f>
@@ -8626,7 +8713,7 @@
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1">
       <c r="A29" s="67" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B29" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I29,손익계산서!$G:$G,0)),0)</f>
@@ -8679,7 +8766,7 @@
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1">
       <c r="A30" s="67" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B30" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I30,손익계산서!$G:$G,0)),0)</f>
@@ -8732,7 +8819,7 @@
     </row>
     <row r="31" spans="1:16" ht="16.5" customHeight="1">
       <c r="A31" s="67" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B31" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I31,손익계산서!$G:$G,0)),0)</f>
@@ -8785,7 +8872,7 @@
     </row>
     <row r="32" spans="1:16" ht="16.5" customHeight="1">
       <c r="A32" s="67" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B32" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I32,손익계산서!$G:$G,0)),0)</f>
@@ -8838,7 +8925,7 @@
     </row>
     <row r="33" spans="1:16" ht="16.5" customHeight="1">
       <c r="A33" s="67" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B33" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I33,손익계산서!$G:$G,0)),0)</f>
@@ -8891,7 +8978,7 @@
     </row>
     <row r="34" spans="1:16" ht="16.5" customHeight="1">
       <c r="A34" s="67" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B34" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I34,손익계산서!$G:$G,0)),0)</f>
@@ -8944,7 +9031,7 @@
     </row>
     <row r="35" spans="1:16" ht="16.5" customHeight="1">
       <c r="A35" s="67" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B35" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I35,손익계산서!$G:$G,0)),0)</f>
@@ -8997,7 +9084,7 @@
     </row>
     <row r="36" spans="1:16" ht="16.5" customHeight="1">
       <c r="A36" s="67" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B36" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I36,손익계산서!$G:$G,0)),0)</f>
@@ -9050,7 +9137,7 @@
     </row>
     <row r="37" spans="1:16" ht="16.5" customHeight="1">
       <c r="A37" s="67" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B37" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I37,손익계산서!$G:$G,0)),0)</f>
@@ -9103,7 +9190,7 @@
     </row>
     <row r="38" spans="1:16" ht="16.5" customHeight="1">
       <c r="A38" s="67" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B38" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I38,손익계산서!$G:$G,0)),0)</f>
@@ -9156,7 +9243,7 @@
     </row>
     <row r="39" spans="1:16" ht="16.5" customHeight="1">
       <c r="A39" s="67" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B39" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I39,손익계산서!$G:$G,0)),0)</f>
@@ -9209,7 +9296,7 @@
     </row>
     <row r="40" spans="1:16" ht="16.5" customHeight="1">
       <c r="A40" s="67" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B40" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I40,손익계산서!$G:$G,0)),0)</f>
@@ -9262,7 +9349,7 @@
     </row>
     <row r="41" spans="1:16" ht="17.25" customHeight="1">
       <c r="A41" s="74" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B41" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I41,손익계산서!$G:$G,0)),0)</f>
@@ -9307,7 +9394,7 @@
     </row>
     <row r="42" spans="1:16" ht="16.5" customHeight="1">
       <c r="A42" s="74" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B42" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I42,손익계산서!$G:$G,0)),0)</f>
@@ -9352,7 +9439,7 @@
     </row>
     <row r="43" spans="1:16" ht="16.5" customHeight="1">
       <c r="A43" s="67" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B43" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I43,손익계산서!$G:$G,0)),0)</f>
@@ -9397,7 +9484,7 @@
     </row>
     <row r="44" spans="1:16" ht="16.5" customHeight="1">
       <c r="A44" s="67" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B44" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I44,손익계산서!$G:$G,0)),0)</f>
@@ -9442,7 +9529,7 @@
     </row>
     <row r="45" spans="1:16" ht="16.5" customHeight="1">
       <c r="A45" s="67" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B45" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I45,손익계산서!$G:$G,0)),0)</f>
@@ -9487,7 +9574,7 @@
     </row>
     <row r="46" spans="1:16" ht="16.5" customHeight="1">
       <c r="A46" s="67" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B46" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I46,손익계산서!$G:$G,0)),0)</f>
@@ -9532,7 +9619,7 @@
     </row>
     <row r="47" spans="1:16" ht="16.5" customHeight="1">
       <c r="A47" s="67" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B47" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I47,손익계산서!$G:$G,0)),0)</f>
@@ -9577,7 +9664,7 @@
     </row>
     <row r="48" spans="1:16" ht="16.5" customHeight="1">
       <c r="A48" s="67" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B48" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I48,손익계산서!$G:$G,0)),0)</f>
@@ -9622,7 +9709,7 @@
     </row>
     <row r="49" spans="1:11" ht="16.5" customHeight="1">
       <c r="A49" s="67" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B49" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I49,손익계산서!$G:$G,0)),0)</f>
@@ -9667,7 +9754,7 @@
     </row>
     <row r="50" spans="1:11" ht="16.5" customHeight="1">
       <c r="A50" s="74" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B50" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I50,손익계산서!$G:$G,0)),0)</f>
@@ -9712,7 +9799,7 @@
     </row>
     <row r="51" spans="1:11" ht="16.5" customHeight="1">
       <c r="A51" s="67" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B51" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I51,손익계산서!$G:$G,0)),0)</f>
@@ -9757,7 +9844,7 @@
     </row>
     <row r="52" spans="1:11" ht="16.5" customHeight="1">
       <c r="A52" s="67" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B52" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I52,손익계산서!$G:$G,0)),0)</f>
@@ -9802,7 +9889,7 @@
     </row>
     <row r="53" spans="1:11" ht="16.5" customHeight="1">
       <c r="A53" s="67" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B53" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I53,손익계산서!$G:$G,0)),0)</f>
@@ -9847,7 +9934,7 @@
     </row>
     <row r="54" spans="1:11" ht="16.5" customHeight="1">
       <c r="A54" s="67" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B54" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I54,손익계산서!$G:$G,0)),0)</f>
@@ -9892,7 +9979,7 @@
     </row>
     <row r="55" spans="1:11" ht="16.5" customHeight="1">
       <c r="A55" s="101" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B55" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I55,손익계산서!$G:$G,0)),0)</f>
@@ -9937,7 +10024,7 @@
     </row>
     <row r="56" spans="1:11" ht="16.5" customHeight="1">
       <c r="A56" s="67" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B56" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I56,손익계산서!$G:$G,0)),0)</f>
@@ -9982,7 +10069,7 @@
     </row>
     <row r="57" spans="1:11" ht="16.5" customHeight="1">
       <c r="A57" s="67" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B57" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I57,손익계산서!$G:$G,0)),0)</f>
@@ -10027,7 +10114,7 @@
     </row>
     <row r="58" spans="1:11" ht="17.25" customHeight="1">
       <c r="A58" s="74" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B58" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I58,손익계산서!$G:$G,0)),0)</f>
@@ -10072,7 +10159,7 @@
     </row>
     <row r="59" spans="1:11" ht="16.5" customHeight="1">
       <c r="A59" s="74" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B59" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I59,손익계산서!$G:$G,0)),0)</f>
@@ -10117,7 +10204,7 @@
     </row>
     <row r="60" spans="1:11" ht="16.5" customHeight="1">
       <c r="A60" s="67" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B60" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I60,손익계산서!$G:$G,0)),0)</f>
@@ -10156,7 +10243,7 @@
     </row>
     <row r="61" spans="1:11" ht="17.25" customHeight="1">
       <c r="A61" s="74" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B61" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I61,손익계산서!$G:$G,0)),0)</f>
@@ -10234,7 +10321,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.59027777777777801" bottom="0.35486111111111102" header="0.511811023622047" footer="0.31527777777777799"/>
-  <pageSetup paperSize="9" scale="77" orientation="portrait" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="77" orientation="portrait" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P/1</oddFooter>
   </headerFooter>
@@ -10265,16 +10352,16 @@
         <f>"손익계산서(전월대비 증감내역)"</f>
         <v>손익계산서(전월대비 증감내역)</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
       <c r="L1" s="156"/>
       <c r="M1" s="153"/>
     </row>
@@ -10284,51 +10371,51 @@
         <f>"기간 : "&amp;TEXT(EOMONTH(인덱스!$K$1,-2)+1,"yyyy")&amp;"년"&amp;TEXT(MONTH(EOMONTH(인덱스!$K$1,-2)+1),"00")&amp;"월"&amp;TEXT(DAY(EOMONTH(인덱스!$K$1,-2)+1),"00")&amp;"일"&amp;"부터 - "&amp;TEXT(인덱스!$K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH(인덱스!$K$1),"00")&amp;"월"&amp;TEXT(DAY(인덱스!$K$1),"00")&amp;"일"&amp;"까지"</f>
         <v>기간 : 2026년06월01일부터 - 2026년07월31일까지</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
       <c r="L3" s="156"/>
       <c r="M3" s="153"/>
     </row>
     <row r="5" spans="1:17" ht="11.25" customHeight="1">
       <c r="A5" s="63" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M5" s="103" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="35.25" customHeight="1">
       <c r="A6" s="65" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B6" s="65" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>187</v>
+      </c>
+      <c r="E6" s="65" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="F6" s="65" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="G6" s="65" t="s">
         <v>190</v>
       </c>
-      <c r="E6" s="65" t="s">
+      <c r="H6" s="65" t="s">
         <v>191</v>
-      </c>
-      <c r="F6" s="65" t="s">
-        <v>192</v>
-      </c>
-      <c r="G6" s="65" t="s">
-        <v>193</v>
-      </c>
-      <c r="H6" s="65" t="s">
-        <v>194</v>
       </c>
       <c r="I6" s="65" t="str">
         <f>"전월("&amp;MONTH(EOMONTH(인덱스!$K$1,-1))&amp;"월)"</f>
@@ -10339,24 +10426,24 @@
         <v>당월(7월)</v>
       </c>
       <c r="K6" s="104" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="L6" s="104" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M6" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="P6" s="66" t="s">
-        <v>52</v>
-      </c>
       <c r="Q6" s="66" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="22.5" customHeight="1">
       <c r="A7" s="105" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B7" s="91">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O7,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10400,6 +10487,7 @@
       </c>
       <c r="L7" s="106" t="str">
         <f>IF(J7-I7&gt;0,"증가",IF(J7-I7=0,"변동없음","감소"))</f>
+        <v>감소</v>
       </c>
       <c r="M7" s="107"/>
       <c r="N7" t="str">
@@ -10421,7 +10509,7 @@
     </row>
     <row r="8" spans="1:17" ht="22.5" customHeight="1">
       <c r="A8" s="108" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B8" s="95">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O8,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10484,7 +10572,7 @@
     </row>
     <row r="9" spans="1:17" ht="22.5" customHeight="1">
       <c r="A9" s="108" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B9" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O9,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10547,7 +10635,7 @@
     </row>
     <row r="10" spans="1:17" ht="22.5" customHeight="1">
       <c r="A10" s="105" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B10" s="112">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O10,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10591,6 +10679,7 @@
       </c>
       <c r="L10" s="106" t="str">
         <f>IF(J10-I10&gt;0,"증가",IF(J10-I10=0,"변동없음","감소"))</f>
+        <v>감소</v>
       </c>
       <c r="M10" s="107"/>
       <c r="N10" t="str">
@@ -10612,7 +10701,7 @@
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
       <c r="A11" s="108" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B11" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O11,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10675,7 +10764,7 @@
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
       <c r="A12" s="108" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B12" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O12,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10738,7 +10827,7 @@
     </row>
     <row r="13" spans="1:17" ht="22.5" customHeight="1">
       <c r="A13" s="108" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B13" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O13,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10801,7 +10890,7 @@
     </row>
     <row r="14" spans="1:17" ht="22.5" customHeight="1">
       <c r="A14" s="108" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B14" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O14,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10864,7 +10953,7 @@
     </row>
     <row r="15" spans="1:17" ht="22.5" customHeight="1">
       <c r="A15" s="108" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B15" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O15,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10927,7 +11016,7 @@
     </row>
     <row r="16" spans="1:17" ht="24" customHeight="1">
       <c r="A16" s="74" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B16" s="91">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O16,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10970,7 +11059,8 @@
         <v>-74249696</v>
       </c>
       <c r="L16" s="106" t="str">
-        <f>IF(J16-I16&gt;0,"증가",IF(J16-I16=0,"변동없음","감소"))</f>
+        <f t="shared" ref="L16:L54" si="3">IF(J16-I16&gt;0,"증가",IF(J16-I16=0,"변동없음","감소"))</f>
+        <v>감소</v>
       </c>
       <c r="M16" s="107"/>
       <c r="N16" t="str">
@@ -10992,7 +11082,7 @@
     </row>
     <row r="17" spans="1:17" ht="22.5" customHeight="1">
       <c r="A17" s="105" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B17" s="112">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O17,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11035,7 +11125,8 @@
         <v>-89655498</v>
       </c>
       <c r="L17" s="106" t="str">
-        <f>IF(J17-I17&gt;0,"증가",IF(J17-I17=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M17" s="107"/>
       <c r="N17" t="str">
@@ -11057,7 +11148,7 @@
     </row>
     <row r="18" spans="1:17" ht="22.5" customHeight="1">
       <c r="A18" s="108" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B18" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O18,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11100,10 +11191,11 @@
         <v>-8666660</v>
       </c>
       <c r="L18" s="113" t="str">
-        <f>IF(J18-I18&gt;0,"증가",IF(J18-I18=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M18" s="114" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="1"/>
@@ -11124,7 +11216,7 @@
     </row>
     <row r="19" spans="1:17" ht="22.5" customHeight="1">
       <c r="A19" s="108" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B19" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O19,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11166,8 +11258,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L19" s="113">
-        <f>IF(J19-I19&gt;0,"증가",IF(J19-I19=0,"변동없음","감소"))</f>
+      <c r="L19" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M19" s="115"/>
       <c r="N19" t="str">
@@ -11189,7 +11282,7 @@
     </row>
     <row r="20" spans="1:17" ht="22.5" customHeight="1">
       <c r="A20" s="108" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B20" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O20,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11231,11 +11324,12 @@
         <f t="shared" si="0"/>
         <v>-85067840</v>
       </c>
-      <c r="L20" s="113">
-        <f>IF(J20-I20&gt;0,"증가",IF(J20-I20=0,"변동없음","감소"))</f>
+      <c r="L20" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M20" s="114" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="1"/>
@@ -11256,7 +11350,7 @@
     </row>
     <row r="21" spans="1:17" ht="22.5" customHeight="1">
       <c r="A21" s="108" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B21" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O21,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11298,11 +11392,12 @@
         <f t="shared" si="0"/>
         <v>2390923</v>
       </c>
-      <c r="L21" s="113">
-        <f>IF(J21-I21&gt;0,"증가",IF(J21-I21=0,"변동없음","감소"))</f>
+      <c r="L21" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>증가</v>
       </c>
       <c r="M21" s="115" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="1"/>
@@ -11323,7 +11418,7 @@
     </row>
     <row r="22" spans="1:17" ht="22.5" customHeight="1">
       <c r="A22" s="108" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B22" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O22,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11365,11 +11460,12 @@
         <f t="shared" si="0"/>
         <v>-114086</v>
       </c>
-      <c r="L22" s="113">
-        <f>IF(J22-I22&gt;0,"증가",IF(J22-I22=0,"변동없음","감소"))</f>
+      <c r="L22" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M22" s="115" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="1"/>
@@ -11390,7 +11486,7 @@
     </row>
     <row r="23" spans="1:17" ht="22.5" customHeight="1">
       <c r="A23" s="108" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B23" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O23,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11432,8 +11528,9 @@
         <f t="shared" si="0"/>
         <v>38202</v>
       </c>
-      <c r="L23" s="113">
-        <f>IF(J23-I23&gt;0,"증가",IF(J23-I23=0,"변동없음","감소"))</f>
+      <c r="L23" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>증가</v>
       </c>
       <c r="M23" s="115"/>
       <c r="N23" t="str">
@@ -11455,7 +11552,7 @@
     </row>
     <row r="24" spans="1:17" ht="22.5" customHeight="1">
       <c r="A24" s="108" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B24" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O24,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11497,11 +11594,12 @@
         <f t="shared" si="0"/>
         <v>-56651</v>
       </c>
-      <c r="L24" s="113">
-        <f>IF(J24-I24&gt;0,"증가",IF(J24-I24=0,"변동없음","감소"))</f>
+      <c r="L24" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M24" s="115" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="1"/>
@@ -11522,7 +11620,7 @@
     </row>
     <row r="25" spans="1:17" ht="22.5" customHeight="1">
       <c r="A25" s="108" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B25" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O25,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11564,11 +11662,12 @@
         <f t="shared" si="0"/>
         <v>15800</v>
       </c>
-      <c r="L25" s="113">
-        <f>IF(J25-I25&gt;0,"증가",IF(J25-I25=0,"변동없음","감소"))</f>
+      <c r="L25" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>증가</v>
       </c>
       <c r="M25" s="115" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="1"/>
@@ -11589,7 +11688,7 @@
     </row>
     <row r="26" spans="1:17" ht="22.5" customHeight="1">
       <c r="A26" s="108" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B26" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O26,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11631,11 +11730,12 @@
         <f t="shared" si="0"/>
         <v>292880</v>
       </c>
-      <c r="L26" s="113">
-        <f>IF(J26-I26&gt;0,"증가",IF(J26-I26=0,"변동없음","감소"))</f>
+      <c r="L26" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>증가</v>
       </c>
       <c r="M26" s="115" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="N26" t="str">
         <f t="shared" si="1"/>
@@ -11656,7 +11756,7 @@
     </row>
     <row r="27" spans="1:17" ht="23.25" customHeight="1">
       <c r="A27" s="108" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B27" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O27,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11698,11 +11798,12 @@
         <f t="shared" si="0"/>
         <v>-970130</v>
       </c>
-      <c r="L27" s="113">
-        <f>IF(J27-I27&gt;0,"증가",IF(J27-I27=0,"변동없음","감소"))</f>
+      <c r="L27" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M27" s="115" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="N27" t="str">
         <f t="shared" si="1"/>
@@ -11723,7 +11824,7 @@
     </row>
     <row r="28" spans="1:17" ht="22.5" customHeight="1">
       <c r="A28" s="108" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B28" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O28,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11766,10 +11867,11 @@
         <v>0</v>
       </c>
       <c r="L28" s="113" t="str">
-        <f>IF(J28-I28&gt;0,"증가",IF(J28-I28=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M28" s="115" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N28" t="str">
         <f t="shared" si="1"/>
@@ -11790,7 +11892,7 @@
     </row>
     <row r="29" spans="1:17" ht="22.5" customHeight="1">
       <c r="A29" s="108" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B29" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O29,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11832,11 +11934,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L29" s="113">
-        <f>IF(J29-I29&gt;0,"증가",IF(J29-I29=0,"변동없음","감소"))</f>
+      <c r="L29" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M29" s="115" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="N29" t="str">
         <f t="shared" si="1"/>
@@ -11857,7 +11960,7 @@
     </row>
     <row r="30" spans="1:17" ht="22.5" customHeight="1">
       <c r="A30" s="108" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B30" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O30,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11900,10 +12003,11 @@
         <v>-866500</v>
       </c>
       <c r="L30" s="113" t="str">
-        <f>IF(J30-I30&gt;0,"증가",IF(J30-I30=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M30" s="115" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N30" t="str">
         <f t="shared" si="1"/>
@@ -11924,7 +12028,7 @@
     </row>
     <row r="31" spans="1:17" ht="22.5" customHeight="1">
       <c r="A31" s="108" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B31" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O31,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11967,10 +12071,11 @@
         <v>2420017</v>
       </c>
       <c r="L31" s="113" t="str">
-        <f>IF(J31-I31&gt;0,"증가",IF(J31-I31=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>증가</v>
       </c>
       <c r="M31" s="115" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="N31" t="str">
         <f t="shared" si="1"/>
@@ -11991,7 +12096,7 @@
     </row>
     <row r="32" spans="1:17" ht="22.5" customHeight="1">
       <c r="A32" s="108" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B32" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O32,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12034,10 +12139,11 @@
         <v>-1211928</v>
       </c>
       <c r="L32" s="113" t="str">
-        <f>IF(J32-I32&gt;0,"증가",IF(J32-I32=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M32" s="115" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="N32" t="str">
         <f t="shared" si="1"/>
@@ -12058,7 +12164,7 @@
     </row>
     <row r="33" spans="1:17" ht="22.5" customHeight="1">
       <c r="A33" s="108" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B33" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O33,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12100,11 +12206,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L33" s="113">
-        <f>IF(J33-I33&gt;0,"증가",IF(J33-I33=0,"변동없음","감소"))</f>
+      <c r="L33" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M33" s="115" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="N33" t="str">
         <f t="shared" si="1"/>
@@ -12125,7 +12232,7 @@
     </row>
     <row r="34" spans="1:17" ht="22.5" customHeight="1">
       <c r="A34" s="108" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B34" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O34,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12168,10 +12275,11 @@
         <v>3960168</v>
       </c>
       <c r="L34" s="113" t="str">
-        <f>IF(J34-I34&gt;0,"증가",IF(J34-I34=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>증가</v>
       </c>
       <c r="M34" s="115" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="N34" t="str">
         <f t="shared" si="1"/>
@@ -12192,7 +12300,7 @@
     </row>
     <row r="35" spans="1:17" ht="26.25" customHeight="1">
       <c r="A35" s="108" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B35" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O35,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12235,10 +12343,11 @@
         <v>-1819693</v>
       </c>
       <c r="L35" s="113" t="str">
-        <f>IF(J35-I35&gt;0,"증가",IF(J35-I35=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M35" s="114" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="N35" t="str">
         <f t="shared" si="1"/>
@@ -12259,7 +12368,7 @@
     </row>
     <row r="36" spans="1:17" ht="22.5" customHeight="1">
       <c r="A36" s="108" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B36" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O36,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12301,11 +12410,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L36" s="113">
-        <f>IF(J36-I36&gt;0,"증가",IF(J36-I36=0,"변동없음","감소"))</f>
+      <c r="L36" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M36" s="115" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N36" t="str">
         <f t="shared" si="1"/>
@@ -12326,7 +12436,7 @@
     </row>
     <row r="37" spans="1:17" ht="22.5" customHeight="1">
       <c r="A37" s="108" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B37" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O37,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12368,11 +12478,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L37" s="113">
-        <f>IF(J37-I37&gt;0,"증가",IF(J37-I37=0,"변동없음","감소"))</f>
+      <c r="L37" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M37" s="115" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="N37" t="str">
         <f t="shared" si="1"/>
@@ -12393,7 +12504,7 @@
     </row>
     <row r="38" spans="1:17" ht="24" customHeight="1">
       <c r="A38" s="74" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B38" s="91">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O38,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12436,7 +12547,8 @@
         <v>15405802</v>
       </c>
       <c r="L38" s="106" t="str">
-        <f>IF(J38-I38&gt;0,"증가",IF(J38-I38=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>증가</v>
       </c>
       <c r="M38" s="107"/>
       <c r="N38" t="str">
@@ -12458,7 +12570,7 @@
     </row>
     <row r="39" spans="1:17" ht="22.5" customHeight="1">
       <c r="A39" s="74" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B39" s="91">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O39,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12501,7 +12613,8 @@
         <v>-33721088</v>
       </c>
       <c r="L39" s="106" t="str">
-        <f>IF(J39-I39&gt;0,"증가",IF(J39-I39=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M39" s="107"/>
       <c r="N39" t="str">
@@ -12523,7 +12636,7 @@
     </row>
     <row r="40" spans="1:17" ht="22.5" customHeight="1">
       <c r="A40" s="67" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B40" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O40,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12566,10 +12679,11 @@
         <v>-33716084</v>
       </c>
       <c r="L40" s="113" t="str">
-        <f>IF(J40-I40&gt;0,"증가",IF(J40-I40=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M40" s="115" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="N40" t="str">
         <f t="shared" si="1"/>
@@ -12590,7 +12704,7 @@
     </row>
     <row r="41" spans="1:17" ht="22.5" customHeight="1">
       <c r="A41" s="67" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B41" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O41,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12632,8 +12746,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L41" s="113">
-        <f>IF(J41-I41&gt;0,"증가",IF(J41-I41=0,"변동없음","감소"))</f>
+      <c r="L41" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M41" s="110"/>
       <c r="N41" t="str">
@@ -12655,7 +12770,7 @@
     </row>
     <row r="42" spans="1:17" ht="22.5" customHeight="1">
       <c r="A42" s="67" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B42" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O42,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12697,8 +12812,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L42" s="113">
-        <f>IF(J42-I42&gt;0,"증가",IF(J42-I42=0,"변동없음","감소"))</f>
+      <c r="L42" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M42" s="110"/>
       <c r="N42" t="str">
@@ -12720,7 +12836,7 @@
     </row>
     <row r="43" spans="1:17" ht="22.5" customHeight="1">
       <c r="A43" s="67" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B43" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O43,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12762,8 +12878,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L43" s="113">
-        <f>IF(J43-I43&gt;0,"증가",IF(J43-I43=0,"변동없음","감소"))</f>
+      <c r="L43" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M43" s="110"/>
       <c r="N43" t="str">
@@ -12785,7 +12902,7 @@
     </row>
     <row r="44" spans="1:17" ht="22.5" customHeight="1">
       <c r="A44" s="67" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B44" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O44,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12828,10 +12945,11 @@
         <v>-5004</v>
       </c>
       <c r="L44" s="113" t="str">
-        <f>IF(J44-I44&gt;0,"증가",IF(J44-I44=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M44" s="116" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="N44" t="str">
         <f t="shared" si="1"/>
@@ -12852,7 +12970,7 @@
     </row>
     <row r="45" spans="1:17" ht="22.5" customHeight="1">
       <c r="A45" s="74" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B45" s="112">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O45,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12895,7 +13013,8 @@
         <v>-90076</v>
       </c>
       <c r="L45" s="106" t="str">
-        <f>IF(J45-I45&gt;0,"증가",IF(J45-I45=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M45" s="107"/>
       <c r="N45" t="str">
@@ -12917,7 +13036,7 @@
     </row>
     <row r="46" spans="1:17" ht="22.5" customHeight="1">
       <c r="A46" s="67" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B46" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O46,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12959,8 +13078,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L46" s="113">
-        <f>IF(J46-I46&gt;0,"증가",IF(J46-I46=0,"변동없음","감소"))</f>
+      <c r="L46" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M46" s="110"/>
       <c r="N46" t="str">
@@ -12982,7 +13102,7 @@
     </row>
     <row r="47" spans="1:17" ht="22.5" customHeight="1">
       <c r="A47" s="67" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B47" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O47,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13024,8 +13144,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L47" s="113">
-        <f>IF(J47-I47&gt;0,"증가",IF(J47-I47=0,"변동없음","감소"))</f>
+      <c r="L47" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M47" s="110"/>
       <c r="N47" t="str">
@@ -13047,7 +13168,7 @@
     </row>
     <row r="48" spans="1:17" ht="22.5" customHeight="1">
       <c r="A48" s="67" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B48" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O48,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13089,8 +13210,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L48" s="113">
-        <f>IF(J48-I48&gt;0,"증가",IF(J48-I48=0,"변동없음","감소"))</f>
+      <c r="L48" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M48" s="110"/>
       <c r="N48" t="str">
@@ -13112,7 +13234,7 @@
     </row>
     <row r="49" spans="1:17" ht="22.5" customHeight="1">
       <c r="A49" s="67" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B49" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O49,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13155,7 +13277,8 @@
         <v>-90076</v>
       </c>
       <c r="L49" s="113" t="str">
-        <f>IF(J49-I49&gt;0,"증가",IF(J49-I49=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M49" s="110"/>
       <c r="N49" t="str">
@@ -13177,7 +13300,7 @@
     </row>
     <row r="50" spans="1:17" ht="22.5" customHeight="1">
       <c r="A50" s="108" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B50" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O50,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13219,8 +13342,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L50" s="113">
-        <f>IF(J50-I50&gt;0,"증가",IF(J50-I50=0,"변동없음","감소"))</f>
+      <c r="L50" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M50" s="110"/>
       <c r="N50" t="str">
@@ -13242,7 +13366,7 @@
     </row>
     <row r="51" spans="1:17" ht="24" customHeight="1">
       <c r="A51" s="74" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B51" s="91">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O51,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13285,7 +13409,8 @@
         <v>-18225210</v>
       </c>
       <c r="L51" s="106" t="str">
-        <f>IF(J51-I51&gt;0,"증가",IF(J51-I51=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M51" s="107"/>
       <c r="N51" t="str">
@@ -13307,7 +13432,7 @@
     </row>
     <row r="52" spans="1:17" ht="22.5" customHeight="1">
       <c r="A52" s="74" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B52" s="91">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O52,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13349,8 +13474,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L52" s="106">
-        <f>IF(J52-I52&gt;0,"증가",IF(J52-I52=0,"변동없음","감소"))</f>
+      <c r="L52" s="106" t="str">
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M52" s="107"/>
       <c r="N52" t="str">
@@ -13372,7 +13498,7 @@
     </row>
     <row r="53" spans="1:17" ht="22.5" customHeight="1">
       <c r="A53" s="67" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B53" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O53,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13414,8 +13540,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L53" s="113">
-        <f>IF(J53-I53&gt;0,"증가",IF(J53-I53=0,"변동없음","감소"))</f>
+      <c r="L53" s="113" t="str">
+        <f t="shared" si="3"/>
+        <v>변동없음</v>
       </c>
       <c r="M53" s="110"/>
       <c r="N53" t="str">
@@ -13437,7 +13564,7 @@
     </row>
     <row r="54" spans="1:17" ht="24" customHeight="1">
       <c r="A54" s="74" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B54" s="91">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O54,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13480,7 +13607,8 @@
         <v>-18225210</v>
       </c>
       <c r="L54" s="106" t="str">
-        <f>IF(J54-I54&gt;0,"증가",IF(J54-I54=0,"변동없음","감소"))</f>
+        <f t="shared" si="3"/>
+        <v>감소</v>
       </c>
       <c r="M54" s="107"/>
       <c r="N54" t="str">
@@ -13530,7 +13658,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.59027777777777801" bottom="0.35486111111111102" header="0.511811023622047" footer="0.31527777777777799"/>
-  <pageSetup paperSize="9" scale="61" orientation="portrait" blackAndWhite="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="61" orientation="portrait" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P/1</oddFooter>
   </headerFooter>
@@ -13675,31 +13803,31 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" customHeight="1">
       <c r="A1" s="157" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B1" s="159" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C1" s="160"/>
       <c r="D1" s="159" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E1" s="160"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" customHeight="1">
       <c r="A2" s="161"/>
       <c r="B2" s="157" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C2" s="158"/>
       <c r="D2" s="157" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E2" s="158"/>
     </row>
     <row r="3" spans="1:7" ht="12" customHeight="1">
       <c r="A3" s="119" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B3" s="120"/>
       <c r="C3" s="120"/>
@@ -13716,15 +13844,15 @@
     </row>
     <row r="4" spans="1:7" ht="12" customHeight="1">
       <c r="A4" s="121" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B4" s="120"/>
       <c r="C4" s="120" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="120" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" si="0"/>
@@ -13737,15 +13865,15 @@
     </row>
     <row r="5" spans="1:7" ht="12" customHeight="1">
       <c r="A5" s="121" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B5" s="120"/>
       <c r="C5" s="120" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D5" s="120"/>
       <c r="E5" s="120" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F5" t="str">
         <f t="shared" si="0"/>
@@ -13758,15 +13886,15 @@
     </row>
     <row r="6" spans="1:7" ht="12" customHeight="1">
       <c r="A6" s="119" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B6" s="120"/>
       <c r="C6" s="120" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D6" s="120"/>
       <c r="E6" s="120" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F6" t="str">
         <f t="shared" si="0"/>
@@ -13779,15 +13907,15 @@
     </row>
     <row r="7" spans="1:7" ht="12" customHeight="1">
       <c r="A7" s="119" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B7" s="120"/>
       <c r="C7" s="120" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D7" s="120"/>
       <c r="E7" s="120" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="0"/>
@@ -13800,15 +13928,15 @@
     </row>
     <row r="8" spans="1:7" ht="12" customHeight="1">
       <c r="A8" s="119" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B8" s="120"/>
       <c r="C8" s="120" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D8" s="120"/>
       <c r="E8" s="120" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F8" t="str">
         <f t="shared" si="0"/>
@@ -13821,15 +13949,15 @@
     </row>
     <row r="9" spans="1:7" ht="12" customHeight="1">
       <c r="A9" s="119" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B9" s="120"/>
       <c r="C9" s="120" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D9" s="120"/>
       <c r="E9" s="120" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" si="0"/>
@@ -13842,14 +13970,14 @@
     </row>
     <row r="10" spans="1:7" ht="12" customHeight="1">
       <c r="A10" s="119" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B10" s="120" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C10" s="120"/>
       <c r="D10" s="120" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E10" s="120"/>
       <c r="F10" t="str">
@@ -13863,19 +13991,19 @@
     </row>
     <row r="11" spans="1:7" ht="12" customHeight="1">
       <c r="A11" s="119" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B11" s="120" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C11" s="120" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D11" s="120" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E11" s="120" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="0"/>
@@ -13888,14 +14016,14 @@
     </row>
     <row r="12" spans="1:7" ht="12" customHeight="1">
       <c r="A12" s="119" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B12" s="120" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C12" s="120"/>
       <c r="D12" s="120" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E12" s="120"/>
       <c r="F12" t="str">
@@ -13909,19 +14037,19 @@
     </row>
     <row r="13" spans="1:7" ht="12" customHeight="1">
       <c r="A13" s="119" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B13" s="120" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C13" s="120" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D13" s="120" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E13" s="120" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="0"/>
@@ -13934,15 +14062,15 @@
     </row>
     <row r="14" spans="1:7" ht="12" customHeight="1">
       <c r="A14" s="122" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B14" s="120"/>
       <c r="C14" s="120" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D14" s="120"/>
       <c r="E14" s="120" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F14" t="str">
         <f t="shared" si="0"/>
@@ -13955,15 +14083,15 @@
     </row>
     <row r="15" spans="1:7" ht="12" customHeight="1">
       <c r="A15" s="119" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B15" s="120"/>
       <c r="C15" s="120" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D15" s="120"/>
       <c r="E15" s="120" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F15" t="str">
         <f t="shared" si="0"/>
@@ -13976,15 +14104,15 @@
     </row>
     <row r="16" spans="1:7" ht="12" customHeight="1">
       <c r="A16" s="119" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B16" s="120"/>
       <c r="C16" s="120" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D16" s="120"/>
       <c r="E16" s="120" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F16" t="str">
         <f t="shared" si="0"/>
@@ -13997,15 +14125,15 @@
     </row>
     <row r="17" spans="1:7" ht="12" customHeight="1">
       <c r="A17" s="119" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B17" s="120"/>
       <c r="C17" s="120" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D17" s="120"/>
       <c r="E17" s="120" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F17" t="str">
         <f t="shared" si="0"/>
@@ -14018,11 +14146,11 @@
     </row>
     <row r="18" spans="1:7" ht="12" customHeight="1">
       <c r="A18" s="119" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B18" s="120"/>
       <c r="C18" s="120" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D18" s="120"/>
       <c r="E18" s="120"/>
@@ -14037,11 +14165,11 @@
     </row>
     <row r="19" spans="1:7" ht="12" customHeight="1">
       <c r="A19" s="119" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B19" s="120"/>
       <c r="C19" s="120" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D19" s="120"/>
       <c r="E19" s="120"/>
@@ -14056,15 +14184,15 @@
     </row>
     <row r="20" spans="1:7" ht="12" customHeight="1">
       <c r="A20" s="121" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B20" s="120"/>
       <c r="C20" s="120" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D20" s="120"/>
       <c r="E20" s="120" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F20" t="str">
         <f t="shared" si="0"/>
@@ -14077,15 +14205,15 @@
     </row>
     <row r="21" spans="1:7" ht="12" customHeight="1">
       <c r="A21" s="119" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B21" s="120"/>
       <c r="C21" s="120" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D21" s="120"/>
       <c r="E21" s="120" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F21" t="str">
         <f t="shared" si="0"/>
@@ -14098,15 +14226,15 @@
     </row>
     <row r="22" spans="1:7" ht="12" customHeight="1">
       <c r="A22" s="121" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B22" s="120"/>
       <c r="C22" s="120" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D22" s="120"/>
       <c r="E22" s="120" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F22" t="str">
         <f t="shared" si="0"/>
@@ -14119,15 +14247,15 @@
     </row>
     <row r="23" spans="1:7" ht="12" customHeight="1">
       <c r="A23" s="119" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B23" s="120"/>
       <c r="C23" s="120" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D23" s="120"/>
       <c r="E23" s="120" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F23" t="str">
         <f t="shared" si="0"/>
@@ -14140,15 +14268,15 @@
     </row>
     <row r="24" spans="1:7" ht="12" customHeight="1">
       <c r="A24" s="122" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B24" s="120"/>
       <c r="C24" s="120" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D24" s="120"/>
       <c r="E24" s="120" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F24" t="str">
         <f t="shared" si="0"/>
@@ -14161,15 +14289,15 @@
     </row>
     <row r="25" spans="1:7" ht="12" customHeight="1">
       <c r="A25" s="121" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B25" s="120"/>
       <c r="C25" s="120" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D25" s="120"/>
       <c r="E25" s="120" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F25" t="str">
         <f t="shared" si="0"/>
@@ -14182,15 +14310,15 @@
     </row>
     <row r="26" spans="1:7" ht="12" customHeight="1">
       <c r="A26" s="119" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B26" s="120"/>
       <c r="C26" s="120" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D26" s="120"/>
       <c r="E26" s="120" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F26" t="str">
         <f t="shared" si="0"/>
@@ -14203,15 +14331,15 @@
     </row>
     <row r="27" spans="1:7" ht="12" customHeight="1">
       <c r="A27" s="122" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B27" s="120"/>
       <c r="C27" s="120" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D27" s="120"/>
       <c r="E27" s="120" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F27" t="str">
         <f t="shared" si="0"/>
@@ -14224,14 +14352,14 @@
     </row>
     <row r="28" spans="1:7" ht="12" customHeight="1">
       <c r="A28" s="119" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B28" s="120" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C28" s="120"/>
       <c r="D28" s="120" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E28" s="120"/>
       <c r="F28" t="str">
@@ -14245,19 +14373,19 @@
     </row>
     <row r="29" spans="1:7" ht="12" customHeight="1">
       <c r="A29" s="119" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B29" s="120" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C29" s="120" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D29" s="120" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E29" s="120" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F29" t="str">
         <f t="shared" si="0"/>
@@ -14270,14 +14398,14 @@
     </row>
     <row r="30" spans="1:7" ht="12" customHeight="1">
       <c r="A30" s="119" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B30" s="120" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C30" s="120"/>
       <c r="D30" s="120" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E30" s="120"/>
       <c r="F30" t="str">
@@ -14291,19 +14419,19 @@
     </row>
     <row r="31" spans="1:7" ht="12" customHeight="1">
       <c r="A31" s="119" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B31" s="120" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C31" s="120" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D31" s="120" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E31" s="120" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F31" t="str">
         <f t="shared" si="0"/>
@@ -14316,14 +14444,14 @@
     </row>
     <row r="32" spans="1:7" ht="12" customHeight="1">
       <c r="A32" s="119" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B32" s="120" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C32" s="120"/>
       <c r="D32" s="120" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E32" s="120"/>
       <c r="F32" t="str">
@@ -14337,19 +14465,19 @@
     </row>
     <row r="33" spans="1:7" ht="12" customHeight="1">
       <c r="A33" s="119" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B33" s="120" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C33" s="120" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D33" s="120" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E33" s="120" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F33" t="str">
         <f t="shared" si="0"/>
@@ -14362,14 +14490,14 @@
     </row>
     <row r="34" spans="1:7" ht="12" customHeight="1">
       <c r="A34" s="119" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B34" s="120" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C34" s="120"/>
       <c r="D34" s="120" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E34" s="120"/>
       <c r="F34" t="str">
@@ -14383,19 +14511,19 @@
     </row>
     <row r="35" spans="1:7" ht="12" customHeight="1">
       <c r="A35" s="119" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B35" s="120" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C35" s="120" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D35" s="120" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E35" s="120" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F35" t="str">
         <f t="shared" ref="F35:F70" si="1">IF(A35="","",SUBSTITUTE(A35," ",""))</f>
@@ -14408,7 +14536,7 @@
     </row>
     <row r="36" spans="1:7" ht="12" customHeight="1">
       <c r="A36" s="119" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B36" s="120"/>
       <c r="C36" s="120"/>
@@ -14425,15 +14553,15 @@
     </row>
     <row r="37" spans="1:7" ht="12" customHeight="1">
       <c r="A37" s="122" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B37" s="120"/>
       <c r="C37" s="120" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D37" s="120"/>
       <c r="E37" s="120" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F37" t="str">
         <f t="shared" si="1"/>
@@ -14446,15 +14574,15 @@
     </row>
     <row r="38" spans="1:7" ht="12" customHeight="1">
       <c r="A38" s="122" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B38" s="120"/>
       <c r="C38" s="120" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D38" s="120"/>
       <c r="E38" s="120" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F38" t="str">
         <f t="shared" si="1"/>
@@ -14467,15 +14595,15 @@
     </row>
     <row r="39" spans="1:7" ht="12" customHeight="1">
       <c r="A39" s="122" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B39" s="120"/>
       <c r="C39" s="120" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D39" s="120"/>
       <c r="E39" s="120" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F39" t="str">
         <f t="shared" si="1"/>
@@ -14488,15 +14616,15 @@
     </row>
     <row r="40" spans="1:7" ht="12" customHeight="1">
       <c r="A40" s="122" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B40" s="120"/>
       <c r="C40" s="120" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D40" s="120"/>
       <c r="E40" s="120" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F40" t="str">
         <f t="shared" si="1"/>
@@ -14509,15 +14637,15 @@
     </row>
     <row r="41" spans="1:7" ht="12" customHeight="1">
       <c r="A41" s="119" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B41" s="120"/>
       <c r="C41" s="120" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D41" s="120"/>
       <c r="E41" s="120" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F41" t="str">
         <f t="shared" si="1"/>
@@ -14530,7 +14658,7 @@
     </row>
     <row r="42" spans="1:7" ht="12" customHeight="1">
       <c r="A42" s="119" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B42" s="120"/>
       <c r="C42" s="120"/>
@@ -14547,15 +14675,15 @@
     </row>
     <row r="43" spans="1:7" ht="12" customHeight="1">
       <c r="A43" s="119" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B43" s="120"/>
       <c r="C43" s="120" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D43" s="120"/>
       <c r="E43" s="120" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F43" t="str">
         <f t="shared" si="1"/>
@@ -14568,15 +14696,15 @@
     </row>
     <row r="44" spans="1:7" ht="12" customHeight="1">
       <c r="A44" s="119" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B44" s="120"/>
       <c r="C44" s="120" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D44" s="120"/>
       <c r="E44" s="120" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F44" t="str">
         <f t="shared" si="1"/>
@@ -14589,15 +14717,15 @@
     </row>
     <row r="45" spans="1:7" ht="12" customHeight="1">
       <c r="A45" s="119" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B45" s="120"/>
       <c r="C45" s="120" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D45" s="120"/>
       <c r="E45" s="120" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F45" t="str">
         <f t="shared" si="1"/>
@@ -14610,15 +14738,15 @@
     </row>
     <row r="46" spans="1:7" ht="12" customHeight="1">
       <c r="A46" s="122" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B46" s="120"/>
       <c r="C46" s="120" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D46" s="120"/>
       <c r="E46" s="120" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F46" t="str">
         <f t="shared" si="1"/>
@@ -14631,11 +14759,11 @@
     </row>
     <row r="47" spans="1:7" ht="12" customHeight="1">
       <c r="A47" s="119" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B47" s="120"/>
       <c r="C47" s="120" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D47" s="120"/>
       <c r="E47" s="120"/>
@@ -14650,11 +14778,11 @@
     </row>
     <row r="48" spans="1:7" ht="12" customHeight="1">
       <c r="A48" s="119" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B48" s="120"/>
       <c r="C48" s="120" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D48" s="120"/>
       <c r="E48" s="120"/>
@@ -14669,15 +14797,15 @@
     </row>
     <row r="49" spans="1:7" ht="12" customHeight="1">
       <c r="A49" s="119" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B49" s="120"/>
       <c r="C49" s="120" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D49" s="120"/>
       <c r="E49" s="120" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F49" t="str">
         <f t="shared" si="1"/>
@@ -14690,13 +14818,13 @@
     </row>
     <row r="50" spans="1:7" ht="12" customHeight="1">
       <c r="A50" s="121" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B50" s="120"/>
       <c r="C50" s="120"/>
       <c r="D50" s="120"/>
       <c r="E50" s="120" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F50" t="str">
         <f t="shared" si="1"/>
@@ -14709,15 +14837,15 @@
     </row>
     <row r="51" spans="1:7" ht="12" customHeight="1">
       <c r="A51" s="119" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B51" s="120"/>
       <c r="C51" s="120" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D51" s="120"/>
       <c r="E51" s="120" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F51" t="str">
         <f t="shared" si="1"/>
@@ -14730,15 +14858,15 @@
     </row>
     <row r="52" spans="1:7" ht="12" customHeight="1">
       <c r="A52" s="119" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B52" s="120"/>
       <c r="C52" s="120" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D52" s="120"/>
       <c r="E52" s="120" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F52" t="str">
         <f t="shared" si="1"/>
@@ -14751,13 +14879,13 @@
     </row>
     <row r="53" spans="1:7" ht="12" customHeight="1">
       <c r="A53" s="119" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B53" s="120"/>
       <c r="C53" s="120"/>
       <c r="D53" s="120"/>
       <c r="E53" s="120" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F53" t="str">
         <f t="shared" si="1"/>
@@ -14770,15 +14898,15 @@
     </row>
     <row r="54" spans="1:7" ht="12" customHeight="1">
       <c r="A54" s="119" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B54" s="120"/>
       <c r="C54" s="120" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D54" s="120"/>
       <c r="E54" s="120" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F54" t="str">
         <f t="shared" si="1"/>
@@ -14791,15 +14919,15 @@
     </row>
     <row r="55" spans="1:7" ht="12" customHeight="1">
       <c r="A55" s="121" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B55" s="120"/>
       <c r="C55" s="120" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D55" s="120"/>
       <c r="E55" s="120" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F55" t="str">
         <f t="shared" si="1"/>
@@ -14812,7 +14940,7 @@
     </row>
     <row r="56" spans="1:7" ht="12" customHeight="1">
       <c r="A56" s="122" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B56" s="120"/>
       <c r="C56" s="120"/>
@@ -14829,15 +14957,15 @@
     </row>
     <row r="57" spans="1:7" ht="12" customHeight="1">
       <c r="A57" s="119" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B57" s="120"/>
       <c r="C57" s="120" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D57" s="120"/>
       <c r="E57" s="120" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F57" t="str">
         <f t="shared" si="1"/>
@@ -14850,15 +14978,15 @@
     </row>
     <row r="58" spans="1:7" ht="12" customHeight="1">
       <c r="A58" s="119" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B58" s="120"/>
       <c r="C58" s="120" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D58" s="120"/>
       <c r="E58" s="120" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F58" t="str">
         <f t="shared" si="1"/>
@@ -14871,15 +14999,15 @@
     </row>
     <row r="59" spans="1:7" ht="12" customHeight="1">
       <c r="A59" s="119" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B59" s="120"/>
       <c r="C59" s="120" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D59" s="120"/>
       <c r="E59" s="120" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F59" t="str">
         <f t="shared" si="1"/>
@@ -14892,15 +15020,15 @@
     </row>
     <row r="60" spans="1:7" ht="12" customHeight="1">
       <c r="A60" s="119" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B60" s="120"/>
       <c r="C60" s="120" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D60" s="120"/>
       <c r="E60" s="120" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F60" t="str">
         <f t="shared" si="1"/>
@@ -14913,7 +15041,7 @@
     </row>
     <row r="61" spans="1:7" ht="12" customHeight="1">
       <c r="A61" s="121" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B61" s="120"/>
       <c r="C61" s="120"/>
@@ -14930,7 +15058,7 @@
     </row>
     <row r="62" spans="1:7" ht="12" customHeight="1">
       <c r="A62" s="119" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B62" s="120"/>
       <c r="C62" s="120"/>
@@ -14947,15 +15075,15 @@
     </row>
     <row r="63" spans="1:7" ht="12" customHeight="1">
       <c r="A63" s="122" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B63" s="120"/>
       <c r="C63" s="120" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D63" s="120"/>
       <c r="E63" s="120" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F63" t="str">
         <f t="shared" si="1"/>
@@ -14968,15 +15096,15 @@
     </row>
     <row r="64" spans="1:7" ht="12" customHeight="1">
       <c r="A64" s="119" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B64" s="120"/>
       <c r="C64" s="120" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D64" s="120"/>
       <c r="E64" s="120" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F64" t="str">
         <f t="shared" si="1"/>
@@ -14989,15 +15117,15 @@
     </row>
     <row r="65" spans="1:7" ht="12" customHeight="1">
       <c r="A65" s="122" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B65" s="120"/>
       <c r="C65" s="120" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D65" s="120"/>
       <c r="E65" s="120" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F65" t="str">
         <f t="shared" si="1"/>
@@ -15010,7 +15138,7 @@
     </row>
     <row r="66" spans="1:7" ht="12" customHeight="1">
       <c r="A66" s="122" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B66" s="120"/>
       <c r="C66" s="120"/>
@@ -15027,7 +15155,7 @@
     </row>
     <row r="67" spans="1:7" ht="12" customHeight="1">
       <c r="A67" s="122" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B67" s="120"/>
       <c r="C67" s="120"/>
@@ -15044,7 +15172,7 @@
     </row>
     <row r="68" spans="1:7" ht="12" customHeight="1">
       <c r="A68" s="119" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B68" s="120"/>
       <c r="C68" s="120"/>
@@ -15061,15 +15189,15 @@
     </row>
     <row r="69" spans="1:7" ht="12" customHeight="1">
       <c r="A69" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B69" s="120"/>
       <c r="C69" s="120" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D69" s="120"/>
       <c r="E69" s="120" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F69" t="str">
         <f t="shared" si="1"/>
@@ -15082,15 +15210,15 @@
     </row>
     <row r="70" spans="1:7" ht="12" customHeight="1">
       <c r="A70" s="121" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B70" s="120"/>
       <c r="C70" s="120" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D70" s="120"/>
       <c r="E70" s="120" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F70" t="str">
         <f t="shared" si="1"/>
@@ -15309,51 +15437,51 @@
   <sheetData>
     <row r="1" spans="1:17" ht="18.75" customHeight="1">
       <c r="A1" s="118" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B1" s="118" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" s="123" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1" s="123" t="s">
+        <v>187</v>
+      </c>
+      <c r="E1" s="123" t="s">
         <v>188</v>
       </c>
-      <c r="C1" s="123" t="s">
+      <c r="F1" s="123" t="s">
         <v>189</v>
       </c>
-      <c r="D1" s="123" t="s">
+      <c r="G1" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="E1" s="123" t="s">
+      <c r="H1" s="123" t="s">
         <v>191</v>
       </c>
-      <c r="F1" s="123" t="s">
-        <v>192</v>
-      </c>
-      <c r="G1" s="123" t="s">
-        <v>193</v>
-      </c>
-      <c r="H1" s="123" t="s">
-        <v>194</v>
-      </c>
       <c r="I1" s="123" t="s">
+        <v>312</v>
+      </c>
+      <c r="J1" s="123" t="s">
+        <v>313</v>
+      </c>
+      <c r="K1" s="123" t="s">
+        <v>314</v>
+      </c>
+      <c r="L1" s="123" t="s">
+        <v>315</v>
+      </c>
+      <c r="M1" s="123" t="s">
         <v>316</v>
       </c>
-      <c r="J1" s="123" t="s">
+      <c r="N1" s="123" t="s">
         <v>317</v>
-      </c>
-      <c r="K1" s="123" t="s">
-        <v>318</v>
-      </c>
-      <c r="L1" s="123" t="s">
-        <v>319</v>
-      </c>
-      <c r="M1" s="123" t="s">
-        <v>320</v>
-      </c>
-      <c r="N1" s="123" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="13.5" customHeight="1">
       <c r="A2" s="121" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B2" s="124">
         <v>21519965336</v>
@@ -15395,7 +15523,7 @@
     </row>
     <row r="3" spans="1:17" ht="13.5" customHeight="1">
       <c r="A3" s="119" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B3" s="124">
         <v>21466362478</v>
@@ -15437,7 +15565,7 @@
     </row>
     <row r="4" spans="1:17" ht="13.5" customHeight="1">
       <c r="A4" s="119" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B4" s="124">
         <v>53602858</v>
@@ -15479,7 +15607,7 @@
     </row>
     <row r="5" spans="1:17" ht="13.5" customHeight="1">
       <c r="A5" s="121" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B5" s="124">
         <v>17650813148</v>
@@ -15521,7 +15649,7 @@
     </row>
     <row r="6" spans="1:17" ht="13.5" customHeight="1">
       <c r="A6" s="119" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B6" s="124">
         <v>17650813148</v>
@@ -15563,7 +15691,7 @@
     </row>
     <row r="7" spans="1:17" ht="13.5" customHeight="1">
       <c r="A7" s="119" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B7" s="124">
         <v>2126111102</v>
@@ -15605,7 +15733,7 @@
     </row>
     <row r="8" spans="1:17" ht="13.5" customHeight="1">
       <c r="A8" s="119" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B8" s="124">
         <v>18479894308</v>
@@ -15647,7 +15775,7 @@
     </row>
     <row r="9" spans="1:17" ht="13.5" customHeight="1">
       <c r="A9" s="119" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B9" s="124">
         <v>91576826</v>
@@ -15689,7 +15817,7 @@
     </row>
     <row r="10" spans="1:17" ht="13.5" customHeight="1">
       <c r="A10" s="119" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B10" s="124">
         <v>2863615436</v>
@@ -15731,7 +15859,7 @@
     </row>
     <row r="11" spans="1:17" ht="13.5" customHeight="1">
       <c r="A11" s="121" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B11" s="124">
         <v>3869152188</v>
@@ -15773,7 +15901,7 @@
     </row>
     <row r="12" spans="1:17" ht="13.5" customHeight="1">
       <c r="A12" s="121" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B12" s="124">
         <v>2161095954</v>
@@ -15815,7 +15943,7 @@
     </row>
     <row r="13" spans="1:17" ht="13.5" customHeight="1">
       <c r="A13" s="119" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B13" s="124">
         <v>1229848831</v>
@@ -15857,7 +15985,7 @@
     </row>
     <row r="14" spans="1:17" ht="11.25" customHeight="1">
       <c r="A14" s="122" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B14" s="124">
         <v>88091340</v>
@@ -15899,7 +16027,7 @@
     </row>
     <row r="15" spans="1:17" ht="13.5" customHeight="1">
       <c r="A15" s="119" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B15" s="124">
         <v>110546776</v>
@@ -15941,7 +16069,7 @@
     </row>
     <row r="16" spans="1:17" ht="13.5" customHeight="1">
       <c r="A16" s="119" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B16" s="124">
         <v>7859988</v>
@@ -15983,7 +16111,7 @@
     </row>
     <row r="17" spans="1:17" ht="13.5" customHeight="1">
       <c r="A17" s="119" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B17" s="124">
         <v>43323349</v>
@@ -16025,7 +16153,7 @@
     </row>
     <row r="18" spans="1:17" ht="13.5" customHeight="1">
       <c r="A18" s="119" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B18" s="124">
         <v>10884279</v>
@@ -16067,7 +16195,7 @@
     </row>
     <row r="19" spans="1:17" ht="13.5" customHeight="1">
       <c r="A19" s="119" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B19" s="124">
         <v>658900</v>
@@ -16109,7 +16237,7 @@
     </row>
     <row r="20" spans="1:17" ht="13.5" customHeight="1">
       <c r="A20" s="119" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B20" s="124">
         <v>9937528</v>
@@ -16151,7 +16279,7 @@
     </row>
     <row r="21" spans="1:17" ht="13.5" customHeight="1">
       <c r="A21" s="119" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B21" s="124">
         <v>61818760</v>
@@ -16193,7 +16321,7 @@
     </row>
     <row r="22" spans="1:17" ht="13.5" customHeight="1">
       <c r="A22" s="119" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B22" s="124">
         <v>71625807</v>
@@ -16235,7 +16363,7 @@
     </row>
     <row r="23" spans="1:17" ht="13.5" customHeight="1">
       <c r="A23" s="119" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B23" s="124">
         <v>94500000</v>
@@ -16277,7 +16405,7 @@
     </row>
     <row r="24" spans="1:17" ht="13.5" customHeight="1">
       <c r="A24" s="119" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B24" s="124">
         <v>48751589</v>
@@ -16319,7 +16447,7 @@
     </row>
     <row r="25" spans="1:17" ht="13.5" customHeight="1">
       <c r="A25" s="119" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B25" s="124">
         <v>155024259</v>
@@ -16361,7 +16489,7 @@
     </row>
     <row r="26" spans="1:17" ht="13.5" customHeight="1">
       <c r="A26" s="119" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B26" s="124">
         <v>11781419</v>
@@ -16403,7 +16531,7 @@
     </row>
     <row r="27" spans="1:17" ht="13.5" customHeight="1">
       <c r="A27" s="119" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B27" s="124">
         <v>18876205</v>
@@ -16445,7 +16573,7 @@
     </row>
     <row r="28" spans="1:17" ht="11.25" customHeight="1">
       <c r="A28" s="122" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B28" s="124">
         <v>196598820</v>
@@ -16487,7 +16615,7 @@
     </row>
     <row r="29" spans="1:17" ht="13.5" customHeight="1">
       <c r="A29" s="119" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B29" s="124">
         <v>968104</v>
@@ -16529,7 +16657,7 @@
     </row>
     <row r="30" spans="1:17" ht="13.5" customHeight="1">
       <c r="A30" s="119" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B30" s="124">
         <v>1708056234</v>
@@ -16571,7 +16699,7 @@
     </row>
     <row r="31" spans="1:17" ht="11.25" customHeight="1">
       <c r="A31" s="121" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B31" s="124">
         <v>145089917</v>
@@ -16613,7 +16741,7 @@
     </row>
     <row r="32" spans="1:17" ht="13.5" customHeight="1">
       <c r="A32" s="119" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B32" s="124">
         <v>113934601</v>
@@ -16655,7 +16783,7 @@
     </row>
     <row r="33" spans="1:17" ht="13.5" customHeight="1">
       <c r="A33" s="122" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B33" s="124">
         <v>9493467</v>
@@ -16697,7 +16825,7 @@
     </row>
     <row r="34" spans="1:17" ht="13.5" customHeight="1">
       <c r="A34" s="122" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B34" s="124">
         <v>7089909</v>
@@ -16739,7 +16867,7 @@
     </row>
     <row r="35" spans="1:17" ht="13.5" customHeight="1">
       <c r="A35" s="119" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B35" s="124">
         <v>14571940</v>
@@ -16781,7 +16909,7 @@
     </row>
     <row r="36" spans="1:17" ht="13.5" customHeight="1">
       <c r="A36" s="119" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B36" s="124">
         <v>1315405</v>
@@ -16823,7 +16951,7 @@
     </row>
     <row r="37" spans="1:17" ht="13.5" customHeight="1">
       <c r="A37" s="119" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B37" s="124">
         <v>1131469</v>
@@ -16865,7 +16993,7 @@
     </row>
     <row r="38" spans="1:17" ht="11.25" customHeight="1">
       <c r="A38" s="122" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B38" s="124">
         <v>2000</v>
@@ -16907,7 +17035,7 @@
     </row>
     <row r="39" spans="1:17" ht="13.5" customHeight="1">
       <c r="A39" s="119" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B39" s="124">
         <v>181936</v>
@@ -16949,7 +17077,7 @@
     </row>
     <row r="40" spans="1:17" ht="13.5" customHeight="1">
       <c r="A40" s="121" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B40" s="124">
         <v>1851830746</v>
@@ -16991,7 +17119,7 @@
     </row>
     <row r="41" spans="1:17" ht="11.25" customHeight="1">
       <c r="A41" s="121" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B41" s="124">
         <v>0</v>
@@ -17033,7 +17161,7 @@
     </row>
     <row r="42" spans="1:17" ht="13.5" customHeight="1">
       <c r="A42" s="119" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B42" s="124">
         <v>1851830746</v>
@@ -17348,51 +17476,51 @@
   <sheetData>
     <row r="1" spans="1:16" ht="16.5" customHeight="1">
       <c r="A1" s="118" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B1" s="118" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" s="123" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1" s="123" t="s">
+        <v>187</v>
+      </c>
+      <c r="E1" s="123" t="s">
         <v>188</v>
       </c>
-      <c r="C1" s="123" t="s">
+      <c r="F1" s="123" t="s">
         <v>189</v>
       </c>
-      <c r="D1" s="123" t="s">
+      <c r="G1" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="E1" s="123" t="s">
+      <c r="H1" s="123" t="s">
         <v>191</v>
       </c>
-      <c r="F1" s="123" t="s">
-        <v>192</v>
-      </c>
-      <c r="G1" s="123" t="s">
-        <v>193</v>
-      </c>
-      <c r="H1" s="123" t="s">
-        <v>194</v>
-      </c>
       <c r="I1" s="123" t="s">
+        <v>312</v>
+      </c>
+      <c r="J1" s="123" t="s">
+        <v>313</v>
+      </c>
+      <c r="K1" s="123" t="s">
+        <v>314</v>
+      </c>
+      <c r="L1" s="123" t="s">
+        <v>315</v>
+      </c>
+      <c r="M1" s="123" t="s">
         <v>316</v>
       </c>
-      <c r="J1" s="123" t="s">
+      <c r="N1" s="123" t="s">
         <v>317</v>
-      </c>
-      <c r="K1" s="123" t="s">
-        <v>318</v>
-      </c>
-      <c r="L1" s="123" t="s">
-        <v>319</v>
-      </c>
-      <c r="M1" s="123" t="s">
-        <v>320</v>
-      </c>
-      <c r="N1" s="123" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="13.5" customHeight="1">
       <c r="A2" s="121" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B2" s="124">
         <v>19689650568</v>
@@ -17434,7 +17562,7 @@
     </row>
     <row r="3" spans="1:16" ht="13.5" customHeight="1">
       <c r="A3" s="119" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B3" s="124">
         <v>19576088228</v>
@@ -17476,7 +17604,7 @@
     </row>
     <row r="4" spans="1:16" ht="13.5" customHeight="1">
       <c r="A4" s="119" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B4" s="124">
         <v>113562340</v>
@@ -17518,7 +17646,7 @@
     </row>
     <row r="5" spans="1:16" ht="13.5" customHeight="1">
       <c r="A5" s="121" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B5" s="124">
         <v>16467043458</v>
@@ -17560,7 +17688,7 @@
     </row>
     <row r="6" spans="1:16" ht="13.5" customHeight="1">
       <c r="A6" s="119" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B6" s="124">
         <v>16467043458</v>
@@ -17602,7 +17730,7 @@
     </row>
     <row r="7" spans="1:16" ht="13.5" customHeight="1">
       <c r="A7" s="119" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B7" s="124">
         <v>2098835763</v>
@@ -17644,7 +17772,7 @@
     </row>
     <row r="8" spans="1:16" ht="13.5" customHeight="1">
       <c r="A8" s="119" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B8" s="124">
         <v>16610240340</v>
@@ -17686,7 +17814,7 @@
     </row>
     <row r="9" spans="1:16" ht="13.5" customHeight="1">
       <c r="A9" s="119" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B9" s="124">
         <v>62693149</v>
@@ -17728,7 +17856,7 @@
     </row>
     <row r="10" spans="1:16" ht="13.5" customHeight="1">
       <c r="A10" s="119" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B10" s="124">
         <v>2179339496</v>
@@ -17770,7 +17898,7 @@
     </row>
     <row r="11" spans="1:16" ht="13.5" customHeight="1">
       <c r="A11" s="121" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B11" s="124">
         <v>3222607110</v>
@@ -17812,7 +17940,7 @@
     </row>
     <row r="12" spans="1:16" ht="13.5" customHeight="1">
       <c r="A12" s="121" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B12" s="124">
         <v>1948634682</v>
@@ -17854,7 +17982,7 @@
     </row>
     <row r="13" spans="1:16" ht="13.5" customHeight="1">
       <c r="A13" s="119" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B13" s="124">
         <v>1170857179</v>
@@ -17896,7 +18024,7 @@
     </row>
     <row r="14" spans="1:16" ht="13.5" customHeight="1">
       <c r="A14" s="119" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B14" s="124">
         <v>3419250</v>
@@ -17938,7 +18066,7 @@
     </row>
     <row r="15" spans="1:16" ht="13.5" customHeight="1">
       <c r="A15" s="119" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B15" s="124">
         <v>97328369</v>
@@ -17980,7 +18108,7 @@
     </row>
     <row r="16" spans="1:16" ht="13.5" customHeight="1">
       <c r="A16" s="119" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B16" s="124">
         <v>4245185</v>
@@ -18022,7 +18150,7 @@
     </row>
     <row r="17" spans="1:16" ht="13.5" customHeight="1">
       <c r="A17" s="119" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B17" s="124">
         <v>39117430</v>
@@ -18064,7 +18192,7 @@
     </row>
     <row r="18" spans="1:16" ht="13.5" customHeight="1">
       <c r="A18" s="119" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B18" s="124">
         <v>10964361</v>
@@ -18106,7 +18234,7 @@
     </row>
     <row r="19" spans="1:16" ht="13.5" customHeight="1">
       <c r="A19" s="119" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B19" s="124">
         <v>537830</v>
@@ -18148,7 +18276,7 @@
     </row>
     <row r="20" spans="1:16" ht="13.5" customHeight="1">
       <c r="A20" s="119" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B20" s="124">
         <v>9546653</v>
@@ -18190,7 +18318,7 @@
     </row>
     <row r="21" spans="1:16" ht="13.5" customHeight="1">
       <c r="A21" s="119" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B21" s="124">
         <v>58666660</v>
@@ -18232,7 +18360,7 @@
     </row>
     <row r="22" spans="1:16" ht="13.5" customHeight="1">
       <c r="A22" s="119" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B22" s="124">
         <v>86462149</v>
@@ -18274,7 +18402,7 @@
     </row>
     <row r="23" spans="1:16" ht="13.5" customHeight="1">
       <c r="A23" s="119" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B23" s="124">
         <v>94500000</v>
@@ -18316,7 +18444,7 @@
     </row>
     <row r="24" spans="1:16" ht="13.5" customHeight="1">
       <c r="A24" s="119" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B24" s="124">
         <v>49358485</v>
@@ -18358,7 +18486,7 @@
     </row>
     <row r="25" spans="1:16" ht="13.5" customHeight="1">
       <c r="A25" s="119" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B25" s="124">
         <v>136538142</v>
@@ -18400,7 +18528,7 @@
     </row>
     <row r="26" spans="1:16" ht="13.5" customHeight="1">
       <c r="A26" s="119" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B26" s="124">
         <v>16218767</v>
@@ -18442,7 +18570,7 @@
     </row>
     <row r="27" spans="1:16" ht="13.5" customHeight="1">
       <c r="A27" s="119" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B27" s="124">
         <v>10701551</v>
@@ -18484,7 +18612,7 @@
     </row>
     <row r="28" spans="1:16" ht="13.5" customHeight="1">
       <c r="A28" s="119" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B28" s="124">
         <v>157513549</v>
@@ -18526,7 +18654,7 @@
     </row>
     <row r="29" spans="1:16" ht="13.5" customHeight="1">
       <c r="A29" s="119" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B29" s="124">
         <v>2659122</v>
@@ -18568,7 +18696,7 @@
     </row>
     <row r="30" spans="1:16" ht="13.5" customHeight="1">
       <c r="A30" s="121" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B30" s="124">
         <v>1273972428</v>
@@ -18610,7 +18738,7 @@
     </row>
     <row r="31" spans="1:16" ht="13.5" customHeight="1">
       <c r="A31" s="121" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B31" s="124">
         <v>110853921</v>
@@ -18652,7 +18780,7 @@
     </row>
     <row r="32" spans="1:16" ht="13.5" customHeight="1">
       <c r="A32" s="119" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B32" s="124">
         <v>107412653</v>
@@ -18694,7 +18822,7 @@
     </row>
     <row r="33" spans="1:16" ht="13.5" customHeight="1">
       <c r="A33" s="119" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B33" s="124">
         <v>726273</v>
@@ -18736,7 +18864,7 @@
     </row>
     <row r="34" spans="1:16" ht="13.5" customHeight="1">
       <c r="A34" s="119" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B34" s="124">
         <v>2714995</v>
@@ -18778,7 +18906,7 @@
     </row>
     <row r="35" spans="1:16" ht="13.5" customHeight="1">
       <c r="A35" s="121" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B35" s="124">
         <v>40033270</v>
@@ -18820,7 +18948,7 @@
     </row>
     <row r="36" spans="1:16" ht="13.5" customHeight="1">
       <c r="A36" s="119" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B36" s="124">
         <v>1282550</v>
@@ -18862,7 +18990,7 @@
     </row>
     <row r="37" spans="1:16" ht="13.5" customHeight="1">
       <c r="A37" s="119" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B37" s="124">
         <v>214000</v>
@@ -18904,7 +19032,7 @@
     </row>
     <row r="38" spans="1:16" ht="13.5" customHeight="1">
       <c r="A38" s="119" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B38" s="124">
         <v>38536720</v>
@@ -18946,7 +19074,7 @@
     </row>
     <row r="39" spans="1:16" ht="13.5" customHeight="1">
       <c r="A39" s="121" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B39" s="124">
         <v>1344793079</v>
@@ -18988,7 +19116,7 @@
     </row>
     <row r="40" spans="1:16" ht="13.5" customHeight="1">
       <c r="A40" s="121" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B40" s="124">
         <v>0</v>
@@ -19030,7 +19158,7 @@
     </row>
     <row r="41" spans="1:16" ht="13.5" customHeight="1">
       <c r="A41" s="121" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B41" s="124">
         <v>1344793079</v>
@@ -19254,31 +19382,31 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" customHeight="1">
       <c r="A1" s="159" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B1" s="159" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C1" s="160"/>
       <c r="D1" s="159" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E1" s="160"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" customHeight="1">
       <c r="A2" s="162"/>
       <c r="B2" s="159" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C2" s="160"/>
       <c r="D2" s="159" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E2" s="160"/>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1">
       <c r="A3" s="121" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B3" s="124">
         <v>0</v>
@@ -19303,7 +19431,7 @@
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1">
       <c r="A4" s="119" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B4" s="124">
         <v>21466362478</v>
@@ -19328,7 +19456,7 @@
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
       <c r="A5" s="119" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B5" s="124">
         <v>53602858</v>
@@ -19353,7 +19481,7 @@
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
       <c r="A6" s="121" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B6" s="124">
         <v>0</v>
@@ -19378,7 +19506,7 @@
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1">
       <c r="A7" s="119" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B7" s="124">
         <v>0</v>
@@ -19403,7 +19531,7 @@
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1">
       <c r="A8" s="119" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B8" s="124">
         <v>2126111102</v>
@@ -19428,7 +19556,7 @@
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
       <c r="A9" s="119" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B9" s="124">
         <v>18479894308</v>
@@ -19453,7 +19581,7 @@
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1">
       <c r="A10" s="119" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B10" s="124">
         <v>91576826</v>
@@ -19478,7 +19606,7 @@
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
       <c r="A11" s="119" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B11" s="124">
         <v>2863615436</v>
@@ -19503,7 +19631,7 @@
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1">
       <c r="A12" s="121" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B12" s="124">
         <v>0</v>
@@ -19528,7 +19656,7 @@
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1">
       <c r="A13" s="121" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B13" s="124">
         <v>0</v>
@@ -19553,7 +19681,7 @@
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1">
       <c r="A14" s="119" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B14" s="124">
         <v>1229848831</v>
@@ -19578,7 +19706,7 @@
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1">
       <c r="A15" s="119" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B15" s="124">
         <v>0</v>
@@ -19603,7 +19731,7 @@
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1">
       <c r="A16" s="119" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B16" s="124">
         <v>0</v>
@@ -19628,7 +19756,7 @@
     </row>
     <row r="17" spans="1:7" ht="13.5" customHeight="1">
       <c r="A17" s="119" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B17" s="124">
         <v>88091340</v>
@@ -19653,7 +19781,7 @@
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1">
       <c r="A18" s="119" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B18" s="124">
         <v>110546776</v>
@@ -19678,7 +19806,7 @@
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
       <c r="A19" s="119" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B19" s="124">
         <v>7859988</v>
@@ -19703,7 +19831,7 @@
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
       <c r="A20" s="119" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B20" s="124">
         <v>43323349</v>
@@ -19728,7 +19856,7 @@
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1">
       <c r="A21" s="119" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B21" s="124">
         <v>10884279</v>
@@ -19753,7 +19881,7 @@
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1">
       <c r="A22" s="119" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B22" s="124">
         <v>658900</v>
@@ -19778,7 +19906,7 @@
     </row>
     <row r="23" spans="1:7" ht="13.5" customHeight="1">
       <c r="A23" s="119" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B23" s="124">
         <v>9937528</v>
@@ -19803,7 +19931,7 @@
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1">
       <c r="A24" s="119" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B24" s="124">
         <v>61818760</v>
@@ -19828,7 +19956,7 @@
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1">
       <c r="A25" s="119" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B25" s="124">
         <v>71625807</v>
@@ -19853,7 +19981,7 @@
     </row>
     <row r="26" spans="1:7" ht="13.5" customHeight="1">
       <c r="A26" s="119" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B26" s="124">
         <v>94500000</v>
@@ -19878,7 +20006,7 @@
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
       <c r="A27" s="119" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B27" s="124">
         <v>48751589</v>
@@ -19903,7 +20031,7 @@
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
       <c r="A28" s="119" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B28" s="124">
         <v>155024259</v>
@@ -19928,7 +20056,7 @@
     </row>
     <row r="29" spans="1:7" ht="13.5" customHeight="1">
       <c r="A29" s="119" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B29" s="124">
         <v>11781419</v>
@@ -19953,7 +20081,7 @@
     </row>
     <row r="30" spans="1:7" ht="11.25" customHeight="1">
       <c r="A30" s="119" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B30" s="124">
         <v>18876205</v>
@@ -19978,7 +20106,7 @@
     </row>
     <row r="31" spans="1:7" ht="13.5" customHeight="1">
       <c r="A31" s="119" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B31" s="124">
         <v>196598820</v>
@@ -20003,7 +20131,7 @@
     </row>
     <row r="32" spans="1:7" ht="13.5" customHeight="1">
       <c r="A32" s="119" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B32" s="124">
         <v>0</v>
@@ -20028,7 +20156,7 @@
     </row>
     <row r="33" spans="1:7" ht="13.5" customHeight="1">
       <c r="A33" s="119" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B33" s="124">
         <v>968104</v>
@@ -20053,7 +20181,7 @@
     </row>
     <row r="34" spans="1:7" ht="13.5" customHeight="1">
       <c r="A34" s="119" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B34" s="124">
         <v>0</v>
@@ -20078,7 +20206,7 @@
     </row>
     <row r="35" spans="1:7" ht="13.5" customHeight="1">
       <c r="A35" s="121" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B35" s="124">
         <v>0</v>
@@ -20103,7 +20231,7 @@
     </row>
     <row r="36" spans="1:7" ht="13.5" customHeight="1">
       <c r="A36" s="122" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B36" s="124">
         <v>113934601</v>
@@ -20128,7 +20256,7 @@
     </row>
     <row r="37" spans="1:7" ht="13.5" customHeight="1">
       <c r="A37" s="119" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B37" s="124">
         <v>9493467</v>
@@ -20153,7 +20281,7 @@
     </row>
     <row r="38" spans="1:7" ht="13.5" customHeight="1">
       <c r="A38" s="119" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B38" s="124">
         <v>7089909</v>
@@ -20178,7 +20306,7 @@
     </row>
     <row r="39" spans="1:7" ht="11.25" customHeight="1">
       <c r="A39" s="119" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B39" s="124">
         <v>14571940</v>
@@ -20203,7 +20331,7 @@
     </row>
     <row r="40" spans="1:7" ht="13.5" customHeight="1">
       <c r="A40" s="119" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B40" s="124">
         <v>0</v>
@@ -20228,7 +20356,7 @@
     </row>
     <row r="41" spans="1:7" ht="11.25" customHeight="1">
       <c r="A41" s="119" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B41" s="124">
         <v>1131469</v>
@@ -20253,7 +20381,7 @@
     </row>
     <row r="42" spans="1:7" ht="11.25" customHeight="1">
       <c r="A42" s="119" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B42" s="124">
         <v>0</v>
@@ -20278,7 +20406,7 @@
     </row>
     <row r="43" spans="1:7" ht="13.5" customHeight="1">
       <c r="A43" s="119" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B43" s="124">
         <v>2000</v>
@@ -20303,7 +20431,7 @@
     </row>
     <row r="44" spans="1:7" ht="13.5" customHeight="1">
       <c r="A44" s="122" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B44" s="124">
         <v>181936</v>
@@ -20328,7 +20456,7 @@
     </row>
     <row r="45" spans="1:7" ht="11.25" customHeight="1">
       <c r="A45" s="119" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B45" s="124">
         <v>0</v>
@@ -20353,7 +20481,7 @@
     </row>
     <row r="46" spans="1:7" ht="13.5" customHeight="1">
       <c r="A46" s="119" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B46" s="124">
         <v>0</v>
@@ -20378,7 +20506,7 @@
     </row>
     <row r="47" spans="1:7" ht="13.5" customHeight="1">
       <c r="A47" s="119" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B47" s="124">
         <v>0</v>
@@ -20403,7 +20531,7 @@
     </row>
     <row r="48" spans="1:7" ht="11.25" customHeight="1">
       <c r="A48" s="119" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B48" s="124">
         <v>0</v>

--- a/monthly_closing_template.xlsx
+++ b/monthly_closing_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\창현관리부\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAADDAC-EA27-4C71-BD9A-32D87E14E000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CC9670-BE69-4A46-BC92-F0DBAD23109E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="인덱스" sheetId="1" r:id="rId1"/>
@@ -4461,13 +4461,13 @@
       <c r="A41" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="58" t="e">
-        <f>SUM(B29:B40)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C41" s="59" t="e">
-        <f>SUM(C29:C40)</f>
-        <v>#N/A</v>
+      <c r="B41" s="58">
+        <f>_xlfn.AGGREGATE(9,6,B29:B40)</f>
+        <v>21519965336</v>
+      </c>
+      <c r="C41" s="59">
+        <f>_xlfn.AGGREGATE(9,6,C29:C40)</f>
+        <v>1708056234</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="3.75" customHeight="1"/>

--- a/monthly_closing_template.xlsx
+++ b/monthly_closing_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\창현관리부\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CC9670-BE69-4A46-BC92-F0DBAD23109E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F09BE58-ADDB-4C6E-8BDF-1BCA0F828D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="인덱스" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="317">
   <si>
     <t>결산기준일</t>
   </si>
@@ -73,9 +73,6 @@
     <t>I N D E X</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>NO</t>
   </si>
   <si>
@@ -184,7 +181,7 @@
     <t>총계</t>
   </si>
   <si>
-    <t>특이사항 : 전년동기(1~5월) 영업외비용에 법인세추납액 3,100만원 포함(업무용승용차 비용 불인정 법인세 납부액)</t>
+    <t>특이사항 : 전년동기(1~7월) 영업외비용에 법인세추납액 3,800만원 포함(업무용승용차 비용 불인정 법인세 납부액)</t>
   </si>
   <si>
     <t>재 무 상 태 표</t>
@@ -256,7 +253,7 @@
     <t xml:space="preserve">      미   수    수   익</t>
   </si>
   <si>
-    <t>단기채권</t>
+    <t>단기채권외</t>
   </si>
   <si>
     <t xml:space="preserve">      미      수      금</t>
@@ -379,7 +376,7 @@
     <t xml:space="preserve">      가      수      금</t>
   </si>
   <si>
-    <t>한국엡손외</t>
+    <t>한국엡손외(연말 결산시 반영)</t>
   </si>
   <si>
     <t xml:space="preserve">      선      수      금</t>
@@ -646,7 +643,7 @@
     <t>증감                (전월대비)</t>
   </si>
   <si>
-    <t>5월: 총36명, 6월: 총36명</t>
+    <t>6월: 총36명, 7월: 총36명</t>
   </si>
   <si>
     <t>6월:상반기 퇴직연금 불입</t>
@@ -691,7 +688,7 @@
     <t>전지사 소모품비</t>
   </si>
   <si>
-    <t>카드수수료, 차량렌트료(7대), 기타외</t>
+    <t>카드수수료, 차량렌트료(6대), 기타외</t>
   </si>
   <si>
     <t>대손금 충당액</t>
@@ -703,7 +700,7 @@
     <t>단기금융상품 이자수익</t>
   </si>
   <si>
-    <t>단기대여금이자(윤인희)</t>
+    <t>단기대여금이자(윤인희)외</t>
   </si>
   <si>
     <t>16,824,297,117</t>
@@ -997,25 +994,25 @@
     <t>17,096,058,114</t>
   </si>
   <si>
+    <t>7월</t>
+  </si>
+  <si>
+    <t>8월</t>
+  </si>
+  <si>
+    <t>9월</t>
+  </si>
+  <si>
+    <t>10월</t>
+  </si>
+  <si>
+    <t>11월</t>
+  </si>
+  <si>
+    <t>12월</t>
+  </si>
+  <si>
     <t xml:space="preserve">      유형자산 처분 이익</t>
-  </si>
-  <si>
-    <t>7월</t>
-  </si>
-  <si>
-    <t>8월</t>
-  </si>
-  <si>
-    <t>9월</t>
-  </si>
-  <si>
-    <t>10월</t>
-  </si>
-  <si>
-    <t>11월</t>
-  </si>
-  <si>
-    <t>12월</t>
   </si>
 </sst>
 </file>
@@ -2184,23 +2181,26 @@
     <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2212,12 +2212,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2236,6 +2230,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2699,7 +2696,7 @@
             <c:strRef>
               <c:f>요약!$A$29:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1월</c:v>
                 </c:pt>
@@ -2721,21 +2718,6 @@
                 <c:pt idx="6">
                   <c:v>7월</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>8월</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9월</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10월</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11월</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12월</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
@@ -2744,7 +2726,7 @@
               <c:f>요약!$B$29:$B$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0,;\(#,##0,\);\-</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>2735381647</c:v>
                 </c:pt>
@@ -2766,27 +2748,12 @@
                 <c:pt idx="6">
                   <c:v>2306642756</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>#N/A</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E39C-47A0-955D-57FD98B10595}"/>
+              <c16:uniqueId val="{00000000-4179-492B-AD31-098DE0AF0B1C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2896,7 +2863,7 @@
             <c:strRef>
               <c:f>요약!$A$29:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1월</c:v>
                 </c:pt>
@@ -2918,21 +2885,6 @@
                 <c:pt idx="6">
                   <c:v>7월</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>8월</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9월</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10월</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11월</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12월</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
@@ -2941,7 +2893,7 @@
               <c:f>요약!$C$29:$C$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0,;\(#,##0,\);\-</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>201922246</c:v>
                 </c:pt>
@@ -2963,28 +2915,13 @@
                 <c:pt idx="6">
                   <c:v>166909868</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>#N/A</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E39C-47A0-955D-57FD98B10595}"/>
+              <c16:uniqueId val="{00000001-4179-492B-AD31-098DE0AF0B1C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3471,17 +3408,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1">
-      <c r="A1" s="126" t="str">
+      <c r="A1" s="134" t="str">
         <f>TEXT($K$1,"yyyy")&amp;"년 1월~"&amp;MONTH($K$1)&amp;"월 월차 결산서 [ ㈜ 창현 ]"</f>
         <v>2026년 1월~7월 월차 결산서 [ ㈜ 창현 ]</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
       <c r="J1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3499,179 +3436,175 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A3" s="136" t="s">
+      <c r="A3" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-    </row>
-    <row r="4" spans="1:13" ht="34.5" customHeight="1">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+    </row>
+    <row r="4" spans="1:13" ht="34.5" customHeight="1"/>
     <row r="5" spans="1:13" ht="40.5" customHeight="1">
       <c r="A5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="136" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="128" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="129"/>
-      <c r="D5" s="129"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="129"/>
-      <c r="H5" s="130"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="131"/>
+      <c r="E5" s="131"/>
+      <c r="F5" s="131"/>
+      <c r="G5" s="131"/>
+      <c r="H5" s="132"/>
     </row>
     <row r="6" spans="1:13" ht="43.5" customHeight="1">
       <c r="A6" s="8">
         <v>1</v>
       </c>
-      <c r="B6" s="140" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="129"/>
-      <c r="D6" s="129"/>
-      <c r="E6" s="129"/>
-      <c r="F6" s="129"/>
-      <c r="G6" s="129"/>
-      <c r="H6" s="130"/>
+      <c r="B6" s="133" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="131"/>
+      <c r="D6" s="131"/>
+      <c r="E6" s="131"/>
+      <c r="F6" s="131"/>
+      <c r="G6" s="131"/>
+      <c r="H6" s="132"/>
     </row>
     <row r="7" spans="1:13" ht="43.5" customHeight="1">
       <c r="A7" s="9">
         <v>2</v>
       </c>
-      <c r="B7" s="135" t="str">
+      <c r="B7" s="130" t="str">
         <f>"재무상태표 ["&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 현재]"</f>
         <v>재무상태표 [2026년07월31일 현재]</v>
       </c>
-      <c r="C7" s="129"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="130"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="132"/>
     </row>
     <row r="8" spans="1:13" ht="43.5" customHeight="1">
       <c r="A8" s="8">
         <v>3</v>
       </c>
-      <c r="B8" s="140" t="str">
+      <c r="B8" s="133" t="str">
         <f>"손익계산서(매출액대비 비율분석) ["&amp;TEXT(DATE(YEAR($K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR($K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR($K$1),1,1)),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
         <v>손익계산서(매출액대비 비율분석) [2026년01월01일 부터 2026년07월31일 까지]</v>
       </c>
-      <c r="C8" s="129"/>
-      <c r="D8" s="129"/>
-      <c r="E8" s="129"/>
-      <c r="F8" s="129"/>
-      <c r="G8" s="129"/>
-      <c r="H8" s="130"/>
+      <c r="C8" s="131"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
+      <c r="G8" s="131"/>
+      <c r="H8" s="132"/>
     </row>
     <row r="9" spans="1:13" ht="43.5" customHeight="1">
       <c r="A9" s="9">
         <v>4</v>
       </c>
-      <c r="B9" s="135" t="str">
+      <c r="B9" s="130" t="str">
         <f>"손익계산서(전월대비 증감) ["&amp;TEXT(EOMONTH($K$1,-2)+1,"yyyy")&amp;"년"&amp;TEXT(MONTH(EOMONTH($K$1,-2)+1),"00")&amp;"월"&amp;TEXT(DAY(EOMONTH($K$1,-2)+1),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
         <v>손익계산서(전월대비 증감) [2026년06월01일 부터 2026년07월31일 까지]</v>
       </c>
-      <c r="C9" s="129"/>
-      <c r="D9" s="129"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="129"/>
-      <c r="G9" s="129"/>
-      <c r="H9" s="130"/>
+      <c r="C9" s="131"/>
+      <c r="D9" s="131"/>
+      <c r="E9" s="131"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="132"/>
     </row>
     <row r="10" spans="1:13" ht="43.5" customHeight="1">
       <c r="A10" s="8">
         <v>5</v>
       </c>
-      <c r="B10" s="137" t="str">
+      <c r="B10" s="138" t="str">
         <f>"기간별손익계산서 ["&amp;TEXT(DATE(YEAR($K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR($K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR($K$1),1,1)),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
         <v>기간별손익계산서 [2026년01월01일 부터 2026년07월31일 까지]</v>
       </c>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="129"/>
-      <c r="H10" s="130"/>
+      <c r="C10" s="131"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="131"/>
+      <c r="F10" s="131"/>
+      <c r="G10" s="131"/>
+      <c r="H10" s="132"/>
     </row>
     <row r="11" spans="1:13" ht="43.5" customHeight="1">
       <c r="A11" s="9">
         <v>6</v>
       </c>
-      <c r="B11" s="138" t="str">
+      <c r="B11" s="139" t="str">
         <f>TEXT($K$1,"yyyy")&amp;"년 차량별 비용현황[연간누계/월별/당월상세]"</f>
         <v>2026년 차량별 비용현황[연간누계/월별/당월상세]</v>
       </c>
-      <c r="C11" s="129"/>
-      <c r="D11" s="129"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="130"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="132"/>
     </row>
     <row r="12" spans="1:13" ht="43.5" customHeight="1">
       <c r="A12" s="8">
         <v>7</v>
       </c>
-      <c r="B12" s="137" t="str">
+      <c r="B12" s="138" t="str">
         <f>TEXT($K$1,"yyyy")&amp;"년 운송비 개인별 비용"</f>
         <v>2026년 운송비 개인별 비용</v>
       </c>
-      <c r="C12" s="129"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="130"/>
+      <c r="C12" s="131"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="131"/>
+      <c r="F12" s="131"/>
+      <c r="G12" s="131"/>
+      <c r="H12" s="132"/>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1"/>
     <row r="14" spans="1:13" ht="32.25" customHeight="1"/>
     <row r="15" spans="1:13" ht="9.75" customHeight="1">
-      <c r="D15" s="139" t="s">
+      <c r="D15" s="140" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="126" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="133" t="s">
+      <c r="F15" s="126" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="133" t="s">
+      <c r="G15" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="G15" s="133" t="s">
+      <c r="H15" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="H15" s="133" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="16" spans="1:13" ht="27.75" customHeight="1">
-      <c r="D16" s="132"/>
-      <c r="E16" s="134"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="134"/>
-      <c r="H16" s="134"/>
+      <c r="D16" s="129"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="127"/>
+      <c r="G16" s="127"/>
+      <c r="H16" s="127"/>
     </row>
     <row r="17" spans="4:8" ht="21" customHeight="1">
-      <c r="D17" s="132"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="131"/>
-      <c r="G17" s="131"/>
-      <c r="H17" s="131"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="128"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="128"/>
+      <c r="H17" s="128"/>
     </row>
     <row r="18" spans="4:8" ht="21" customHeight="1">
-      <c r="D18" s="132"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="132"/>
-      <c r="G18" s="132"/>
-      <c r="H18" s="132"/>
+      <c r="D18" s="129"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="129"/>
+      <c r="G18" s="129"/>
+      <c r="H18" s="129"/>
     </row>
     <row r="19" spans="4:8" ht="15" customHeight="1">
       <c r="D19" s="10"/>
@@ -3682,9 +3615,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B6:H6"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="H17:H18"/>
@@ -3701,6 +3631,9 @@
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B6:H6"/>
   </mergeCells>
   <phoneticPr fontId="41" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -3728,55 +3661,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A1" s="141" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
+      <c r="A1" s="148" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
     </row>
     <row r="2" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A2" s="147" t="str">
+      <c r="A2" s="146" t="str">
         <f>TEXT(인덱스!$K$1,"yyyy")&amp;"년 1월 ~ "&amp;MONTH(인덱스!$K$1)&amp;"월 누적 기준 ( 기준일 : "&amp;TEXT(인덱스!$K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH(인덱스!$K$1),"00")&amp;"월"&amp;TEXT(DAY(인덱스!$K$1),"00")&amp;"일 )"</f>
         <v>2026년 1월 ~ 7월 누적 기준 ( 기준일 : 2026년07월31일 )</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
     </row>
     <row r="3" spans="1:8" ht="18.75" customHeight="1"/>
     <row r="4" spans="1:8" ht="15" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A5" s="142" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="148" t="str">
+      <c r="A5" s="141" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="147" t="str">
         <f>"전년동기 대비 ("&amp;(YEAR(인덱스!$K$1)-1)&amp;"년 1~"&amp;MONTH(인덱스!$K$1)&amp;"월)"</f>
         <v>전년동기 대비 (2025년 1~7월)</v>
       </c>
-      <c r="C5" s="145"/>
-      <c r="D5" s="145"/>
-      <c r="E5" s="146"/>
-      <c r="F5" s="144" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="145"/>
-      <c r="H5" s="146"/>
+      <c r="C5" s="144"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="143" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="144"/>
+      <c r="H5" s="145"/>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1">
-      <c r="A6" s="134"/>
+      <c r="A6" s="127"/>
       <c r="B6" s="12" t="str">
         <f>"당기(1~"&amp;MONTH(인덱스!$K$1)&amp;"월)"</f>
         <v>당기(1~7월)</v>
@@ -3786,24 +3719,24 @@
         <v>전년동기(1~7월)</v>
       </c>
       <c r="D6" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="F6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>17</v>
-      </c>
       <c r="G6" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="15" t="s">
         <v>15</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1">
       <c r="A7" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="18">
         <f>'매출액대비 비율분석'!C9</f>
@@ -3836,7 +3769,7 @@
     </row>
     <row r="8" spans="1:8" ht="16.5" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="22">
         <f>'매출액대비 비율분석'!C12</f>
@@ -3869,7 +3802,7 @@
     </row>
     <row r="9" spans="1:8" ht="16.5" customHeight="1">
       <c r="A9" s="25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="26">
         <f>'매출액대비 비율분석'!C18</f>
@@ -3902,7 +3835,7 @@
     </row>
     <row r="10" spans="1:8" ht="16.5" customHeight="1">
       <c r="A10" s="21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="22">
         <f>'매출액대비 비율분석'!C19</f>
@@ -3935,7 +3868,7 @@
     </row>
     <row r="11" spans="1:8" ht="16.5" customHeight="1">
       <c r="A11" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="26">
         <f>'매출액대비 비율분석'!C41</f>
@@ -3968,7 +3901,7 @@
     </row>
     <row r="12" spans="1:8" ht="16.5" customHeight="1">
       <c r="A12" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="22">
         <f>'매출액대비 비율분석'!C42</f>
@@ -4001,7 +3934,7 @@
     </row>
     <row r="13" spans="1:8" ht="16.5" customHeight="1">
       <c r="A13" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="22">
         <f>'매출액대비 비율분석'!C50</f>
@@ -4034,7 +3967,7 @@
     </row>
     <row r="14" spans="1:8" ht="16.5" customHeight="1">
       <c r="A14" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="26">
         <f>'매출액대비 비율분석'!C58</f>
@@ -4067,7 +4000,7 @@
     </row>
     <row r="15" spans="1:8" ht="16.5" customHeight="1">
       <c r="A15" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="22">
         <f>'매출액대비 비율분석'!C59</f>
@@ -4100,7 +4033,7 @@
     </row>
     <row r="16" spans="1:8" ht="16.5" customHeight="1">
       <c r="A16" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="26">
         <f>'매출액대비 비율분석'!C61</f>
@@ -4133,7 +4066,7 @@
     </row>
     <row r="17" spans="1:8" ht="16.5" customHeight="1">
       <c r="A17" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" s="30">
         <f>IFERROR(B11/B7,"")</f>
@@ -4154,7 +4087,7 @@
     </row>
     <row r="18" spans="1:8" ht="16.5" customHeight="1">
       <c r="A18" s="34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" s="35">
         <f>IFERROR(B16/B7,"")</f>
@@ -4175,29 +4108,29 @@
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="30" customHeight="1">
       <c r="A21" s="39" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B21" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="41" t="s">
-        <v>32</v>
-      </c>
       <c r="D21" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="41" t="s">
         <v>15</v>
-      </c>
-      <c r="E21" s="41" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.5" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="18">
         <f>('재무상태표(내역)'!C50)+0</f>
@@ -4218,7 +4151,7 @@
     </row>
     <row r="23" spans="1:8" ht="16.5" customHeight="1">
       <c r="A23" s="46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="26">
         <f>('재무상태표(내역)'!C65)+0</f>
@@ -4239,7 +4172,7 @@
     </row>
     <row r="24" spans="1:8" ht="16.5" customHeight="1">
       <c r="A24" s="46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="26">
         <f>('재무상태표(내역)'!C79)+0</f>
@@ -4260,7 +4193,7 @@
     </row>
     <row r="25" spans="1:8" ht="16.5" customHeight="1">
       <c r="A25" s="49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" s="35">
         <f>IFERROR(B23/B24,"")</f>
@@ -4275,18 +4208,18 @@
     </row>
     <row r="27" spans="1:8" ht="18.75" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="30" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" s="41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
@@ -4387,7 +4320,7 @@
         <v>166909868</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1">
+    <row r="36" spans="1:3" ht="15" hidden="1" customHeight="1">
       <c r="A36" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),8,1))&amp;"월","")</f>
         <v>8월</v>
@@ -4401,7 +4334,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1">
+    <row r="37" spans="1:3" ht="15" hidden="1" customHeight="1">
       <c r="A37" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),9,1))&amp;"월","")</f>
         <v>9월</v>
@@ -4415,7 +4348,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15" customHeight="1">
+    <row r="38" spans="1:3" ht="15" hidden="1" customHeight="1">
       <c r="A38" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),10,1))&amp;"월","")</f>
         <v>10월</v>
@@ -4429,7 +4362,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1">
+    <row r="39" spans="1:3" ht="15" hidden="1" customHeight="1">
       <c r="A39" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),11,1))&amp;"월","")</f>
         <v>11월</v>
@@ -4443,7 +4376,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15" customHeight="1">
+    <row r="40" spans="1:3" ht="15" hidden="1" customHeight="1">
       <c r="A40" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),12,1))&amp;"월","")</f>
         <v>12월</v>
@@ -4459,7 +4392,7 @@
     </row>
     <row r="41" spans="1:3" ht="16.5" customHeight="1">
       <c r="A41" s="57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="58">
         <f>_xlfn.AGGREGATE(9,6,B29:B40)</f>
@@ -4473,16 +4406,16 @@
     <row r="67" spans="1:8" ht="3.75" customHeight="1"/>
     <row r="68" spans="1:8" ht="27.75" customHeight="1"/>
     <row r="69" spans="1:8" ht="60" customHeight="1">
-      <c r="A69" s="143" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="127"/>
-      <c r="C69" s="127"/>
-      <c r="D69" s="127"/>
-      <c r="E69" s="127"/>
-      <c r="F69" s="127"/>
-      <c r="G69" s="127"/>
-      <c r="H69" s="127"/>
+      <c r="A69" s="142" t="s">
+        <v>39</v>
+      </c>
+      <c r="B69" s="135"/>
+      <c r="C69" s="135"/>
+      <c r="D69" s="135"/>
+      <c r="E69" s="135"/>
+      <c r="F69" s="135"/>
+      <c r="G69" s="135"/>
+      <c r="H69" s="135"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4519,7 +4452,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="1.1812499999999999" bottom="0.98402777777777795" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="64" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="68" orientation="portrait" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -4547,14 +4480,14 @@
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" customHeight="1">
       <c r="A1" s="149" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
+        <v>40</v>
+      </c>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
       <c r="H1" s="60"/>
     </row>
     <row r="2" spans="1:11" ht="10.5" customHeight="1">
@@ -4576,12 +4509,12 @@
         <f>"(당기) "&amp;TEXT(DATE(YEAR(인덱스!$K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR(인덱스!$K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR(인덱스!$K$1),1,1)),"00")&amp;"일"&amp;" - "&amp;TEXT(인덱스!$K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH(인덱스!$K$1),"00")&amp;"월"&amp;TEXT(DAY(인덱스!$K$1),"00")&amp;"일"</f>
         <v>(당기) 2026년01월01일 - 2026년07월31일</v>
       </c>
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
       <c r="H3" s="5"/>
       <c r="I3" s="62" t="str">
         <f>IF(ROUND(F50,0)=ROUND(F80,0),"대차검증(전기): 일치","대차검증(전기): 불일치 ⚠")</f>
@@ -4593,64 +4526,64 @@
         <f>"(전기) "&amp;TEXT(DATE(YEAR(인덱스!$K$1)-1,1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR(인덱스!$K$1)-1,1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR(인덱스!$K$1)-1,1,1)),"00")&amp;"일"&amp;" - "&amp;TEXT(DATE(YEAR(인덱스!$K$1)-1,12,31),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR(인덱스!$K$1)-1,12,31)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR(인덱스!$K$1)-1,12,31)),"00")&amp;"일"</f>
         <v>(전기) 2025년01월01일 - 2025년12월31일</v>
       </c>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
       <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" customHeight="1"/>
     <row r="6" spans="1:11" ht="11.25" customHeight="1">
       <c r="A6" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="64" t="s">
         <v>42</v>
-      </c>
-      <c r="G6" s="64" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18.75" customHeight="1">
       <c r="A7" s="150" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="150" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="150" t="s">
+      <c r="C7" s="132"/>
+      <c r="D7" s="150" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="130"/>
-      <c r="D7" s="150" t="s">
+      <c r="E7" s="150" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="150" t="s">
+      <c r="F7" s="132"/>
+      <c r="G7" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="130"/>
-      <c r="G7" s="150" t="s">
+      <c r="J7" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="66" t="s">
-        <v>49</v>
-      </c>
       <c r="K7" s="66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="18.75" customHeight="1">
       <c r="A8" s="152"/>
       <c r="B8" s="150" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="130"/>
+        <v>49</v>
+      </c>
+      <c r="C8" s="132"/>
       <c r="D8" s="152"/>
       <c r="E8" s="150" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="130"/>
+        <v>50</v>
+      </c>
+      <c r="F8" s="132"/>
       <c r="G8" s="152"/>
     </row>
     <row r="9" spans="1:11" ht="17.25" customHeight="1">
       <c r="A9" s="67" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" s="68"/>
       <c r="C9" s="68"/>
@@ -4677,7 +4610,7 @@
     </row>
     <row r="10" spans="1:11" ht="17.25" customHeight="1">
       <c r="A10" s="74" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I10,재무상태표!$G:$G,0)),0)</f>
@@ -4719,7 +4652,7 @@
     </row>
     <row r="11" spans="1:11" ht="17.25" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I11,재무상태표!$G:$G,0)),0)</f>
@@ -4761,7 +4694,7 @@
     </row>
     <row r="12" spans="1:11" ht="17.25" customHeight="1">
       <c r="A12" s="67" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I12,재무상태표!$G:$G,0)),0)</f>
@@ -4803,7 +4736,7 @@
     </row>
     <row r="13" spans="1:11" ht="17.25" customHeight="1">
       <c r="A13" s="67" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I13,재무상태표!$G:$G,0)),0)</f>
@@ -4845,7 +4778,7 @@
     </row>
     <row r="14" spans="1:11" ht="17.25" customHeight="1">
       <c r="A14" s="67" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B14" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I14,재무상태표!$G:$G,0)),0)</f>
@@ -4887,7 +4820,7 @@
     </row>
     <row r="15" spans="1:11" ht="17.25" customHeight="1">
       <c r="A15" s="67" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B15" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I15,재무상태표!$G:$G,0)),0)</f>
@@ -4929,7 +4862,7 @@
     </row>
     <row r="16" spans="1:11" ht="17.25" customHeight="1">
       <c r="A16" s="67" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I16,재무상태표!$G:$G,0)),0)</f>
@@ -4971,7 +4904,7 @@
     </row>
     <row r="17" spans="1:11" ht="17.25" customHeight="1">
       <c r="A17" s="67" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B17" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I17,재무상태표!$G:$G,0)),0)</f>
@@ -5013,7 +4946,7 @@
     </row>
     <row r="18" spans="1:11" ht="17.25" customHeight="1">
       <c r="A18" s="67" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I18,재무상태표!$G:$G,0)),0)</f>
@@ -5055,7 +4988,7 @@
     </row>
     <row r="19" spans="1:11" ht="17.25" customHeight="1">
       <c r="A19" s="67" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I19,재무상태표!$G:$G,0)),0)</f>
@@ -5097,7 +5030,7 @@
     </row>
     <row r="20" spans="1:11" ht="17.25" customHeight="1">
       <c r="A20" s="67" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B20" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I20,재무상태표!$G:$G,0)),0)</f>
@@ -5139,7 +5072,7 @@
     </row>
     <row r="21" spans="1:11" ht="17.25" customHeight="1">
       <c r="A21" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B21" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I21,재무상태표!$G:$G,0)),0)</f>
@@ -5150,7 +5083,7 @@
         <v>15,136,465</v>
       </c>
       <c r="D21" s="85" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E21" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I21,재무상태표!$G:$G,0)),0)</f>
@@ -5183,7 +5116,7 @@
     </row>
     <row r="22" spans="1:11" ht="21.75" customHeight="1">
       <c r="A22" s="67" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B22" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I22,재무상태표!$G:$G,0)),0)</f>
@@ -5194,7 +5127,7 @@
         <v>253,437,222</v>
       </c>
       <c r="D22" s="85" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E22" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I22,재무상태표!$G:$G,0)),0)</f>
@@ -5227,7 +5160,7 @@
     </row>
     <row r="23" spans="1:11" ht="24.75" customHeight="1">
       <c r="A23" s="67" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B23" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I23,재무상태표!$G:$G,0)),0)</f>
@@ -5238,7 +5171,7 @@
         <v>1,000,000</v>
       </c>
       <c r="D23" s="85" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E23" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I23,재무상태표!$G:$G,0)),0)</f>
@@ -5271,7 +5204,7 @@
     </row>
     <row r="24" spans="1:11" ht="17.25" customHeight="1">
       <c r="A24" s="67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I24,재무상태표!$G:$G,0)),0)</f>
@@ -5282,7 +5215,7 @@
         <v>4,048,315</v>
       </c>
       <c r="D24" s="84" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E24" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I24,재무상태표!$G:$G,0)),0)</f>
@@ -5315,7 +5248,7 @@
     </row>
     <row r="25" spans="1:11" ht="17.25" customHeight="1">
       <c r="A25" s="67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B25" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I25,재무상태표!$G:$G,0)),0)</f>
@@ -5326,7 +5259,7 @@
         <v>900,032,000</v>
       </c>
       <c r="D25" s="85" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E25" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I25,재무상태표!$G:$G,0)),0)</f>
@@ -5359,7 +5292,7 @@
     </row>
     <row r="26" spans="1:11" ht="17.25" customHeight="1">
       <c r="A26" s="67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B26" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I26,재무상태표!$G:$G,0)),0)</f>
@@ -5401,7 +5334,7 @@
     </row>
     <row r="27" spans="1:11" ht="17.25" customHeight="1">
       <c r="A27" s="67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I27,재무상태표!$G:$G,0)),0)</f>
@@ -5412,7 +5345,7 @@
         <v>17,540,440</v>
       </c>
       <c r="D27" s="86" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E27" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I27,재무상태표!$G:$G,0)),0)</f>
@@ -5445,7 +5378,7 @@
     </row>
     <row r="28" spans="1:11" ht="17.25" customHeight="1">
       <c r="A28" s="82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B28" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I28,재무상태표!$G:$G,0)),0)</f>
@@ -5487,7 +5420,7 @@
     </row>
     <row r="29" spans="1:11" ht="17.25" customHeight="1">
       <c r="A29" s="67" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B29" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I29,재무상태표!$G:$G,0)),0)</f>
@@ -5529,7 +5462,7 @@
     </row>
     <row r="30" spans="1:11" ht="17.25" customHeight="1">
       <c r="A30" s="74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B30" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I30,재무상태표!$G:$G,0)),0)</f>
@@ -5571,7 +5504,7 @@
     </row>
     <row r="31" spans="1:11" ht="17.25" customHeight="1">
       <c r="A31" s="82" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B31" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I31,재무상태표!$G:$G,0)),0)</f>
@@ -5613,7 +5546,7 @@
     </row>
     <row r="32" spans="1:11" ht="17.25" customHeight="1">
       <c r="A32" s="67" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B32" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I32,재무상태표!$G:$G,0)),0)</f>
@@ -5655,7 +5588,7 @@
     </row>
     <row r="33" spans="1:11" ht="17.25" customHeight="1">
       <c r="A33" s="82" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B33" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I33,재무상태표!$G:$G,0)),0)</f>
@@ -5697,7 +5630,7 @@
     </row>
     <row r="34" spans="1:11" ht="17.25" customHeight="1">
       <c r="A34" s="67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B34" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I34,재무상태표!$G:$G,0)),0)</f>
@@ -5739,7 +5672,7 @@
     </row>
     <row r="35" spans="1:11" ht="17.25" customHeight="1">
       <c r="A35" s="67" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B35" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I35,재무상태표!$G:$G,0)),0)</f>
@@ -5781,7 +5714,7 @@
     </row>
     <row r="36" spans="1:11" ht="17.25" customHeight="1">
       <c r="A36" s="67" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B36" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I36,재무상태표!$G:$G,0)),0)</f>
@@ -5823,7 +5756,7 @@
     </row>
     <row r="37" spans="1:11" ht="17.25" customHeight="1">
       <c r="A37" s="67" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B37" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I37,재무상태표!$G:$G,0)),0)</f>
@@ -5865,7 +5798,7 @@
     </row>
     <row r="38" spans="1:11" ht="17.25" customHeight="1">
       <c r="A38" s="67" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B38" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I38,재무상태표!$G:$G,0)),0)</f>
@@ -5907,7 +5840,7 @@
     </row>
     <row r="39" spans="1:11" ht="17.25" customHeight="1">
       <c r="A39" s="67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B39" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I39,재무상태표!$G:$G,0)),0)</f>
@@ -5949,7 +5882,7 @@
     </row>
     <row r="40" spans="1:11" ht="17.25" customHeight="1">
       <c r="A40" s="67" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B40" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I40,재무상태표!$G:$G,0)),0)</f>
@@ -5991,7 +5924,7 @@
     </row>
     <row r="41" spans="1:11" ht="17.25" customHeight="1">
       <c r="A41" s="67" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B41" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I41,재무상태표!$G:$G,0)),0)</f>
@@ -6033,7 +5966,7 @@
     </row>
     <row r="42" spans="1:11" ht="17.25" customHeight="1">
       <c r="A42" s="67" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B42" s="83" t="str">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I42,재무상태표!$G:$G,0)),0)</f>
@@ -6075,7 +6008,7 @@
     </row>
     <row r="43" spans="1:11" ht="17.25" customHeight="1">
       <c r="A43" s="82" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B43" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I43,재무상태표!$G:$G,0)),0)</f>
@@ -6117,7 +6050,7 @@
     </row>
     <row r="44" spans="1:11" ht="17.25" customHeight="1">
       <c r="A44" s="82" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B44" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I44,재무상태표!$G:$G,0)),0)</f>
@@ -6159,7 +6092,7 @@
     </row>
     <row r="45" spans="1:11" ht="21.75" customHeight="1">
       <c r="A45" s="67" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B45" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I45,재무상태표!$G:$G,0)),0)</f>
@@ -6201,7 +6134,7 @@
     </row>
     <row r="46" spans="1:11" ht="21.75" customHeight="1">
       <c r="A46" s="67" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B46" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I46,재무상태표!$G:$G,0)),0)</f>
@@ -6243,7 +6176,7 @@
     </row>
     <row r="47" spans="1:11" ht="25.5" customHeight="1">
       <c r="A47" s="67" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B47" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I47,재무상태표!$G:$G,0)),0)</f>
@@ -6254,7 +6187,7 @@
         <v>140,000,000</v>
       </c>
       <c r="D47" s="85" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E47" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I47,재무상태표!$G:$G,0)),0)</f>
@@ -6287,7 +6220,7 @@
     </row>
     <row r="48" spans="1:11" ht="21.75" customHeight="1">
       <c r="A48" s="67" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B48" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I48,재무상태표!$G:$G,0)),0)</f>
@@ -6298,7 +6231,7 @@
         <v>528,095,860</v>
       </c>
       <c r="D48" s="85" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E48" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I48,재무상태표!$G:$G,0)),0)</f>
@@ -6331,7 +6264,7 @@
     </row>
     <row r="49" spans="1:11" ht="21.75" customHeight="1">
       <c r="A49" s="67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B49" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I49,재무상태표!$G:$G,0)),0)</f>
@@ -6373,7 +6306,7 @@
     </row>
     <row r="50" spans="1:11" ht="21.75" customHeight="1">
       <c r="A50" s="88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B50" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I50,재무상태표!$G:$G,0)),0)</f>
@@ -6415,7 +6348,7 @@
     </row>
     <row r="51" spans="1:11" ht="21.75" customHeight="1">
       <c r="A51" s="67" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B51" s="68"/>
       <c r="C51" s="68"/>
@@ -6442,7 +6375,7 @@
     </row>
     <row r="52" spans="1:11" ht="21.75" customHeight="1">
       <c r="A52" s="74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B52" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I52,재무상태표!$G:$G,0)),0)</f>
@@ -6484,7 +6417,7 @@
     </row>
     <row r="53" spans="1:11" ht="21.75" customHeight="1">
       <c r="A53" s="67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B53" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I53,재무상태표!$G:$G,0)),0)</f>
@@ -6526,7 +6459,7 @@
     </row>
     <row r="54" spans="1:11" ht="21.75" customHeight="1">
       <c r="A54" s="67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B54" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I54,재무상태표!$G:$G,0)),0)</f>
@@ -6568,7 +6501,7 @@
     </row>
     <row r="55" spans="1:11" ht="21.75" customHeight="1">
       <c r="A55" s="67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B55" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I55,재무상태표!$G:$G,0)),0)</f>
@@ -6579,7 +6512,7 @@
         <v>28,248,500</v>
       </c>
       <c r="D55" s="84" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E55" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I55,재무상태표!$G:$G,0)),0)</f>
@@ -6612,7 +6545,7 @@
     </row>
     <row r="56" spans="1:11" ht="21.75" customHeight="1">
       <c r="A56" s="67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B56" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I56,재무상태표!$G:$G,0)),0)</f>
@@ -6654,7 +6587,7 @@
     </row>
     <row r="57" spans="1:11" ht="21.75" customHeight="1">
       <c r="A57" s="67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B57" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I57,재무상태표!$G:$G,0)),0)</f>
@@ -6665,7 +6598,7 @@
         <v>43,441,422</v>
       </c>
       <c r="D57" s="85" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E57" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I57,재무상태표!$G:$G,0)),0)</f>
@@ -6698,7 +6631,7 @@
     </row>
     <row r="58" spans="1:11" ht="21.75" customHeight="1">
       <c r="A58" s="67" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B58" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I58,재무상태표!$G:$G,0)),0)</f>
@@ -6740,7 +6673,7 @@
     </row>
     <row r="59" spans="1:11" ht="21.75" customHeight="1">
       <c r="A59" s="67" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B59" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I59,재무상태표!$G:$G,0)),0)</f>
@@ -6782,7 +6715,7 @@
     </row>
     <row r="60" spans="1:11" ht="21.75" customHeight="1">
       <c r="A60" s="67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B60" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I60,재무상태표!$G:$G,0)),0)</f>
@@ -6793,7 +6726,7 @@
         <v>204,130,142</v>
       </c>
       <c r="D60" s="85" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E60" s="68">
         <f>IFERROR(INDEX(재무상태표!$D:$D,MATCH($I60,재무상태표!$G:$G,0)),0)</f>
@@ -6826,7 +6759,7 @@
     </row>
     <row r="61" spans="1:11" ht="21.75" customHeight="1">
       <c r="A61" s="67" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B61" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I61,재무상태표!$G:$G,0)),0)</f>
@@ -6868,7 +6801,7 @@
     </row>
     <row r="62" spans="1:11" ht="21.75" customHeight="1">
       <c r="A62" s="74" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B62" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I62,재무상태표!$G:$G,0)),0)</f>
@@ -6910,7 +6843,7 @@
     </row>
     <row r="63" spans="1:11" ht="21.75" customHeight="1">
       <c r="A63" s="67" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B63" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I63,재무상태표!$G:$G,0)),0)</f>
@@ -6952,7 +6885,7 @@
     </row>
     <row r="64" spans="1:11" ht="21.75" customHeight="1">
       <c r="A64" s="67" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B64" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I64,재무상태표!$G:$G,0)),0)</f>
@@ -6994,7 +6927,7 @@
     </row>
     <row r="65" spans="1:11" ht="21.75" customHeight="1">
       <c r="A65" s="88" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B65" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I65,재무상태표!$G:$G,0)),0)</f>
@@ -7036,7 +6969,7 @@
     </row>
     <row r="66" spans="1:11" ht="21.75" customHeight="1">
       <c r="A66" s="67" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B66" s="68"/>
       <c r="C66" s="68"/>
@@ -7063,7 +6996,7 @@
     </row>
     <row r="67" spans="1:11" ht="21.75" customHeight="1">
       <c r="A67" s="74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B67" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I67,재무상태표!$G:$G,0)),0)</f>
@@ -7105,7 +7038,7 @@
     </row>
     <row r="68" spans="1:11" ht="21.75" customHeight="1">
       <c r="A68" s="67" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B68" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I68,재무상태표!$G:$G,0)),0)</f>
@@ -7147,7 +7080,7 @@
     </row>
     <row r="69" spans="1:11" ht="21.75" customHeight="1">
       <c r="A69" s="74" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B69" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I69,재무상태표!$G:$G,0)),0)</f>
@@ -7189,7 +7122,7 @@
     </row>
     <row r="70" spans="1:11" ht="21.75" customHeight="1">
       <c r="A70" s="67" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B70" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I70,재무상태표!$G:$G,0)),0)</f>
@@ -7231,7 +7164,7 @@
     </row>
     <row r="71" spans="1:11" ht="21.75" customHeight="1">
       <c r="A71" s="74" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B71" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I71,재무상태표!$G:$G,0)),0)</f>
@@ -7273,7 +7206,7 @@
     </row>
     <row r="72" spans="1:11" ht="21.75" customHeight="1">
       <c r="A72" s="74" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B72" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I72,재무상태표!$G:$G,0)),0)</f>
@@ -7315,7 +7248,7 @@
     </row>
     <row r="73" spans="1:11" ht="21.75" customHeight="1">
       <c r="A73" s="74" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B73" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I73,재무상태표!$G:$G,0)),0)</f>
@@ -7357,7 +7290,7 @@
     </row>
     <row r="74" spans="1:11" ht="21.75" customHeight="1">
       <c r="A74" s="67" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B74" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I74,재무상태표!$G:$G,0)),0)</f>
@@ -7399,7 +7332,7 @@
     </row>
     <row r="75" spans="1:11" ht="21.75" customHeight="1">
       <c r="A75" s="67" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B75" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I75,재무상태표!$G:$G,0)),0)</f>
@@ -7441,7 +7374,7 @@
     </row>
     <row r="76" spans="1:11" ht="21.75" customHeight="1">
       <c r="A76" s="82" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B76" s="68">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I76,재무상태표!$G:$G,0)),0)</f>
@@ -7533,7 +7466,7 @@
     </row>
     <row r="79" spans="1:11" ht="21.75" customHeight="1">
       <c r="A79" s="88" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B79" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I79,재무상태표!$G:$G,0)),0)</f>
@@ -7575,7 +7508,7 @@
     </row>
     <row r="80" spans="1:11" ht="21.75" customHeight="1">
       <c r="A80" s="88" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B80" s="75">
         <f>IFERROR(INDEX(재무상태표!$B:$B,MATCH($I80,재무상태표!$G:$G,0)),0)</f>
@@ -7687,14 +7620,14 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
       <c r="A1" s="149" t="s">
-        <v>128</v>
-      </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
+        <v>127</v>
+      </c>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
     </row>
     <row r="2" spans="1:11" ht="6.75" customHeight="1">
       <c r="A2" s="61"/>
@@ -7734,53 +7667,53 @@
     </row>
     <row r="6" spans="1:11" ht="11.25" customHeight="1">
       <c r="A6" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="64" t="s">
         <v>42</v>
-      </c>
-      <c r="G6" s="64" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
       <c r="A7" s="150" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="150" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="150" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="130"/>
+      <c r="C7" s="132"/>
       <c r="D7" s="154" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="132"/>
+      <c r="G7" s="154" t="s">
+        <v>128</v>
+      </c>
+      <c r="J7" s="66" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="66" t="s">
         <v>129</v>
-      </c>
-      <c r="E7" s="150" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="130"/>
-      <c r="G7" s="154" t="s">
-        <v>129</v>
-      </c>
-      <c r="J7" s="66" t="s">
-        <v>49</v>
-      </c>
-      <c r="K7" s="66" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1">
       <c r="A8" s="152"/>
       <c r="B8" s="150" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="130"/>
+        <v>49</v>
+      </c>
+      <c r="C8" s="132"/>
       <c r="D8" s="152"/>
       <c r="E8" s="150" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="130"/>
+        <v>50</v>
+      </c>
+      <c r="F8" s="132"/>
       <c r="G8" s="152"/>
     </row>
     <row r="9" spans="1:11" ht="16.5" customHeight="1">
       <c r="A9" s="74" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B9" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I9,손익계산서!$G:$G,0)),0)</f>
@@ -7825,7 +7758,7 @@
     </row>
     <row r="10" spans="1:11" ht="16.5" customHeight="1">
       <c r="A10" s="67" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B10" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I10,손익계산서!$G:$G,0)),0)</f>
@@ -7864,7 +7797,7 @@
     </row>
     <row r="11" spans="1:11" ht="16.5" customHeight="1">
       <c r="A11" s="67" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B11" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I11,손익계산서!$G:$G,0)),0)</f>
@@ -7903,7 +7836,7 @@
     </row>
     <row r="12" spans="1:11" ht="16.5" customHeight="1">
       <c r="A12" s="74" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B12" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I12,손익계산서!$G:$G,0)),0)</f>
@@ -7948,7 +7881,7 @@
     </row>
     <row r="13" spans="1:11" ht="16.5" customHeight="1">
       <c r="A13" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B13" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I13,손익계산서!$G:$G,0)),0)</f>
@@ -7987,7 +7920,7 @@
     </row>
     <row r="14" spans="1:11" ht="16.5" customHeight="1">
       <c r="A14" s="67" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B14" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I14,손익계산서!$G:$G,0)),0)</f>
@@ -8026,7 +7959,7 @@
     </row>
     <row r="15" spans="1:11" ht="16.5" customHeight="1">
       <c r="A15" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B15" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I15,손익계산서!$G:$G,0)),0)</f>
@@ -8065,7 +7998,7 @@
     </row>
     <row r="16" spans="1:11" ht="16.5" customHeight="1">
       <c r="A16" s="67" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B16" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I16,손익계산서!$G:$G,0)),0)</f>
@@ -8104,7 +8037,7 @@
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1">
       <c r="A17" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B17" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I17,손익계산서!$G:$G,0)),0)</f>
@@ -8143,7 +8076,7 @@
     </row>
     <row r="18" spans="1:16" ht="17.25" customHeight="1">
       <c r="A18" s="74" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B18" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I18,손익계산서!$G:$G,0)),0)</f>
@@ -8188,7 +8121,7 @@
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1">
       <c r="A19" s="74" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B19" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I19,손익계산서!$G:$G,0)),0)</f>
@@ -8231,12 +8164,12 @@
         <v>-1.957789232550973E-2</v>
       </c>
       <c r="M19" s="97" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1">
       <c r="A20" s="67" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B20" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I20,손익계산서!$G:$G,0)),0)</f>
@@ -8289,7 +8222,7 @@
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1">
       <c r="A21" s="67" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B21" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I21,손익계산서!$G:$G,0)),0)</f>
@@ -8342,7 +8275,7 @@
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1">
       <c r="A22" s="67" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B22" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I22,손익계산서!$G:$G,0)),0)</f>
@@ -8395,7 +8328,7 @@
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1">
       <c r="A23" s="67" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B23" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I23,손익계산서!$G:$G,0)),0)</f>
@@ -8448,7 +8381,7 @@
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1">
       <c r="A24" s="67" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B24" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I24,손익계산서!$G:$G,0)),0)</f>
@@ -8501,7 +8434,7 @@
     </row>
     <row r="25" spans="1:16" ht="16.5" customHeight="1">
       <c r="A25" s="67" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B25" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I25,손익계산서!$G:$G,0)),0)</f>
@@ -8554,7 +8487,7 @@
     </row>
     <row r="26" spans="1:16" ht="16.5" customHeight="1">
       <c r="A26" s="67" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B26" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I26,손익계산서!$G:$G,0)),0)</f>
@@ -8607,7 +8540,7 @@
     </row>
     <row r="27" spans="1:16" ht="16.5" customHeight="1">
       <c r="A27" s="67" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B27" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I27,손익계산서!$G:$G,0)),0)</f>
@@ -8660,7 +8593,7 @@
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1">
       <c r="A28" s="67" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B28" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I28,손익계산서!$G:$G,0)),0)</f>
@@ -8713,7 +8646,7 @@
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1">
       <c r="A29" s="67" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B29" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I29,손익계산서!$G:$G,0)),0)</f>
@@ -8766,7 +8699,7 @@
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1">
       <c r="A30" s="67" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B30" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I30,손익계산서!$G:$G,0)),0)</f>
@@ -8819,7 +8752,7 @@
     </row>
     <row r="31" spans="1:16" ht="16.5" customHeight="1">
       <c r="A31" s="67" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B31" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I31,손익계산서!$G:$G,0)),0)</f>
@@ -8872,7 +8805,7 @@
     </row>
     <row r="32" spans="1:16" ht="16.5" customHeight="1">
       <c r="A32" s="67" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B32" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I32,손익계산서!$G:$G,0)),0)</f>
@@ -8925,7 +8858,7 @@
     </row>
     <row r="33" spans="1:16" ht="16.5" customHeight="1">
       <c r="A33" s="67" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B33" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I33,손익계산서!$G:$G,0)),0)</f>
@@ -8978,7 +8911,7 @@
     </row>
     <row r="34" spans="1:16" ht="16.5" customHeight="1">
       <c r="A34" s="67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B34" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I34,손익계산서!$G:$G,0)),0)</f>
@@ -9031,7 +8964,7 @@
     </row>
     <row r="35" spans="1:16" ht="16.5" customHeight="1">
       <c r="A35" s="67" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B35" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I35,손익계산서!$G:$G,0)),0)</f>
@@ -9084,7 +9017,7 @@
     </row>
     <row r="36" spans="1:16" ht="16.5" customHeight="1">
       <c r="A36" s="67" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B36" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I36,손익계산서!$G:$G,0)),0)</f>
@@ -9137,7 +9070,7 @@
     </row>
     <row r="37" spans="1:16" ht="16.5" customHeight="1">
       <c r="A37" s="67" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B37" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I37,손익계산서!$G:$G,0)),0)</f>
@@ -9190,7 +9123,7 @@
     </row>
     <row r="38" spans="1:16" ht="16.5" customHeight="1">
       <c r="A38" s="67" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B38" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I38,손익계산서!$G:$G,0)),0)</f>
@@ -9243,7 +9176,7 @@
     </row>
     <row r="39" spans="1:16" ht="16.5" customHeight="1">
       <c r="A39" s="67" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B39" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I39,손익계산서!$G:$G,0)),0)</f>
@@ -9296,7 +9229,7 @@
     </row>
     <row r="40" spans="1:16" ht="16.5" customHeight="1">
       <c r="A40" s="67" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B40" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I40,손익계산서!$G:$G,0)),0)</f>
@@ -9349,7 +9282,7 @@
     </row>
     <row r="41" spans="1:16" ht="17.25" customHeight="1">
       <c r="A41" s="74" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B41" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I41,손익계산서!$G:$G,0)),0)</f>
@@ -9394,7 +9327,7 @@
     </row>
     <row r="42" spans="1:16" ht="16.5" customHeight="1">
       <c r="A42" s="74" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B42" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I42,손익계산서!$G:$G,0)),0)</f>
@@ -9439,7 +9372,7 @@
     </row>
     <row r="43" spans="1:16" ht="16.5" customHeight="1">
       <c r="A43" s="67" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B43" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I43,손익계산서!$G:$G,0)),0)</f>
@@ -9484,7 +9417,7 @@
     </row>
     <row r="44" spans="1:16" ht="16.5" customHeight="1">
       <c r="A44" s="67" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B44" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I44,손익계산서!$G:$G,0)),0)</f>
@@ -9529,7 +9462,7 @@
     </row>
     <row r="45" spans="1:16" ht="16.5" customHeight="1">
       <c r="A45" s="67" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B45" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I45,손익계산서!$G:$G,0)),0)</f>
@@ -9574,7 +9507,7 @@
     </row>
     <row r="46" spans="1:16" ht="16.5" customHeight="1">
       <c r="A46" s="67" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I46,손익계산서!$G:$G,0)),0)</f>
@@ -9619,7 +9552,7 @@
     </row>
     <row r="47" spans="1:16" ht="16.5" customHeight="1">
       <c r="A47" s="67" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B47" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I47,손익계산서!$G:$G,0)),0)</f>
@@ -9664,7 +9597,7 @@
     </row>
     <row r="48" spans="1:16" ht="16.5" customHeight="1">
       <c r="A48" s="67" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B48" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I48,손익계산서!$G:$G,0)),0)</f>
@@ -9709,7 +9642,7 @@
     </row>
     <row r="49" spans="1:11" ht="16.5" customHeight="1">
       <c r="A49" s="67" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B49" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I49,손익계산서!$G:$G,0)),0)</f>
@@ -9754,7 +9687,7 @@
     </row>
     <row r="50" spans="1:11" ht="16.5" customHeight="1">
       <c r="A50" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B50" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I50,손익계산서!$G:$G,0)),0)</f>
@@ -9799,7 +9732,7 @@
     </row>
     <row r="51" spans="1:11" ht="16.5" customHeight="1">
       <c r="A51" s="67" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B51" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I51,손익계산서!$G:$G,0)),0)</f>
@@ -9844,7 +9777,7 @@
     </row>
     <row r="52" spans="1:11" ht="16.5" customHeight="1">
       <c r="A52" s="67" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B52" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I52,손익계산서!$G:$G,0)),0)</f>
@@ -9889,7 +9822,7 @@
     </row>
     <row r="53" spans="1:11" ht="16.5" customHeight="1">
       <c r="A53" s="67" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B53" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I53,손익계산서!$G:$G,0)),0)</f>
@@ -9934,7 +9867,7 @@
     </row>
     <row r="54" spans="1:11" ht="16.5" customHeight="1">
       <c r="A54" s="67" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B54" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I54,손익계산서!$G:$G,0)),0)</f>
@@ -9979,7 +9912,7 @@
     </row>
     <row r="55" spans="1:11" ht="16.5" customHeight="1">
       <c r="A55" s="101" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B55" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I55,손익계산서!$G:$G,0)),0)</f>
@@ -10024,7 +9957,7 @@
     </row>
     <row r="56" spans="1:11" ht="16.5" customHeight="1">
       <c r="A56" s="67" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B56" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I56,손익계산서!$G:$G,0)),0)</f>
@@ -10069,7 +10002,7 @@
     </row>
     <row r="57" spans="1:11" ht="16.5" customHeight="1">
       <c r="A57" s="67" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B57" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I57,손익계산서!$G:$G,0)),0)</f>
@@ -10114,7 +10047,7 @@
     </row>
     <row r="58" spans="1:11" ht="17.25" customHeight="1">
       <c r="A58" s="74" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B58" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I58,손익계산서!$G:$G,0)),0)</f>
@@ -10159,7 +10092,7 @@
     </row>
     <row r="59" spans="1:11" ht="16.5" customHeight="1">
       <c r="A59" s="74" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B59" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I59,손익계산서!$G:$G,0)),0)</f>
@@ -10204,7 +10137,7 @@
     </row>
     <row r="60" spans="1:11" ht="16.5" customHeight="1">
       <c r="A60" s="67" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B60" s="95">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I60,손익계산서!$G:$G,0)),0)</f>
@@ -10243,7 +10176,7 @@
     </row>
     <row r="61" spans="1:11" ht="17.25" customHeight="1">
       <c r="A61" s="74" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B61" s="91">
         <f>IFERROR(INDEX(손익계산서!$B:$B,MATCH($I61,손익계산서!$G:$G,0)),0)</f>
@@ -10352,16 +10285,16 @@
         <f>"손익계산서(전월대비 증감내역)"</f>
         <v>손익계산서(전월대비 증감내역)</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
       <c r="L1" s="156"/>
       <c r="M1" s="153"/>
     </row>
@@ -10371,51 +10304,51 @@
         <f>"기간 : "&amp;TEXT(EOMONTH(인덱스!$K$1,-2)+1,"yyyy")&amp;"년"&amp;TEXT(MONTH(EOMONTH(인덱스!$K$1,-2)+1),"00")&amp;"월"&amp;TEXT(DAY(EOMONTH(인덱스!$K$1,-2)+1),"00")&amp;"일"&amp;"부터 - "&amp;TEXT(인덱스!$K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH(인덱스!$K$1),"00")&amp;"월"&amp;TEXT(DAY(인덱스!$K$1),"00")&amp;"일"&amp;"까지"</f>
         <v>기간 : 2026년06월01일부터 - 2026년07월31일까지</v>
       </c>
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
       <c r="L3" s="156"/>
       <c r="M3" s="153"/>
     </row>
     <row r="5" spans="1:17" ht="11.25" customHeight="1">
       <c r="A5" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="103" t="s">
         <v>42</v>
-      </c>
-      <c r="M5" s="103" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="35.25" customHeight="1">
       <c r="A6" s="65" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="65" t="s">
         <v>185</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="D6" s="65" t="s">
         <v>186</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="E6" s="65" t="s">
         <v>187</v>
       </c>
-      <c r="E6" s="65" t="s">
+      <c r="F6" s="65" t="s">
         <v>188</v>
       </c>
-      <c r="F6" s="65" t="s">
+      <c r="G6" s="65" t="s">
         <v>189</v>
       </c>
-      <c r="G6" s="65" t="s">
+      <c r="H6" s="65" t="s">
         <v>190</v>
-      </c>
-      <c r="H6" s="65" t="s">
-        <v>191</v>
       </c>
       <c r="I6" s="65" t="str">
         <f>"전월("&amp;MONTH(EOMONTH(인덱스!$K$1,-1))&amp;"월)"</f>
@@ -10426,24 +10359,24 @@
         <v>당월(7월)</v>
       </c>
       <c r="K6" s="104" t="s">
+        <v>191</v>
+      </c>
+      <c r="L6" s="104" t="s">
         <v>192</v>
       </c>
-      <c r="L6" s="104" t="s">
-        <v>193</v>
-      </c>
       <c r="M6" s="65" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P6" s="66" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="22.5" customHeight="1">
       <c r="A7" s="105" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B7" s="91">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O7,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10509,7 +10442,7 @@
     </row>
     <row r="8" spans="1:17" ht="22.5" customHeight="1">
       <c r="A8" s="108" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B8" s="95">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O8,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10572,7 +10505,7 @@
     </row>
     <row r="9" spans="1:17" ht="22.5" customHeight="1">
       <c r="A9" s="108" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B9" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O9,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10635,7 +10568,7 @@
     </row>
     <row r="10" spans="1:17" ht="22.5" customHeight="1">
       <c r="A10" s="105" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B10" s="112">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O10,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10701,7 +10634,7 @@
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
       <c r="A11" s="108" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B11" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O11,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10764,7 +10697,7 @@
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
       <c r="A12" s="108" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B12" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O12,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10827,7 +10760,7 @@
     </row>
     <row r="13" spans="1:17" ht="22.5" customHeight="1">
       <c r="A13" s="108" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B13" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O13,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10890,7 +10823,7 @@
     </row>
     <row r="14" spans="1:17" ht="22.5" customHeight="1">
       <c r="A14" s="108" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B14" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O14,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -10953,7 +10886,7 @@
     </row>
     <row r="15" spans="1:17" ht="22.5" customHeight="1">
       <c r="A15" s="108" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B15" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O15,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11016,7 +10949,7 @@
     </row>
     <row r="16" spans="1:17" ht="24" customHeight="1">
       <c r="A16" s="74" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B16" s="91">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O16,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11082,7 +11015,7 @@
     </row>
     <row r="17" spans="1:17" ht="22.5" customHeight="1">
       <c r="A17" s="105" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B17" s="112">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O17,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11148,7 +11081,7 @@
     </row>
     <row r="18" spans="1:17" ht="22.5" customHeight="1">
       <c r="A18" s="108" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B18" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O18,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11195,7 +11128,7 @@
         <v>감소</v>
       </c>
       <c r="M18" s="114" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="1"/>
@@ -11216,7 +11149,7 @@
     </row>
     <row r="19" spans="1:17" ht="22.5" customHeight="1">
       <c r="A19" s="108" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B19" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O19,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11282,7 +11215,7 @@
     </row>
     <row r="20" spans="1:17" ht="22.5" customHeight="1">
       <c r="A20" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B20" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O20,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11329,7 +11262,7 @@
         <v>감소</v>
       </c>
       <c r="M20" s="114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="1"/>
@@ -11350,7 +11283,7 @@
     </row>
     <row r="21" spans="1:17" ht="22.5" customHeight="1">
       <c r="A21" s="108" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B21" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O21,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11397,7 +11330,7 @@
         <v>증가</v>
       </c>
       <c r="M21" s="115" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="1"/>
@@ -11418,7 +11351,7 @@
     </row>
     <row r="22" spans="1:17" ht="22.5" customHeight="1">
       <c r="A22" s="108" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B22" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O22,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11465,7 +11398,7 @@
         <v>감소</v>
       </c>
       <c r="M22" s="115" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="1"/>
@@ -11486,7 +11419,7 @@
     </row>
     <row r="23" spans="1:17" ht="22.5" customHeight="1">
       <c r="A23" s="108" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B23" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O23,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11552,7 +11485,7 @@
     </row>
     <row r="24" spans="1:17" ht="22.5" customHeight="1">
       <c r="A24" s="108" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B24" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O24,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11599,7 +11532,7 @@
         <v>감소</v>
       </c>
       <c r="M24" s="115" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="1"/>
@@ -11620,7 +11553,7 @@
     </row>
     <row r="25" spans="1:17" ht="22.5" customHeight="1">
       <c r="A25" s="108" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B25" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O25,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11667,7 +11600,7 @@
         <v>증가</v>
       </c>
       <c r="M25" s="115" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="1"/>
@@ -11688,7 +11621,7 @@
     </row>
     <row r="26" spans="1:17" ht="22.5" customHeight="1">
       <c r="A26" s="108" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B26" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O26,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11735,7 +11668,7 @@
         <v>증가</v>
       </c>
       <c r="M26" s="115" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N26" t="str">
         <f t="shared" si="1"/>
@@ -11756,7 +11689,7 @@
     </row>
     <row r="27" spans="1:17" ht="23.25" customHeight="1">
       <c r="A27" s="108" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B27" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O27,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11803,7 +11736,7 @@
         <v>감소</v>
       </c>
       <c r="M27" s="115" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N27" t="str">
         <f t="shared" si="1"/>
@@ -11824,7 +11757,7 @@
     </row>
     <row r="28" spans="1:17" ht="22.5" customHeight="1">
       <c r="A28" s="108" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B28" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O28,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11871,7 +11804,7 @@
         <v>변동없음</v>
       </c>
       <c r="M28" s="115" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N28" t="str">
         <f t="shared" si="1"/>
@@ -11892,7 +11825,7 @@
     </row>
     <row r="29" spans="1:17" ht="22.5" customHeight="1">
       <c r="A29" s="108" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B29" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O29,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -11939,7 +11872,7 @@
         <v>변동없음</v>
       </c>
       <c r="M29" s="115" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N29" t="str">
         <f t="shared" si="1"/>
@@ -11960,7 +11893,7 @@
     </row>
     <row r="30" spans="1:17" ht="22.5" customHeight="1">
       <c r="A30" s="108" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B30" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O30,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12007,7 +11940,7 @@
         <v>감소</v>
       </c>
       <c r="M30" s="115" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N30" t="str">
         <f t="shared" si="1"/>
@@ -12028,7 +11961,7 @@
     </row>
     <row r="31" spans="1:17" ht="22.5" customHeight="1">
       <c r="A31" s="108" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B31" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O31,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12075,7 +12008,7 @@
         <v>증가</v>
       </c>
       <c r="M31" s="115" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N31" t="str">
         <f t="shared" si="1"/>
@@ -12096,7 +12029,7 @@
     </row>
     <row r="32" spans="1:17" ht="22.5" customHeight="1">
       <c r="A32" s="108" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B32" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O32,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12143,7 +12076,7 @@
         <v>감소</v>
       </c>
       <c r="M32" s="115" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N32" t="str">
         <f t="shared" si="1"/>
@@ -12164,7 +12097,7 @@
     </row>
     <row r="33" spans="1:17" ht="22.5" customHeight="1">
       <c r="A33" s="108" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B33" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O33,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12211,7 +12144,7 @@
         <v>변동없음</v>
       </c>
       <c r="M33" s="115" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N33" t="str">
         <f t="shared" si="1"/>
@@ -12232,7 +12165,7 @@
     </row>
     <row r="34" spans="1:17" ht="22.5" customHeight="1">
       <c r="A34" s="108" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B34" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O34,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12279,7 +12212,7 @@
         <v>증가</v>
       </c>
       <c r="M34" s="115" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N34" t="str">
         <f t="shared" si="1"/>
@@ -12300,7 +12233,7 @@
     </row>
     <row r="35" spans="1:17" ht="26.25" customHeight="1">
       <c r="A35" s="108" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B35" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O35,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12347,7 +12280,7 @@
         <v>감소</v>
       </c>
       <c r="M35" s="114" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N35" t="str">
         <f t="shared" si="1"/>
@@ -12368,7 +12301,7 @@
     </row>
     <row r="36" spans="1:17" ht="22.5" customHeight="1">
       <c r="A36" s="108" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B36" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O36,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12415,7 +12348,7 @@
         <v>변동없음</v>
       </c>
       <c r="M36" s="115" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N36" t="str">
         <f t="shared" si="1"/>
@@ -12436,7 +12369,7 @@
     </row>
     <row r="37" spans="1:17" ht="22.5" customHeight="1">
       <c r="A37" s="108" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B37" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O37,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12483,7 +12416,7 @@
         <v>변동없음</v>
       </c>
       <c r="M37" s="115" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N37" t="str">
         <f t="shared" si="1"/>
@@ -12504,7 +12437,7 @@
     </row>
     <row r="38" spans="1:17" ht="24" customHeight="1">
       <c r="A38" s="74" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B38" s="91">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O38,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12570,7 +12503,7 @@
     </row>
     <row r="39" spans="1:17" ht="22.5" customHeight="1">
       <c r="A39" s="74" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B39" s="91">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O39,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12636,7 +12569,7 @@
     </row>
     <row r="40" spans="1:17" ht="22.5" customHeight="1">
       <c r="A40" s="67" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B40" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O40,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12683,7 +12616,7 @@
         <v>감소</v>
       </c>
       <c r="M40" s="115" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N40" t="str">
         <f t="shared" si="1"/>
@@ -12704,7 +12637,7 @@
     </row>
     <row r="41" spans="1:17" ht="22.5" customHeight="1">
       <c r="A41" s="67" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B41" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O41,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12770,7 +12703,7 @@
     </row>
     <row r="42" spans="1:17" ht="22.5" customHeight="1">
       <c r="A42" s="67" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B42" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O42,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12836,7 +12769,7 @@
     </row>
     <row r="43" spans="1:17" ht="22.5" customHeight="1">
       <c r="A43" s="67" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B43" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O43,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12902,7 +12835,7 @@
     </row>
     <row r="44" spans="1:17" ht="22.5" customHeight="1">
       <c r="A44" s="67" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B44" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O44,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -12949,7 +12882,7 @@
         <v>감소</v>
       </c>
       <c r="M44" s="116" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N44" t="str">
         <f t="shared" si="1"/>
@@ -12970,7 +12903,7 @@
     </row>
     <row r="45" spans="1:17" ht="22.5" customHeight="1">
       <c r="A45" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B45" s="112">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O45,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13036,7 +12969,7 @@
     </row>
     <row r="46" spans="1:17" ht="22.5" customHeight="1">
       <c r="A46" s="67" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B46" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O46,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13102,7 +13035,7 @@
     </row>
     <row r="47" spans="1:17" ht="22.5" customHeight="1">
       <c r="A47" s="67" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O47,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13168,7 +13101,7 @@
     </row>
     <row r="48" spans="1:17" ht="22.5" customHeight="1">
       <c r="A48" s="67" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B48" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O48,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13234,7 +13167,7 @@
     </row>
     <row r="49" spans="1:17" ht="22.5" customHeight="1">
       <c r="A49" s="67" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B49" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O49,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13300,7 +13233,7 @@
     </row>
     <row r="50" spans="1:17" ht="22.5" customHeight="1">
       <c r="A50" s="108" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B50" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O50,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13366,7 +13299,7 @@
     </row>
     <row r="51" spans="1:17" ht="24" customHeight="1">
       <c r="A51" s="74" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B51" s="91">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O51,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13432,7 +13365,7 @@
     </row>
     <row r="52" spans="1:17" ht="22.5" customHeight="1">
       <c r="A52" s="74" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B52" s="91">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O52,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13498,7 +13431,7 @@
     </row>
     <row r="53" spans="1:17" ht="22.5" customHeight="1">
       <c r="A53" s="67" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B53" s="111">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O53,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13564,7 +13497,7 @@
     </row>
     <row r="54" spans="1:17" ht="24" customHeight="1">
       <c r="A54" s="74" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B54" s="91">
         <f>IFERROR(INDEX(기간별손익계산서!$B:$B,MATCH($O54,기간별손익계산서!$Q:$Q,0)),0)</f>
@@ -13803,31 +13736,31 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" customHeight="1">
       <c r="A1" s="157" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="159" t="s">
         <v>44</v>
-      </c>
-      <c r="B1" s="159" t="s">
-        <v>45</v>
       </c>
       <c r="C1" s="160"/>
       <c r="D1" s="159" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E1" s="160"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" customHeight="1">
       <c r="A2" s="161"/>
       <c r="B2" s="157" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="158"/>
       <c r="D2" s="157" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E2" s="158"/>
     </row>
     <row r="3" spans="1:7" ht="12" customHeight="1">
       <c r="A3" s="119" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" s="120"/>
       <c r="C3" s="120"/>
@@ -13844,15 +13777,15 @@
     </row>
     <row r="4" spans="1:7" ht="12" customHeight="1">
       <c r="A4" s="121" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" s="120"/>
       <c r="C4" s="120" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="120" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" si="0"/>
@@ -13865,15 +13798,15 @@
     </row>
     <row r="5" spans="1:7" ht="12" customHeight="1">
       <c r="A5" s="121" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" s="120"/>
       <c r="C5" s="120" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D5" s="120"/>
       <c r="E5" s="120" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F5" t="str">
         <f t="shared" si="0"/>
@@ -13886,15 +13819,15 @@
     </row>
     <row r="6" spans="1:7" ht="12" customHeight="1">
       <c r="A6" s="119" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6" s="120"/>
       <c r="C6" s="120" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D6" s="120"/>
       <c r="E6" s="120" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F6" t="str">
         <f t="shared" si="0"/>
@@ -13907,15 +13840,15 @@
     </row>
     <row r="7" spans="1:7" ht="12" customHeight="1">
       <c r="A7" s="119" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B7" s="120"/>
       <c r="C7" s="120" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D7" s="120"/>
       <c r="E7" s="120" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="0"/>
@@ -13928,15 +13861,15 @@
     </row>
     <row r="8" spans="1:7" ht="12" customHeight="1">
       <c r="A8" s="119" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="120"/>
       <c r="C8" s="120" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D8" s="120"/>
       <c r="E8" s="120" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F8" t="str">
         <f t="shared" si="0"/>
@@ -13949,15 +13882,15 @@
     </row>
     <row r="9" spans="1:7" ht="12" customHeight="1">
       <c r="A9" s="119" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B9" s="120"/>
       <c r="C9" s="120" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D9" s="120"/>
       <c r="E9" s="120" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" si="0"/>
@@ -13970,14 +13903,14 @@
     </row>
     <row r="10" spans="1:7" ht="12" customHeight="1">
       <c r="A10" s="119" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="120" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C10" s="120"/>
       <c r="D10" s="120" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E10" s="120"/>
       <c r="F10" t="str">
@@ -13991,19 +13924,19 @@
     </row>
     <row r="11" spans="1:7" ht="12" customHeight="1">
       <c r="A11" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B11" s="120" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="120" t="s">
         <v>228</v>
       </c>
-      <c r="C11" s="120" t="s">
+      <c r="D11" s="120" t="s">
+        <v>227</v>
+      </c>
+      <c r="E11" s="120" t="s">
         <v>229</v>
-      </c>
-      <c r="D11" s="120" t="s">
-        <v>228</v>
-      </c>
-      <c r="E11" s="120" t="s">
-        <v>230</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="0"/>
@@ -14016,14 +13949,14 @@
     </row>
     <row r="12" spans="1:7" ht="12" customHeight="1">
       <c r="A12" s="119" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12" s="120" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C12" s="120"/>
       <c r="D12" s="120" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E12" s="120"/>
       <c r="F12" t="str">
@@ -14037,19 +13970,19 @@
     </row>
     <row r="13" spans="1:7" ht="12" customHeight="1">
       <c r="A13" s="119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="120" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="120" t="s">
         <v>233</v>
       </c>
-      <c r="C13" s="120" t="s">
+      <c r="D13" s="120" t="s">
+        <v>232</v>
+      </c>
+      <c r="E13" s="120" t="s">
         <v>234</v>
-      </c>
-      <c r="D13" s="120" t="s">
-        <v>233</v>
-      </c>
-      <c r="E13" s="120" t="s">
-        <v>235</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="0"/>
@@ -14062,15 +13995,15 @@
     </row>
     <row r="14" spans="1:7" ht="12" customHeight="1">
       <c r="A14" s="122" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B14" s="120"/>
       <c r="C14" s="120" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D14" s="120"/>
       <c r="E14" s="120" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F14" t="str">
         <f t="shared" si="0"/>
@@ -14083,15 +14016,15 @@
     </row>
     <row r="15" spans="1:7" ht="12" customHeight="1">
       <c r="A15" s="119" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="120"/>
       <c r="C15" s="120" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D15" s="120"/>
       <c r="E15" s="120" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F15" t="str">
         <f t="shared" si="0"/>
@@ -14104,15 +14037,15 @@
     </row>
     <row r="16" spans="1:7" ht="12" customHeight="1">
       <c r="A16" s="119" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="120"/>
       <c r="C16" s="120" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D16" s="120"/>
       <c r="E16" s="120" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F16" t="str">
         <f t="shared" si="0"/>
@@ -14125,15 +14058,15 @@
     </row>
     <row r="17" spans="1:7" ht="12" customHeight="1">
       <c r="A17" s="119" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B17" s="120"/>
       <c r="C17" s="120" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D17" s="120"/>
       <c r="E17" s="120" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F17" t="str">
         <f t="shared" si="0"/>
@@ -14146,11 +14079,11 @@
     </row>
     <row r="18" spans="1:7" ht="12" customHeight="1">
       <c r="A18" s="119" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="120"/>
       <c r="C18" s="120" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D18" s="120"/>
       <c r="E18" s="120"/>
@@ -14165,11 +14098,11 @@
     </row>
     <row r="19" spans="1:7" ht="12" customHeight="1">
       <c r="A19" s="119" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19" s="120"/>
       <c r="C19" s="120" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D19" s="120"/>
       <c r="E19" s="120"/>
@@ -14184,15 +14117,15 @@
     </row>
     <row r="20" spans="1:7" ht="12" customHeight="1">
       <c r="A20" s="121" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="120"/>
       <c r="C20" s="120" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D20" s="120"/>
       <c r="E20" s="120" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F20" t="str">
         <f t="shared" si="0"/>
@@ -14205,15 +14138,15 @@
     </row>
     <row r="21" spans="1:7" ht="12" customHeight="1">
       <c r="A21" s="119" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" s="120"/>
       <c r="C21" s="120" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D21" s="120"/>
       <c r="E21" s="120" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F21" t="str">
         <f t="shared" si="0"/>
@@ -14226,15 +14159,15 @@
     </row>
     <row r="22" spans="1:7" ht="12" customHeight="1">
       <c r="A22" s="121" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B22" s="120"/>
       <c r="C22" s="120" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D22" s="120"/>
       <c r="E22" s="120" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F22" t="str">
         <f t="shared" si="0"/>
@@ -14247,15 +14180,15 @@
     </row>
     <row r="23" spans="1:7" ht="12" customHeight="1">
       <c r="A23" s="119" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B23" s="120"/>
       <c r="C23" s="120" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D23" s="120"/>
       <c r="E23" s="120" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F23" t="str">
         <f t="shared" si="0"/>
@@ -14268,15 +14201,15 @@
     </row>
     <row r="24" spans="1:7" ht="12" customHeight="1">
       <c r="A24" s="122" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B24" s="120"/>
       <c r="C24" s="120" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D24" s="120"/>
       <c r="E24" s="120" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F24" t="str">
         <f t="shared" si="0"/>
@@ -14289,15 +14222,15 @@
     </row>
     <row r="25" spans="1:7" ht="12" customHeight="1">
       <c r="A25" s="121" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B25" s="120"/>
       <c r="C25" s="120" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D25" s="120"/>
       <c r="E25" s="120" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F25" t="str">
         <f t="shared" si="0"/>
@@ -14310,15 +14243,15 @@
     </row>
     <row r="26" spans="1:7" ht="12" customHeight="1">
       <c r="A26" s="119" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="120"/>
       <c r="C26" s="120" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D26" s="120"/>
       <c r="E26" s="120" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F26" t="str">
         <f t="shared" si="0"/>
@@ -14331,15 +14264,15 @@
     </row>
     <row r="27" spans="1:7" ht="12" customHeight="1">
       <c r="A27" s="122" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B27" s="120"/>
       <c r="C27" s="120" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D27" s="120"/>
       <c r="E27" s="120" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F27" t="str">
         <f t="shared" si="0"/>
@@ -14352,14 +14285,14 @@
     </row>
     <row r="28" spans="1:7" ht="12" customHeight="1">
       <c r="A28" s="119" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B28" s="120" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C28" s="120"/>
       <c r="D28" s="120" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E28" s="120"/>
       <c r="F28" t="str">
@@ -14373,19 +14306,19 @@
     </row>
     <row r="29" spans="1:7" ht="12" customHeight="1">
       <c r="A29" s="119" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B29" s="120" t="s">
+        <v>255</v>
+      </c>
+      <c r="C29" s="120" t="s">
         <v>256</v>
       </c>
-      <c r="C29" s="120" t="s">
+      <c r="D29" s="120" t="s">
         <v>257</v>
       </c>
-      <c r="D29" s="120" t="s">
+      <c r="E29" s="120" t="s">
         <v>258</v>
-      </c>
-      <c r="E29" s="120" t="s">
-        <v>259</v>
       </c>
       <c r="F29" t="str">
         <f t="shared" si="0"/>
@@ -14398,14 +14331,14 @@
     </row>
     <row r="30" spans="1:7" ht="12" customHeight="1">
       <c r="A30" s="119" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B30" s="120" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C30" s="120"/>
       <c r="D30" s="120" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E30" s="120"/>
       <c r="F30" t="str">
@@ -14419,19 +14352,19 @@
     </row>
     <row r="31" spans="1:7" ht="12" customHeight="1">
       <c r="A31" s="119" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B31" s="120" t="s">
+        <v>260</v>
+      </c>
+      <c r="C31" s="120" t="s">
         <v>261</v>
       </c>
-      <c r="C31" s="120" t="s">
-        <v>262</v>
-      </c>
       <c r="D31" s="120" t="s">
+        <v>260</v>
+      </c>
+      <c r="E31" s="120" t="s">
         <v>261</v>
-      </c>
-      <c r="E31" s="120" t="s">
-        <v>262</v>
       </c>
       <c r="F31" t="str">
         <f t="shared" si="0"/>
@@ -14444,14 +14377,14 @@
     </row>
     <row r="32" spans="1:7" ht="12" customHeight="1">
       <c r="A32" s="119" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B32" s="120" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C32" s="120"/>
       <c r="D32" s="120" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E32" s="120"/>
       <c r="F32" t="str">
@@ -14465,19 +14398,19 @@
     </row>
     <row r="33" spans="1:7" ht="12" customHeight="1">
       <c r="A33" s="119" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B33" s="120" t="s">
+        <v>264</v>
+      </c>
+      <c r="C33" s="120" t="s">
         <v>265</v>
       </c>
-      <c r="C33" s="120" t="s">
+      <c r="D33" s="120" t="s">
         <v>266</v>
       </c>
-      <c r="D33" s="120" t="s">
+      <c r="E33" s="120" t="s">
         <v>267</v>
-      </c>
-      <c r="E33" s="120" t="s">
-        <v>268</v>
       </c>
       <c r="F33" t="str">
         <f t="shared" si="0"/>
@@ -14490,14 +14423,14 @@
     </row>
     <row r="34" spans="1:7" ht="12" customHeight="1">
       <c r="A34" s="119" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B34" s="120" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C34" s="120"/>
       <c r="D34" s="120" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E34" s="120"/>
       <c r="F34" t="str">
@@ -14511,19 +14444,19 @@
     </row>
     <row r="35" spans="1:7" ht="12" customHeight="1">
       <c r="A35" s="119" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B35" s="120" t="s">
+        <v>269</v>
+      </c>
+      <c r="C35" s="120" t="s">
         <v>270</v>
       </c>
-      <c r="C35" s="120" t="s">
+      <c r="D35" s="120" t="s">
         <v>271</v>
       </c>
-      <c r="D35" s="120" t="s">
+      <c r="E35" s="120" t="s">
         <v>272</v>
-      </c>
-      <c r="E35" s="120" t="s">
-        <v>273</v>
       </c>
       <c r="F35" t="str">
         <f t="shared" ref="F35:F70" si="1">IF(A35="","",SUBSTITUTE(A35," ",""))</f>
@@ -14536,7 +14469,7 @@
     </row>
     <row r="36" spans="1:7" ht="12" customHeight="1">
       <c r="A36" s="119" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B36" s="120"/>
       <c r="C36" s="120"/>
@@ -14553,15 +14486,15 @@
     </row>
     <row r="37" spans="1:7" ht="12" customHeight="1">
       <c r="A37" s="122" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B37" s="120"/>
       <c r="C37" s="120" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D37" s="120"/>
       <c r="E37" s="120" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F37" t="str">
         <f t="shared" si="1"/>
@@ -14574,15 +14507,15 @@
     </row>
     <row r="38" spans="1:7" ht="12" customHeight="1">
       <c r="A38" s="122" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B38" s="120"/>
       <c r="C38" s="120" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D38" s="120"/>
       <c r="E38" s="120" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F38" t="str">
         <f t="shared" si="1"/>
@@ -14595,15 +14528,15 @@
     </row>
     <row r="39" spans="1:7" ht="12" customHeight="1">
       <c r="A39" s="122" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B39" s="120"/>
       <c r="C39" s="120" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D39" s="120"/>
       <c r="E39" s="120" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F39" t="str">
         <f t="shared" si="1"/>
@@ -14616,15 +14549,15 @@
     </row>
     <row r="40" spans="1:7" ht="12" customHeight="1">
       <c r="A40" s="122" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B40" s="120"/>
       <c r="C40" s="120" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D40" s="120"/>
       <c r="E40" s="120" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F40" t="str">
         <f t="shared" si="1"/>
@@ -14637,15 +14570,15 @@
     </row>
     <row r="41" spans="1:7" ht="12" customHeight="1">
       <c r="A41" s="119" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B41" s="120"/>
       <c r="C41" s="120" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D41" s="120"/>
       <c r="E41" s="120" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F41" t="str">
         <f t="shared" si="1"/>
@@ -14658,7 +14591,7 @@
     </row>
     <row r="42" spans="1:7" ht="12" customHeight="1">
       <c r="A42" s="119" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B42" s="120"/>
       <c r="C42" s="120"/>
@@ -14675,15 +14608,15 @@
     </row>
     <row r="43" spans="1:7" ht="12" customHeight="1">
       <c r="A43" s="119" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B43" s="120"/>
       <c r="C43" s="120" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D43" s="120"/>
       <c r="E43" s="120" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F43" t="str">
         <f t="shared" si="1"/>
@@ -14696,15 +14629,15 @@
     </row>
     <row r="44" spans="1:7" ht="12" customHeight="1">
       <c r="A44" s="119" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B44" s="120"/>
       <c r="C44" s="120" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D44" s="120"/>
       <c r="E44" s="120" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F44" t="str">
         <f t="shared" si="1"/>
@@ -14717,15 +14650,15 @@
     </row>
     <row r="45" spans="1:7" ht="12" customHeight="1">
       <c r="A45" s="119" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B45" s="120"/>
       <c r="C45" s="120" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D45" s="120"/>
       <c r="E45" s="120" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F45" t="str">
         <f t="shared" si="1"/>
@@ -14738,15 +14671,15 @@
     </row>
     <row r="46" spans="1:7" ht="12" customHeight="1">
       <c r="A46" s="122" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B46" s="120"/>
       <c r="C46" s="120" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D46" s="120"/>
       <c r="E46" s="120" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F46" t="str">
         <f t="shared" si="1"/>
@@ -14759,11 +14692,11 @@
     </row>
     <row r="47" spans="1:7" ht="12" customHeight="1">
       <c r="A47" s="119" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B47" s="120"/>
       <c r="C47" s="120" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D47" s="120"/>
       <c r="E47" s="120"/>
@@ -14778,11 +14711,11 @@
     </row>
     <row r="48" spans="1:7" ht="12" customHeight="1">
       <c r="A48" s="119" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B48" s="120"/>
       <c r="C48" s="120" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D48" s="120"/>
       <c r="E48" s="120"/>
@@ -14797,15 +14730,15 @@
     </row>
     <row r="49" spans="1:7" ht="12" customHeight="1">
       <c r="A49" s="119" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B49" s="120"/>
       <c r="C49" s="120" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D49" s="120"/>
       <c r="E49" s="120" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F49" t="str">
         <f t="shared" si="1"/>
@@ -14818,13 +14751,13 @@
     </row>
     <row r="50" spans="1:7" ht="12" customHeight="1">
       <c r="A50" s="121" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B50" s="120"/>
       <c r="C50" s="120"/>
       <c r="D50" s="120"/>
       <c r="E50" s="120" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F50" t="str">
         <f t="shared" si="1"/>
@@ -14837,15 +14770,15 @@
     </row>
     <row r="51" spans="1:7" ht="12" customHeight="1">
       <c r="A51" s="119" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B51" s="120"/>
       <c r="C51" s="120" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D51" s="120"/>
       <c r="E51" s="120" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F51" t="str">
         <f t="shared" si="1"/>
@@ -14858,15 +14791,15 @@
     </row>
     <row r="52" spans="1:7" ht="12" customHeight="1">
       <c r="A52" s="119" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B52" s="120"/>
       <c r="C52" s="120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D52" s="120"/>
       <c r="E52" s="120" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F52" t="str">
         <f t="shared" si="1"/>
@@ -14879,13 +14812,13 @@
     </row>
     <row r="53" spans="1:7" ht="12" customHeight="1">
       <c r="A53" s="119" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B53" s="120"/>
       <c r="C53" s="120"/>
       <c r="D53" s="120"/>
       <c r="E53" s="120" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F53" t="str">
         <f t="shared" si="1"/>
@@ -14898,15 +14831,15 @@
     </row>
     <row r="54" spans="1:7" ht="12" customHeight="1">
       <c r="A54" s="119" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B54" s="120"/>
       <c r="C54" s="120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D54" s="120"/>
       <c r="E54" s="120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F54" t="str">
         <f t="shared" si="1"/>
@@ -14919,15 +14852,15 @@
     </row>
     <row r="55" spans="1:7" ht="12" customHeight="1">
       <c r="A55" s="121" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B55" s="120"/>
       <c r="C55" s="120" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D55" s="120"/>
       <c r="E55" s="120" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F55" t="str">
         <f t="shared" si="1"/>
@@ -14940,7 +14873,7 @@
     </row>
     <row r="56" spans="1:7" ht="12" customHeight="1">
       <c r="A56" s="122" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B56" s="120"/>
       <c r="C56" s="120"/>
@@ -14957,15 +14890,15 @@
     </row>
     <row r="57" spans="1:7" ht="12" customHeight="1">
       <c r="A57" s="119" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B57" s="120"/>
       <c r="C57" s="120" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D57" s="120"/>
       <c r="E57" s="120" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F57" t="str">
         <f t="shared" si="1"/>
@@ -14978,15 +14911,15 @@
     </row>
     <row r="58" spans="1:7" ht="12" customHeight="1">
       <c r="A58" s="119" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B58" s="120"/>
       <c r="C58" s="120" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D58" s="120"/>
       <c r="E58" s="120" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F58" t="str">
         <f t="shared" si="1"/>
@@ -14999,15 +14932,15 @@
     </row>
     <row r="59" spans="1:7" ht="12" customHeight="1">
       <c r="A59" s="119" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B59" s="120"/>
       <c r="C59" s="120" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D59" s="120"/>
       <c r="E59" s="120" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F59" t="str">
         <f t="shared" si="1"/>
@@ -15020,15 +14953,15 @@
     </row>
     <row r="60" spans="1:7" ht="12" customHeight="1">
       <c r="A60" s="119" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B60" s="120"/>
       <c r="C60" s="120" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D60" s="120"/>
       <c r="E60" s="120" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F60" t="str">
         <f t="shared" si="1"/>
@@ -15041,7 +14974,7 @@
     </row>
     <row r="61" spans="1:7" ht="12" customHeight="1">
       <c r="A61" s="121" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B61" s="120"/>
       <c r="C61" s="120"/>
@@ -15058,7 +14991,7 @@
     </row>
     <row r="62" spans="1:7" ht="12" customHeight="1">
       <c r="A62" s="119" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B62" s="120"/>
       <c r="C62" s="120"/>
@@ -15075,15 +15008,15 @@
     </row>
     <row r="63" spans="1:7" ht="12" customHeight="1">
       <c r="A63" s="122" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B63" s="120"/>
       <c r="C63" s="120" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D63" s="120"/>
       <c r="E63" s="120" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F63" t="str">
         <f t="shared" si="1"/>
@@ -15096,15 +15029,15 @@
     </row>
     <row r="64" spans="1:7" ht="12" customHeight="1">
       <c r="A64" s="119" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B64" s="120"/>
       <c r="C64" s="120" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D64" s="120"/>
       <c r="E64" s="120" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F64" t="str">
         <f t="shared" si="1"/>
@@ -15117,15 +15050,15 @@
     </row>
     <row r="65" spans="1:7" ht="12" customHeight="1">
       <c r="A65" s="122" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B65" s="120"/>
       <c r="C65" s="120" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D65" s="120"/>
       <c r="E65" s="120" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F65" t="str">
         <f t="shared" si="1"/>
@@ -15138,7 +15071,7 @@
     </row>
     <row r="66" spans="1:7" ht="12" customHeight="1">
       <c r="A66" s="122" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B66" s="120"/>
       <c r="C66" s="120"/>
@@ -15155,7 +15088,7 @@
     </row>
     <row r="67" spans="1:7" ht="12" customHeight="1">
       <c r="A67" s="122" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B67" s="120"/>
       <c r="C67" s="120"/>
@@ -15172,7 +15105,7 @@
     </row>
     <row r="68" spans="1:7" ht="12" customHeight="1">
       <c r="A68" s="119" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B68" s="120"/>
       <c r="C68" s="120"/>
@@ -15189,15 +15122,15 @@
     </row>
     <row r="69" spans="1:7" ht="12" customHeight="1">
       <c r="A69" s="119" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B69" s="120"/>
       <c r="C69" s="120" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D69" s="120"/>
       <c r="E69" s="120" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F69" t="str">
         <f t="shared" si="1"/>
@@ -15210,15 +15143,15 @@
     </row>
     <row r="70" spans="1:7" ht="12" customHeight="1">
       <c r="A70" s="121" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B70" s="120"/>
       <c r="C70" s="120" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D70" s="120"/>
       <c r="E70" s="120" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F70" t="str">
         <f t="shared" si="1"/>
@@ -15437,51 +15370,51 @@
   <sheetData>
     <row r="1" spans="1:17" ht="18.75" customHeight="1">
       <c r="A1" s="118" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="118" t="s">
+        <v>184</v>
+      </c>
+      <c r="C1" s="123" t="s">
         <v>185</v>
       </c>
-      <c r="C1" s="123" t="s">
+      <c r="D1" s="123" t="s">
         <v>186</v>
       </c>
-      <c r="D1" s="123" t="s">
+      <c r="E1" s="123" t="s">
         <v>187</v>
       </c>
-      <c r="E1" s="123" t="s">
+      <c r="F1" s="123" t="s">
         <v>188</v>
       </c>
-      <c r="F1" s="123" t="s">
+      <c r="G1" s="123" t="s">
         <v>189</v>
       </c>
-      <c r="G1" s="123" t="s">
+      <c r="H1" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="H1" s="123" t="s">
-        <v>191</v>
-      </c>
       <c r="I1" s="123" t="s">
+        <v>310</v>
+      </c>
+      <c r="J1" s="123" t="s">
+        <v>311</v>
+      </c>
+      <c r="K1" s="123" t="s">
         <v>312</v>
       </c>
-      <c r="J1" s="123" t="s">
+      <c r="L1" s="123" t="s">
         <v>313</v>
       </c>
-      <c r="K1" s="123" t="s">
+      <c r="M1" s="123" t="s">
         <v>314</v>
       </c>
-      <c r="L1" s="123" t="s">
+      <c r="N1" s="123" t="s">
         <v>315</v>
-      </c>
-      <c r="M1" s="123" t="s">
-        <v>316</v>
-      </c>
-      <c r="N1" s="123" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="13.5" customHeight="1">
       <c r="A2" s="121" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B2" s="124">
         <v>21519965336</v>
@@ -15523,7 +15456,7 @@
     </row>
     <row r="3" spans="1:17" ht="13.5" customHeight="1">
       <c r="A3" s="119" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B3" s="124">
         <v>21466362478</v>
@@ -15565,7 +15498,7 @@
     </row>
     <row r="4" spans="1:17" ht="13.5" customHeight="1">
       <c r="A4" s="119" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B4" s="124">
         <v>53602858</v>
@@ -15607,7 +15540,7 @@
     </row>
     <row r="5" spans="1:17" ht="13.5" customHeight="1">
       <c r="A5" s="121" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B5" s="124">
         <v>17650813148</v>
@@ -15649,7 +15582,7 @@
     </row>
     <row r="6" spans="1:17" ht="13.5" customHeight="1">
       <c r="A6" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B6" s="124">
         <v>17650813148</v>
@@ -15691,7 +15624,7 @@
     </row>
     <row r="7" spans="1:17" ht="13.5" customHeight="1">
       <c r="A7" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B7" s="124">
         <v>2126111102</v>
@@ -15733,7 +15666,7 @@
     </row>
     <row r="8" spans="1:17" ht="13.5" customHeight="1">
       <c r="A8" s="119" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B8" s="124">
         <v>18479894308</v>
@@ -15775,7 +15708,7 @@
     </row>
     <row r="9" spans="1:17" ht="13.5" customHeight="1">
       <c r="A9" s="119" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B9" s="124">
         <v>91576826</v>
@@ -15817,7 +15750,7 @@
     </row>
     <row r="10" spans="1:17" ht="13.5" customHeight="1">
       <c r="A10" s="119" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B10" s="124">
         <v>2863615436</v>
@@ -15859,7 +15792,7 @@
     </row>
     <row r="11" spans="1:17" ht="13.5" customHeight="1">
       <c r="A11" s="121" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B11" s="124">
         <v>3869152188</v>
@@ -15901,7 +15834,7 @@
     </row>
     <row r="12" spans="1:17" ht="13.5" customHeight="1">
       <c r="A12" s="121" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B12" s="124">
         <v>2161095954</v>
@@ -15943,7 +15876,7 @@
     </row>
     <row r="13" spans="1:17" ht="13.5" customHeight="1">
       <c r="A13" s="119" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B13" s="124">
         <v>1229848831</v>
@@ -15985,7 +15918,7 @@
     </row>
     <row r="14" spans="1:17" ht="11.25" customHeight="1">
       <c r="A14" s="122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B14" s="124">
         <v>88091340</v>
@@ -16027,7 +15960,7 @@
     </row>
     <row r="15" spans="1:17" ht="13.5" customHeight="1">
       <c r="A15" s="119" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B15" s="124">
         <v>110546776</v>
@@ -16069,7 +16002,7 @@
     </row>
     <row r="16" spans="1:17" ht="13.5" customHeight="1">
       <c r="A16" s="119" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B16" s="124">
         <v>7859988</v>
@@ -16111,7 +16044,7 @@
     </row>
     <row r="17" spans="1:17" ht="13.5" customHeight="1">
       <c r="A17" s="119" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B17" s="124">
         <v>43323349</v>
@@ -16153,7 +16086,7 @@
     </row>
     <row r="18" spans="1:17" ht="13.5" customHeight="1">
       <c r="A18" s="119" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B18" s="124">
         <v>10884279</v>
@@ -16195,7 +16128,7 @@
     </row>
     <row r="19" spans="1:17" ht="13.5" customHeight="1">
       <c r="A19" s="119" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B19" s="124">
         <v>658900</v>
@@ -16237,7 +16170,7 @@
     </row>
     <row r="20" spans="1:17" ht="13.5" customHeight="1">
       <c r="A20" s="119" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B20" s="124">
         <v>9937528</v>
@@ -16279,7 +16212,7 @@
     </row>
     <row r="21" spans="1:17" ht="13.5" customHeight="1">
       <c r="A21" s="119" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B21" s="124">
         <v>61818760</v>
@@ -16321,7 +16254,7 @@
     </row>
     <row r="22" spans="1:17" ht="13.5" customHeight="1">
       <c r="A22" s="119" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B22" s="124">
         <v>71625807</v>
@@ -16363,7 +16296,7 @@
     </row>
     <row r="23" spans="1:17" ht="13.5" customHeight="1">
       <c r="A23" s="119" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B23" s="124">
         <v>94500000</v>
@@ -16405,7 +16338,7 @@
     </row>
     <row r="24" spans="1:17" ht="13.5" customHeight="1">
       <c r="A24" s="119" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B24" s="124">
         <v>48751589</v>
@@ -16447,7 +16380,7 @@
     </row>
     <row r="25" spans="1:17" ht="13.5" customHeight="1">
       <c r="A25" s="119" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B25" s="124">
         <v>155024259</v>
@@ -16489,7 +16422,7 @@
     </row>
     <row r="26" spans="1:17" ht="13.5" customHeight="1">
       <c r="A26" s="119" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B26" s="124">
         <v>11781419</v>
@@ -16531,7 +16464,7 @@
     </row>
     <row r="27" spans="1:17" ht="13.5" customHeight="1">
       <c r="A27" s="119" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B27" s="124">
         <v>18876205</v>
@@ -16573,7 +16506,7 @@
     </row>
     <row r="28" spans="1:17" ht="11.25" customHeight="1">
       <c r="A28" s="122" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B28" s="124">
         <v>196598820</v>
@@ -16615,7 +16548,7 @@
     </row>
     <row r="29" spans="1:17" ht="13.5" customHeight="1">
       <c r="A29" s="119" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B29" s="124">
         <v>968104</v>
@@ -16657,7 +16590,7 @@
     </row>
     <row r="30" spans="1:17" ht="13.5" customHeight="1">
       <c r="A30" s="119" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B30" s="124">
         <v>1708056234</v>
@@ -16699,7 +16632,7 @@
     </row>
     <row r="31" spans="1:17" ht="11.25" customHeight="1">
       <c r="A31" s="121" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B31" s="124">
         <v>145089917</v>
@@ -16741,7 +16674,7 @@
     </row>
     <row r="32" spans="1:17" ht="13.5" customHeight="1">
       <c r="A32" s="119" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B32" s="124">
         <v>113934601</v>
@@ -16783,7 +16716,7 @@
     </row>
     <row r="33" spans="1:17" ht="13.5" customHeight="1">
       <c r="A33" s="122" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B33" s="124">
         <v>9493467</v>
@@ -16825,7 +16758,7 @@
     </row>
     <row r="34" spans="1:17" ht="13.5" customHeight="1">
       <c r="A34" s="122" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B34" s="124">
         <v>7089909</v>
@@ -16867,7 +16800,7 @@
     </row>
     <row r="35" spans="1:17" ht="13.5" customHeight="1">
       <c r="A35" s="119" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B35" s="124">
         <v>14571940</v>
@@ -16909,7 +16842,7 @@
     </row>
     <row r="36" spans="1:17" ht="13.5" customHeight="1">
       <c r="A36" s="119" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B36" s="124">
         <v>1315405</v>
@@ -16951,7 +16884,7 @@
     </row>
     <row r="37" spans="1:17" ht="13.5" customHeight="1">
       <c r="A37" s="119" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B37" s="124">
         <v>1131469</v>
@@ -16993,7 +16926,7 @@
     </row>
     <row r="38" spans="1:17" ht="11.25" customHeight="1">
       <c r="A38" s="122" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B38" s="124">
         <v>2000</v>
@@ -17035,7 +16968,7 @@
     </row>
     <row r="39" spans="1:17" ht="13.5" customHeight="1">
       <c r="A39" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B39" s="124">
         <v>181936</v>
@@ -17077,7 +17010,7 @@
     </row>
     <row r="40" spans="1:17" ht="13.5" customHeight="1">
       <c r="A40" s="121" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B40" s="124">
         <v>1851830746</v>
@@ -17119,7 +17052,7 @@
     </row>
     <row r="41" spans="1:17" ht="11.25" customHeight="1">
       <c r="A41" s="121" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B41" s="124">
         <v>0</v>
@@ -17161,7 +17094,7 @@
     </row>
     <row r="42" spans="1:17" ht="13.5" customHeight="1">
       <c r="A42" s="119" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B42" s="124">
         <v>1851830746</v>
@@ -17476,51 +17409,51 @@
   <sheetData>
     <row r="1" spans="1:16" ht="16.5" customHeight="1">
       <c r="A1" s="118" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="118" t="s">
+        <v>184</v>
+      </c>
+      <c r="C1" s="123" t="s">
         <v>185</v>
       </c>
-      <c r="C1" s="123" t="s">
+      <c r="D1" s="123" t="s">
         <v>186</v>
       </c>
-      <c r="D1" s="123" t="s">
+      <c r="E1" s="123" t="s">
         <v>187</v>
       </c>
-      <c r="E1" s="123" t="s">
+      <c r="F1" s="123" t="s">
         <v>188</v>
       </c>
-      <c r="F1" s="123" t="s">
+      <c r="G1" s="123" t="s">
         <v>189</v>
       </c>
-      <c r="G1" s="123" t="s">
+      <c r="H1" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="H1" s="123" t="s">
-        <v>191</v>
-      </c>
       <c r="I1" s="123" t="s">
+        <v>310</v>
+      </c>
+      <c r="J1" s="123" t="s">
+        <v>311</v>
+      </c>
+      <c r="K1" s="123" t="s">
         <v>312</v>
       </c>
-      <c r="J1" s="123" t="s">
+      <c r="L1" s="123" t="s">
         <v>313</v>
       </c>
-      <c r="K1" s="123" t="s">
+      <c r="M1" s="123" t="s">
         <v>314</v>
       </c>
-      <c r="L1" s="123" t="s">
+      <c r="N1" s="123" t="s">
         <v>315</v>
-      </c>
-      <c r="M1" s="123" t="s">
-        <v>316</v>
-      </c>
-      <c r="N1" s="123" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="13.5" customHeight="1">
       <c r="A2" s="121" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B2" s="124">
         <v>19689650568</v>
@@ -17562,7 +17495,7 @@
     </row>
     <row r="3" spans="1:16" ht="13.5" customHeight="1">
       <c r="A3" s="119" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B3" s="124">
         <v>19576088228</v>
@@ -17604,7 +17537,7 @@
     </row>
     <row r="4" spans="1:16" ht="13.5" customHeight="1">
       <c r="A4" s="119" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B4" s="124">
         <v>113562340</v>
@@ -17646,7 +17579,7 @@
     </row>
     <row r="5" spans="1:16" ht="13.5" customHeight="1">
       <c r="A5" s="121" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B5" s="124">
         <v>16467043458</v>
@@ -17688,7 +17621,7 @@
     </row>
     <row r="6" spans="1:16" ht="13.5" customHeight="1">
       <c r="A6" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B6" s="124">
         <v>16467043458</v>
@@ -17730,7 +17663,7 @@
     </row>
     <row r="7" spans="1:16" ht="13.5" customHeight="1">
       <c r="A7" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B7" s="124">
         <v>2098835763</v>
@@ -17772,7 +17705,7 @@
     </row>
     <row r="8" spans="1:16" ht="13.5" customHeight="1">
       <c r="A8" s="119" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B8" s="124">
         <v>16610240340</v>
@@ -17814,7 +17747,7 @@
     </row>
     <row r="9" spans="1:16" ht="13.5" customHeight="1">
       <c r="A9" s="119" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B9" s="124">
         <v>62693149</v>
@@ -17856,7 +17789,7 @@
     </row>
     <row r="10" spans="1:16" ht="13.5" customHeight="1">
       <c r="A10" s="119" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B10" s="124">
         <v>2179339496</v>
@@ -17898,7 +17831,7 @@
     </row>
     <row r="11" spans="1:16" ht="13.5" customHeight="1">
       <c r="A11" s="121" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B11" s="124">
         <v>3222607110</v>
@@ -17940,7 +17873,7 @@
     </row>
     <row r="12" spans="1:16" ht="13.5" customHeight="1">
       <c r="A12" s="121" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B12" s="124">
         <v>1948634682</v>
@@ -17982,7 +17915,7 @@
     </row>
     <row r="13" spans="1:16" ht="13.5" customHeight="1">
       <c r="A13" s="119" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B13" s="124">
         <v>1170857179</v>
@@ -18024,7 +17957,7 @@
     </row>
     <row r="14" spans="1:16" ht="13.5" customHeight="1">
       <c r="A14" s="119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B14" s="124">
         <v>3419250</v>
@@ -18066,7 +17999,7 @@
     </row>
     <row r="15" spans="1:16" ht="13.5" customHeight="1">
       <c r="A15" s="119" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B15" s="124">
         <v>97328369</v>
@@ -18108,7 +18041,7 @@
     </row>
     <row r="16" spans="1:16" ht="13.5" customHeight="1">
       <c r="A16" s="119" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B16" s="124">
         <v>4245185</v>
@@ -18150,7 +18083,7 @@
     </row>
     <row r="17" spans="1:16" ht="13.5" customHeight="1">
       <c r="A17" s="119" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B17" s="124">
         <v>39117430</v>
@@ -18192,7 +18125,7 @@
     </row>
     <row r="18" spans="1:16" ht="13.5" customHeight="1">
       <c r="A18" s="119" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B18" s="124">
         <v>10964361</v>
@@ -18234,7 +18167,7 @@
     </row>
     <row r="19" spans="1:16" ht="13.5" customHeight="1">
       <c r="A19" s="119" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B19" s="124">
         <v>537830</v>
@@ -18276,7 +18209,7 @@
     </row>
     <row r="20" spans="1:16" ht="13.5" customHeight="1">
       <c r="A20" s="119" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B20" s="124">
         <v>9546653</v>
@@ -18318,7 +18251,7 @@
     </row>
     <row r="21" spans="1:16" ht="13.5" customHeight="1">
       <c r="A21" s="119" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B21" s="124">
         <v>58666660</v>
@@ -18360,7 +18293,7 @@
     </row>
     <row r="22" spans="1:16" ht="13.5" customHeight="1">
       <c r="A22" s="119" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B22" s="124">
         <v>86462149</v>
@@ -18402,7 +18335,7 @@
     </row>
     <row r="23" spans="1:16" ht="13.5" customHeight="1">
       <c r="A23" s="119" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B23" s="124">
         <v>94500000</v>
@@ -18444,7 +18377,7 @@
     </row>
     <row r="24" spans="1:16" ht="13.5" customHeight="1">
       <c r="A24" s="119" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B24" s="124">
         <v>49358485</v>
@@ -18486,7 +18419,7 @@
     </row>
     <row r="25" spans="1:16" ht="13.5" customHeight="1">
       <c r="A25" s="119" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B25" s="124">
         <v>136538142</v>
@@ -18528,7 +18461,7 @@
     </row>
     <row r="26" spans="1:16" ht="13.5" customHeight="1">
       <c r="A26" s="119" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B26" s="124">
         <v>16218767</v>
@@ -18570,7 +18503,7 @@
     </row>
     <row r="27" spans="1:16" ht="13.5" customHeight="1">
       <c r="A27" s="119" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B27" s="124">
         <v>10701551</v>
@@ -18612,7 +18545,7 @@
     </row>
     <row r="28" spans="1:16" ht="13.5" customHeight="1">
       <c r="A28" s="119" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B28" s="124">
         <v>157513549</v>
@@ -18654,7 +18587,7 @@
     </row>
     <row r="29" spans="1:16" ht="13.5" customHeight="1">
       <c r="A29" s="119" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B29" s="124">
         <v>2659122</v>
@@ -18696,7 +18629,7 @@
     </row>
     <row r="30" spans="1:16" ht="13.5" customHeight="1">
       <c r="A30" s="121" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B30" s="124">
         <v>1273972428</v>
@@ -18738,7 +18671,7 @@
     </row>
     <row r="31" spans="1:16" ht="13.5" customHeight="1">
       <c r="A31" s="121" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B31" s="124">
         <v>110853921</v>
@@ -18780,7 +18713,7 @@
     </row>
     <row r="32" spans="1:16" ht="13.5" customHeight="1">
       <c r="A32" s="119" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B32" s="124">
         <v>107412653</v>
@@ -18822,7 +18755,7 @@
     </row>
     <row r="33" spans="1:16" ht="13.5" customHeight="1">
       <c r="A33" s="119" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B33" s="124">
         <v>726273</v>
@@ -18864,7 +18797,7 @@
     </row>
     <row r="34" spans="1:16" ht="13.5" customHeight="1">
       <c r="A34" s="119" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B34" s="124">
         <v>2714995</v>
@@ -18906,7 +18839,7 @@
     </row>
     <row r="35" spans="1:16" ht="13.5" customHeight="1">
       <c r="A35" s="121" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B35" s="124">
         <v>40033270</v>
@@ -18948,7 +18881,7 @@
     </row>
     <row r="36" spans="1:16" ht="13.5" customHeight="1">
       <c r="A36" s="119" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B36" s="124">
         <v>1282550</v>
@@ -18990,7 +18923,7 @@
     </row>
     <row r="37" spans="1:16" ht="13.5" customHeight="1">
       <c r="A37" s="119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B37" s="124">
         <v>214000</v>
@@ -19032,7 +18965,7 @@
     </row>
     <row r="38" spans="1:16" ht="13.5" customHeight="1">
       <c r="A38" s="119" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B38" s="124">
         <v>38536720</v>
@@ -19074,7 +19007,7 @@
     </row>
     <row r="39" spans="1:16" ht="13.5" customHeight="1">
       <c r="A39" s="121" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B39" s="124">
         <v>1344793079</v>
@@ -19116,7 +19049,7 @@
     </row>
     <row r="40" spans="1:16" ht="13.5" customHeight="1">
       <c r="A40" s="121" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B40" s="124">
         <v>0</v>
@@ -19158,7 +19091,7 @@
     </row>
     <row r="41" spans="1:16" ht="13.5" customHeight="1">
       <c r="A41" s="121" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B41" s="124">
         <v>1344793079</v>
@@ -19382,31 +19315,31 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" customHeight="1">
       <c r="A1" s="159" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="159" t="s">
         <v>44</v>
-      </c>
-      <c r="B1" s="159" t="s">
-        <v>45</v>
       </c>
       <c r="C1" s="160"/>
       <c r="D1" s="159" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E1" s="160"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" customHeight="1">
       <c r="A2" s="162"/>
       <c r="B2" s="159" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="160"/>
       <c r="D2" s="159" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E2" s="160"/>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1">
       <c r="A3" s="121" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B3" s="124">
         <v>0</v>
@@ -19431,7 +19364,7 @@
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1">
       <c r="A4" s="119" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B4" s="124">
         <v>21466362478</v>
@@ -19456,7 +19389,7 @@
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
       <c r="A5" s="119" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B5" s="124">
         <v>53602858</v>
@@ -19481,7 +19414,7 @@
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
       <c r="A6" s="121" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B6" s="124">
         <v>0</v>
@@ -19506,7 +19439,7 @@
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1">
       <c r="A7" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B7" s="124">
         <v>0</v>
@@ -19531,7 +19464,7 @@
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1">
       <c r="A8" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B8" s="124">
         <v>2126111102</v>
@@ -19556,7 +19489,7 @@
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
       <c r="A9" s="119" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B9" s="124">
         <v>18479894308</v>
@@ -19581,7 +19514,7 @@
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1">
       <c r="A10" s="119" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B10" s="124">
         <v>91576826</v>
@@ -19606,7 +19539,7 @@
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
       <c r="A11" s="119" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B11" s="124">
         <v>2863615436</v>
@@ -19631,7 +19564,7 @@
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1">
       <c r="A12" s="121" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B12" s="124">
         <v>0</v>
@@ -19656,7 +19589,7 @@
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1">
       <c r="A13" s="121" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B13" s="124">
         <v>0</v>
@@ -19681,7 +19614,7 @@
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1">
       <c r="A14" s="119" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B14" s="124">
         <v>1229848831</v>
@@ -19706,7 +19639,7 @@
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1">
       <c r="A15" s="119" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B15" s="124">
         <v>0</v>
@@ -19731,7 +19664,7 @@
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1">
       <c r="A16" s="119" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B16" s="124">
         <v>0</v>
@@ -19756,7 +19689,7 @@
     </row>
     <row r="17" spans="1:7" ht="13.5" customHeight="1">
       <c r="A17" s="119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B17" s="124">
         <v>88091340</v>
@@ -19781,7 +19714,7 @@
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1">
       <c r="A18" s="119" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B18" s="124">
         <v>110546776</v>
@@ -19806,7 +19739,7 @@
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
       <c r="A19" s="119" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B19" s="124">
         <v>7859988</v>
@@ -19831,7 +19764,7 @@
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
       <c r="A20" s="119" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B20" s="124">
         <v>43323349</v>
@@ -19856,7 +19789,7 @@
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1">
       <c r="A21" s="119" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B21" s="124">
         <v>10884279</v>
@@ -19881,7 +19814,7 @@
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1">
       <c r="A22" s="119" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B22" s="124">
         <v>658900</v>
@@ -19906,7 +19839,7 @@
     </row>
     <row r="23" spans="1:7" ht="13.5" customHeight="1">
       <c r="A23" s="119" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B23" s="124">
         <v>9937528</v>
@@ -19931,7 +19864,7 @@
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1">
       <c r="A24" s="119" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B24" s="124">
         <v>61818760</v>
@@ -19956,7 +19889,7 @@
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1">
       <c r="A25" s="119" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B25" s="124">
         <v>71625807</v>
@@ -19981,7 +19914,7 @@
     </row>
     <row r="26" spans="1:7" ht="13.5" customHeight="1">
       <c r="A26" s="119" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B26" s="124">
         <v>94500000</v>
@@ -20006,7 +19939,7 @@
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
       <c r="A27" s="119" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B27" s="124">
         <v>48751589</v>
@@ -20031,7 +19964,7 @@
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
       <c r="A28" s="119" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B28" s="124">
         <v>155024259</v>
@@ -20056,7 +19989,7 @@
     </row>
     <row r="29" spans="1:7" ht="13.5" customHeight="1">
       <c r="A29" s="119" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B29" s="124">
         <v>11781419</v>
@@ -20081,7 +20014,7 @@
     </row>
     <row r="30" spans="1:7" ht="11.25" customHeight="1">
       <c r="A30" s="119" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B30" s="124">
         <v>18876205</v>
@@ -20106,7 +20039,7 @@
     </row>
     <row r="31" spans="1:7" ht="13.5" customHeight="1">
       <c r="A31" s="119" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B31" s="124">
         <v>196598820</v>
@@ -20131,7 +20064,7 @@
     </row>
     <row r="32" spans="1:7" ht="13.5" customHeight="1">
       <c r="A32" s="119" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B32" s="124">
         <v>0</v>
@@ -20156,7 +20089,7 @@
     </row>
     <row r="33" spans="1:7" ht="13.5" customHeight="1">
       <c r="A33" s="119" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B33" s="124">
         <v>968104</v>
@@ -20181,7 +20114,7 @@
     </row>
     <row r="34" spans="1:7" ht="13.5" customHeight="1">
       <c r="A34" s="119" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B34" s="124">
         <v>0</v>
@@ -20206,7 +20139,7 @@
     </row>
     <row r="35" spans="1:7" ht="13.5" customHeight="1">
       <c r="A35" s="121" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B35" s="124">
         <v>0</v>
@@ -20231,7 +20164,7 @@
     </row>
     <row r="36" spans="1:7" ht="13.5" customHeight="1">
       <c r="A36" s="122" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B36" s="124">
         <v>113934601</v>
@@ -20256,7 +20189,7 @@
     </row>
     <row r="37" spans="1:7" ht="13.5" customHeight="1">
       <c r="A37" s="119" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B37" s="124">
         <v>9493467</v>
@@ -20281,7 +20214,7 @@
     </row>
     <row r="38" spans="1:7" ht="13.5" customHeight="1">
       <c r="A38" s="119" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B38" s="124">
         <v>7089909</v>
@@ -20306,7 +20239,7 @@
     </row>
     <row r="39" spans="1:7" ht="11.25" customHeight="1">
       <c r="A39" s="119" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B39" s="124">
         <v>14571940</v>
@@ -20331,7 +20264,7 @@
     </row>
     <row r="40" spans="1:7" ht="13.5" customHeight="1">
       <c r="A40" s="119" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B40" s="124">
         <v>0</v>
@@ -20356,7 +20289,7 @@
     </row>
     <row r="41" spans="1:7" ht="11.25" customHeight="1">
       <c r="A41" s="119" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B41" s="124">
         <v>1131469</v>
@@ -20381,7 +20314,7 @@
     </row>
     <row r="42" spans="1:7" ht="11.25" customHeight="1">
       <c r="A42" s="119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B42" s="124">
         <v>0</v>
@@ -20406,7 +20339,7 @@
     </row>
     <row r="43" spans="1:7" ht="13.5" customHeight="1">
       <c r="A43" s="119" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B43" s="124">
         <v>2000</v>
@@ -20431,7 +20364,7 @@
     </row>
     <row r="44" spans="1:7" ht="13.5" customHeight="1">
       <c r="A44" s="122" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B44" s="124">
         <v>181936</v>
@@ -20456,7 +20389,7 @@
     </row>
     <row r="45" spans="1:7" ht="11.25" customHeight="1">
       <c r="A45" s="119" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B45" s="124">
         <v>0</v>
@@ -20481,7 +20414,7 @@
     </row>
     <row r="46" spans="1:7" ht="13.5" customHeight="1">
       <c r="A46" s="119" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B46" s="124">
         <v>0</v>
@@ -20506,7 +20439,7 @@
     </row>
     <row r="47" spans="1:7" ht="13.5" customHeight="1">
       <c r="A47" s="119" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B47" s="124">
         <v>0</v>
@@ -20531,7 +20464,7 @@
     </row>
     <row r="48" spans="1:7" ht="11.25" customHeight="1">
       <c r="A48" s="119" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B48" s="124">
         <v>0</v>

--- a/monthly_closing_template.xlsx
+++ b/monthly_closing_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\창현관리부\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F09BE58-ADDB-4C6E-8BDF-1BCA0F828D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E719FB-D576-43C7-A819-D00931D8F37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="1230" windowWidth="14715" windowHeight="14250" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="인덱스" sheetId="1" r:id="rId1"/>
@@ -2181,26 +2181,23 @@
     <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2212,6 +2209,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2230,9 +2233,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2696,7 +2696,7 @@
             <c:strRef>
               <c:f>요약!$A$29:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1월</c:v>
                 </c:pt>
@@ -2718,6 +2718,21 @@
                 <c:pt idx="6">
                   <c:v>7월</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>8월</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9월</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10월</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11월</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12월</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
@@ -2726,7 +2741,7 @@
               <c:f>요약!$B$29:$B$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0,;\(#,##0,\);\-</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>2735381647</c:v>
                 </c:pt>
@@ -2747,6 +2762,21 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2306642756</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2863,7 +2893,7 @@
             <c:strRef>
               <c:f>요약!$A$29:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1월</c:v>
                 </c:pt>
@@ -2885,6 +2915,21 @@
                 <c:pt idx="6">
                   <c:v>7월</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>8월</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9월</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10월</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11월</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12월</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
@@ -2893,7 +2938,7 @@
               <c:f>요약!$C$29:$C$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0,;\(#,##0,\);\-</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>201922246</c:v>
                 </c:pt>
@@ -2914,6 +2959,21 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>166909868</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3408,17 +3468,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1">
-      <c r="A1" s="134" t="str">
+      <c r="A1" s="126" t="str">
         <f>TEXT($K$1,"yyyy")&amp;"년 1월~"&amp;MONTH($K$1)&amp;"월 월차 결산서 [ ㈜ 창현 ]"</f>
         <v>2026년 1월~7월 월차 결산서 [ ㈜ 창현 ]</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
       <c r="J1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3436,175 +3496,175 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="136" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
     </row>
     <row r="4" spans="1:13" ht="34.5" customHeight="1"/>
     <row r="5" spans="1:13" ht="40.5" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="136" t="s">
+      <c r="B5" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="131"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="131"/>
-      <c r="F5" s="131"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="132"/>
+      <c r="C5" s="129"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="130"/>
     </row>
     <row r="6" spans="1:13" ht="43.5" customHeight="1">
       <c r="A6" s="8">
         <v>1</v>
       </c>
-      <c r="B6" s="133" t="s">
+      <c r="B6" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="131"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="131"/>
-      <c r="F6" s="131"/>
-      <c r="G6" s="131"/>
-      <c r="H6" s="132"/>
+      <c r="C6" s="129"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="130"/>
     </row>
     <row r="7" spans="1:13" ht="43.5" customHeight="1">
       <c r="A7" s="9">
         <v>2</v>
       </c>
-      <c r="B7" s="130" t="str">
+      <c r="B7" s="135" t="str">
         <f>"재무상태표 ["&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 현재]"</f>
         <v>재무상태표 [2026년07월31일 현재]</v>
       </c>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="132"/>
+      <c r="C7" s="129"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="130"/>
     </row>
     <row r="8" spans="1:13" ht="43.5" customHeight="1">
       <c r="A8" s="8">
         <v>3</v>
       </c>
-      <c r="B8" s="133" t="str">
+      <c r="B8" s="140" t="str">
         <f>"손익계산서(매출액대비 비율분석) ["&amp;TEXT(DATE(YEAR($K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR($K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR($K$1),1,1)),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
         <v>손익계산서(매출액대비 비율분석) [2026년01월01일 부터 2026년07월31일 까지]</v>
       </c>
-      <c r="C8" s="131"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="131"/>
-      <c r="F8" s="131"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="132"/>
+      <c r="C8" s="129"/>
+      <c r="D8" s="129"/>
+      <c r="E8" s="129"/>
+      <c r="F8" s="129"/>
+      <c r="G8" s="129"/>
+      <c r="H8" s="130"/>
     </row>
     <row r="9" spans="1:13" ht="43.5" customHeight="1">
       <c r="A9" s="9">
         <v>4</v>
       </c>
-      <c r="B9" s="130" t="str">
+      <c r="B9" s="135" t="str">
         <f>"손익계산서(전월대비 증감) ["&amp;TEXT(EOMONTH($K$1,-2)+1,"yyyy")&amp;"년"&amp;TEXT(MONTH(EOMONTH($K$1,-2)+1),"00")&amp;"월"&amp;TEXT(DAY(EOMONTH($K$1,-2)+1),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
         <v>손익계산서(전월대비 증감) [2026년06월01일 부터 2026년07월31일 까지]</v>
       </c>
-      <c r="C9" s="131"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="131"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="132"/>
+      <c r="C9" s="129"/>
+      <c r="D9" s="129"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="130"/>
     </row>
     <row r="10" spans="1:13" ht="43.5" customHeight="1">
       <c r="A10" s="8">
         <v>5</v>
       </c>
-      <c r="B10" s="138" t="str">
+      <c r="B10" s="137" t="str">
         <f>"기간별손익계산서 ["&amp;TEXT(DATE(YEAR($K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR($K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR($K$1),1,1)),"00")&amp;"일"&amp;" 부터 "&amp;TEXT($K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH($K$1),"00")&amp;"월"&amp;TEXT(DAY($K$1),"00")&amp;"일"&amp;" 까지]"</f>
         <v>기간별손익계산서 [2026년01월01일 부터 2026년07월31일 까지]</v>
       </c>
-      <c r="C10" s="131"/>
-      <c r="D10" s="131"/>
-      <c r="E10" s="131"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="132"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="129"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="130"/>
     </row>
     <row r="11" spans="1:13" ht="43.5" customHeight="1">
       <c r="A11" s="9">
         <v>6</v>
       </c>
-      <c r="B11" s="139" t="str">
+      <c r="B11" s="138" t="str">
         <f>TEXT($K$1,"yyyy")&amp;"년 차량별 비용현황[연간누계/월별/당월상세]"</f>
         <v>2026년 차량별 비용현황[연간누계/월별/당월상세]</v>
       </c>
-      <c r="C11" s="131"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="132"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="130"/>
     </row>
     <row r="12" spans="1:13" ht="43.5" customHeight="1">
       <c r="A12" s="8">
         <v>7</v>
       </c>
-      <c r="B12" s="138" t="str">
+      <c r="B12" s="137" t="str">
         <f>TEXT($K$1,"yyyy")&amp;"년 운송비 개인별 비용"</f>
         <v>2026년 운송비 개인별 비용</v>
       </c>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="131"/>
-      <c r="G12" s="131"/>
-      <c r="H12" s="132"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="130"/>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1"/>
     <row r="14" spans="1:13" ht="32.25" customHeight="1"/>
     <row r="15" spans="1:13" ht="9.75" customHeight="1">
-      <c r="D15" s="140" t="s">
+      <c r="D15" s="139" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="126" t="s">
+      <c r="E15" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="126" t="s">
+      <c r="F15" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="G15" s="126" t="s">
+      <c r="G15" s="133" t="s">
         <v>9</v>
       </c>
-      <c r="H15" s="126" t="s">
+      <c r="H15" s="133" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="27.75" customHeight="1">
-      <c r="D16" s="129"/>
-      <c r="E16" s="127"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="127"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="134"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="134"/>
     </row>
     <row r="17" spans="4:8" ht="21" customHeight="1">
-      <c r="D17" s="129"/>
-      <c r="E17" s="128"/>
-      <c r="F17" s="128"/>
-      <c r="G17" s="128"/>
-      <c r="H17" s="128"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="131"/>
+      <c r="H17" s="131"/>
     </row>
     <row r="18" spans="4:8" ht="21" customHeight="1">
-      <c r="D18" s="129"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="129"/>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="132"/>
+      <c r="H18" s="132"/>
     </row>
     <row r="19" spans="4:8" ht="15" customHeight="1">
       <c r="D19" s="10"/>
@@ -3615,6 +3675,9 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B6:H6"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="H17:H18"/>
@@ -3631,9 +3694,6 @@
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="E17:E18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B6:H6"/>
   </mergeCells>
   <phoneticPr fontId="41" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -3661,29 +3721,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="141" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
     </row>
     <row r="2" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A2" s="146" t="str">
+      <c r="A2" s="147" t="str">
         <f>TEXT(인덱스!$K$1,"yyyy")&amp;"년 1월 ~ "&amp;MONTH(인덱스!$K$1)&amp;"월 누적 기준 ( 기준일 : "&amp;TEXT(인덱스!$K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH(인덱스!$K$1),"00")&amp;"월"&amp;TEXT(DAY(인덱스!$K$1),"00")&amp;"일 )"</f>
         <v>2026년 1월 ~ 7월 누적 기준 ( 기준일 : 2026년07월31일 )</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
     </row>
     <row r="3" spans="1:8" ht="18.75" customHeight="1"/>
     <row r="4" spans="1:8" ht="15" customHeight="1">
@@ -3692,24 +3752,24 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A5" s="141" t="s">
+      <c r="A5" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="147" t="str">
+      <c r="B5" s="148" t="str">
         <f>"전년동기 대비 ("&amp;(YEAR(인덱스!$K$1)-1)&amp;"년 1~"&amp;MONTH(인덱스!$K$1)&amp;"월)"</f>
         <v>전년동기 대비 (2025년 1~7월)</v>
       </c>
-      <c r="C5" s="144"/>
-      <c r="D5" s="144"/>
-      <c r="E5" s="145"/>
-      <c r="F5" s="143" t="s">
+      <c r="C5" s="145"/>
+      <c r="D5" s="145"/>
+      <c r="E5" s="146"/>
+      <c r="F5" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="144"/>
-      <c r="H5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="146"/>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1">
-      <c r="A6" s="127"/>
+      <c r="A6" s="134"/>
       <c r="B6" s="12" t="str">
         <f>"당기(1~"&amp;MONTH(인덱스!$K$1)&amp;"월)"</f>
         <v>당기(1~7월)</v>
@@ -4320,7 +4380,7 @@
         <v>166909868</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15" hidden="1" customHeight="1">
+    <row r="36" spans="1:3" ht="15" customHeight="1">
       <c r="A36" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),8,1))&amp;"월","")</f>
         <v>8월</v>
@@ -4334,7 +4394,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15" hidden="1" customHeight="1">
+    <row r="37" spans="1:3" ht="15" customHeight="1">
       <c r="A37" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),9,1))&amp;"월","")</f>
         <v>9월</v>
@@ -4348,7 +4408,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15" hidden="1" customHeight="1">
+    <row r="38" spans="1:3" ht="15" customHeight="1">
       <c r="A38" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),10,1))&amp;"월","")</f>
         <v>10월</v>
@@ -4362,7 +4422,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15" hidden="1" customHeight="1">
+    <row r="39" spans="1:3" ht="15" customHeight="1">
       <c r="A39" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),11,1))&amp;"월","")</f>
         <v>11월</v>
@@ -4376,7 +4436,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15" hidden="1" customHeight="1">
+    <row r="40" spans="1:3" ht="15" customHeight="1">
       <c r="A40" s="55" t="str">
         <f>IFERROR(MONTH(DATE(YEAR(인덱스!$K$1),12,1))&amp;"월","")</f>
         <v>12월</v>
@@ -4406,16 +4466,16 @@
     <row r="67" spans="1:8" ht="3.75" customHeight="1"/>
     <row r="68" spans="1:8" ht="27.75" customHeight="1"/>
     <row r="69" spans="1:8" ht="60" customHeight="1">
-      <c r="A69" s="142" t="s">
+      <c r="A69" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="B69" s="135"/>
-      <c r="C69" s="135"/>
-      <c r="D69" s="135"/>
-      <c r="E69" s="135"/>
-      <c r="F69" s="135"/>
-      <c r="G69" s="135"/>
-      <c r="H69" s="135"/>
+      <c r="B69" s="127"/>
+      <c r="C69" s="127"/>
+      <c r="D69" s="127"/>
+      <c r="E69" s="127"/>
+      <c r="F69" s="127"/>
+      <c r="G69" s="127"/>
+      <c r="H69" s="127"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4482,12 +4542,12 @@
       <c r="A1" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
       <c r="H1" s="60"/>
     </row>
     <row r="2" spans="1:11" ht="10.5" customHeight="1">
@@ -4509,12 +4569,12 @@
         <f>"(당기) "&amp;TEXT(DATE(YEAR(인덱스!$K$1),1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR(인덱스!$K$1),1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR(인덱스!$K$1),1,1)),"00")&amp;"일"&amp;" - "&amp;TEXT(인덱스!$K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH(인덱스!$K$1),"00")&amp;"월"&amp;TEXT(DAY(인덱스!$K$1),"00")&amp;"일"</f>
         <v>(당기) 2026년01월01일 - 2026년07월31일</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
       <c r="H3" s="5"/>
       <c r="I3" s="62" t="str">
         <f>IF(ROUND(F50,0)=ROUND(F80,0),"대차검증(전기): 일치","대차검증(전기): 불일치 ⚠")</f>
@@ -4526,12 +4586,12 @@
         <f>"(전기) "&amp;TEXT(DATE(YEAR(인덱스!$K$1)-1,1,1),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR(인덱스!$K$1)-1,1,1)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR(인덱스!$K$1)-1,1,1)),"00")&amp;"일"&amp;" - "&amp;TEXT(DATE(YEAR(인덱스!$K$1)-1,12,31),"yyyy")&amp;"년"&amp;TEXT(MONTH(DATE(YEAR(인덱스!$K$1)-1,12,31)),"00")&amp;"월"&amp;TEXT(DAY(DATE(YEAR(인덱스!$K$1)-1,12,31)),"00")&amp;"일"</f>
         <v>(전기) 2025년01월01일 - 2025년12월31일</v>
       </c>
-      <c r="B4" s="135"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
       <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" customHeight="1"/>
@@ -4550,14 +4610,14 @@
       <c r="B7" s="150" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="132"/>
+      <c r="C7" s="130"/>
       <c r="D7" s="150" t="s">
         <v>45</v>
       </c>
       <c r="E7" s="150" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="132"/>
+      <c r="F7" s="130"/>
       <c r="G7" s="150" t="s">
         <v>47</v>
       </c>
@@ -4573,12 +4633,12 @@
       <c r="B8" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="132"/>
+      <c r="C8" s="130"/>
       <c r="D8" s="152"/>
       <c r="E8" s="150" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="132"/>
+      <c r="F8" s="130"/>
       <c r="G8" s="152"/>
     </row>
     <row r="9" spans="1:11" ht="17.25" customHeight="1">
@@ -7622,12 +7682,12 @@
       <c r="A1" s="149" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
     </row>
     <row r="2" spans="1:11" ht="6.75" customHeight="1">
       <c r="A2" s="61"/>
@@ -7680,14 +7740,14 @@
       <c r="B7" s="150" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="132"/>
+      <c r="C7" s="130"/>
       <c r="D7" s="154" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="150" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="132"/>
+      <c r="F7" s="130"/>
       <c r="G7" s="154" t="s">
         <v>128</v>
       </c>
@@ -7703,12 +7763,12 @@
       <c r="B8" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="132"/>
+      <c r="C8" s="130"/>
       <c r="D8" s="152"/>
       <c r="E8" s="150" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="132"/>
+      <c r="F8" s="130"/>
       <c r="G8" s="152"/>
     </row>
     <row r="9" spans="1:11" ht="16.5" customHeight="1">
@@ -10285,16 +10345,16 @@
         <f>"손익계산서(전월대비 증감내역)"</f>
         <v>손익계산서(전월대비 증감내역)</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
       <c r="L1" s="156"/>
       <c r="M1" s="153"/>
     </row>
@@ -10304,16 +10364,16 @@
         <f>"기간 : "&amp;TEXT(EOMONTH(인덱스!$K$1,-2)+1,"yyyy")&amp;"년"&amp;TEXT(MONTH(EOMONTH(인덱스!$K$1,-2)+1),"00")&amp;"월"&amp;TEXT(DAY(EOMONTH(인덱스!$K$1,-2)+1),"00")&amp;"일"&amp;"부터 - "&amp;TEXT(인덱스!$K$1,"yyyy")&amp;"년"&amp;TEXT(MONTH(인덱스!$K$1),"00")&amp;"월"&amp;TEXT(DAY(인덱스!$K$1),"00")&amp;"일"&amp;"까지"</f>
         <v>기간 : 2026년06월01일부터 - 2026년07월31일까지</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
       <c r="L3" s="156"/>
       <c r="M3" s="153"/>
     </row>
